--- a/data/example/output/dataset.analysis.xlsx
+++ b/data/example/output/dataset.analysis.xlsx
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>11166.35</v>
+        <v>18300</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>1888.95</v>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>11166.35</v>
+        <v>18300</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>3104.36</v>
+        <v>9674.959999999999</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3104.36</v>
+        <v>9674.959999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>13055.3</v>
+        <v>20188.95</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>3104.36</v>
+        <v>9674.959999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>13505.3</v>
+        <v>20638.95</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>3104.36</v>
+        <v>9674.959999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>11166.35</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="27">
@@ -1179,57 +1179,57 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1893.02</v>
+        <v>7215.02</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>452.55</v>
+        <v>1556.79</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>371.69</v>
+        <v>437.55</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Finanzen</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>153.5</v>
+        <v>173.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Mobilität</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>123.6</v>
+        <v>168.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Finanzen</t>
+          <t>Mobilität</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>110</v>
+        <v>123.6</v>
       </c>
     </row>
     <row r="49">
@@ -1293,7 +1293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1348,344 +1348,472 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mobilität</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>26.7</v>
+        <v>0</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>-26.7</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>19</v>
+        <v>1787.9</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>-19</v>
+        <v>-1787.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>13.9</v>
+        <v>388.75</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>-13.9</v>
+        <v>-388.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Mobilität</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-26.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Rückerstattungen</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="5" t="n">
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>February 2025</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Credit in CHF</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Debit in CHF</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Net in CHF</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Einkommen</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>4200</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>1774</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-1774</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>434.7</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>-434.7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Freizeit</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="5" t="n">
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D22" s="5" t="n">
         <v>-3</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>March 2025</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Credit in CHF</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Debit in CHF</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>Net in CHF</t>
         </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Einkommen</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>6966.35</v>
-      </c>
-      <c r="C23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>6966.35</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Leben</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>1787.95</v>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>433.55</v>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>1354.4</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Wohnen</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>1879.12</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>-1879.12</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Einkaufen</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>371.69</v>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>-371.69</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Freizeit</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="5" t="n">
-        <v>150.5</v>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>-150.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mobilität</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>96.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>-96.90000000000001</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Finanzen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>0</v>
+        <v>1787.95</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>85</v>
+        <v>418.55</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>-85</v>
+        <v>1369.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>1879.12</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>-1879.12</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>371.69</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>-371.69</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>165.5</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>-165.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Mobilität</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>-96.90000000000001</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="5" t="n">
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="n">
         <v>12.4</v>
       </c>
-      <c r="D30" s="5" t="n">
+      <c r="D34" s="5" t="n">
         <v>-12.4</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Finanzen</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>April 2025</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Credit in CHF</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>Debit in CHF</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>Net in CHF</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Einkommen</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B41" s="5" t="n">
         <v>4200</v>
       </c>
-      <c r="C36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="5" t="n">
+      <c r="C41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="5" t="n">
         <v>4200</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>1774</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>-1774</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>361.65</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>-361.65</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Finanzen</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>168.5</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>-168.5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>22.85</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Freizeit</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="B46" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="C37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="5" t="n">
+      <c r="C46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="5" t="n">
         <v>100</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Finanzen</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>-25</v>
       </c>
     </row>
   </sheetData>
@@ -1699,7 +1827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1760,586 +1888,775 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Familie</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>19</v>
+        <v>388.75</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-19</v>
+        <v>-388.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mobilität</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Privater Verkehr</t>
+          <t>Lohn</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>26.7</v>
+        <v>0</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>-26.7</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Familie</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Mobilität</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Privater Verkehr</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-26.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Wohnen</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Miete und Hypothek</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1774</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>-1774</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>Haushalt</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="5" t="n">
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="n">
         <v>13.9</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E13" s="5" t="n">
         <v>-13.9</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>February 2025</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Subcategory</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Credit in CHF</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Debit in CHF</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>Net in CHF</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>434.7</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-434.7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Einkommen</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Lohn</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>4200</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Freizeit</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Gastronomie</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="5" t="n">
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E21" s="5" t="n">
         <v>-3</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>March 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Subcategory</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Credit in CHF</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Debit in CHF</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Net in CHF</t>
-        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Supermärkte</t>
+          <t>Miete und Hypothek</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>189.75</v>
+        <v>1774</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-189.75</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Einkaufen</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Detail-Lebensmittel</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>167.29</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>-167.29</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Einkaufen</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Sonstiges Einkaufen</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>14.65</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>-14.65</v>
+        <v>-1774</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Einkommen</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Lohn</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>6966.35</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>6966.35</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Finanzen</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Bargeldbezug</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>-80</v>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>March 2025</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Finanzen</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Fees</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>-5</v>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Subcategory</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Credit in CHF</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Debit in CHF</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Net in CHF</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>150.5</v>
+        <v>189.75</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>-150.5</v>
+        <v>-189.75</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Gesundheit</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>1787.95</v>
+        <v>0</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>101.85</v>
+        <v>167.29</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>1686.1</v>
+        <v>-167.29</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Familie</t>
+          <t>Sonstiges Einkaufen</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>200</v>
+        <v>14.65</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>-200</v>
+        <v>-14.65</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Styling und Wellness</t>
+          <t>Lohn</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>79.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>-79.90000000000001</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Finanzen</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sonstiges Leben</t>
+          <t>Fees</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>51.8</v>
+        <v>5</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>-51.8</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mobilität</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Öffentlicher Verkehr</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>96.90000000000001</v>
+        <v>150.5</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>-96.90000000000001</v>
+        <v>-150.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Miete und Hypothek</t>
+          <t>Kultur</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>1774</v>
+        <v>15</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>-1774</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kommunikation</t>
+          <t>Gesundheit</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>0</v>
+        <v>1787.95</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>70.27</v>
+        <v>101.85</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>-70.27</v>
+        <v>1686.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Haushalt</t>
+          <t>Familie</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>23.95</v>
+        <v>200</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>-23.95</v>
+        <v>-200</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Styling und Wellness</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>-79.90000000000001</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sonstiges Leben</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>-36.8</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Mobilität</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Öffentlicher Verkehr</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>-96.90000000000001</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Wohnen</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Handwerk und Garten</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>-10.9</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>April 2025</t>
-        </is>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Miete und Hypothek</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>1774</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>-1774</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Kommunikation</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>70.27</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>-70.27</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>Subcategory</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>Credit in CHF</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>Debit in CHF</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>Net in CHF</t>
-        </is>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Haushalt</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>-23.95</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Handwerk und Garten</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>-10.9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>April 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Subcategory</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Credit in CHF</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Debit in CHF</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Net in CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>361.65</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>-361.65</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>Einkommen</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Lohn</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C50" s="5" t="n">
         <v>4200</v>
       </c>
-      <c r="D43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="5" t="n">
+      <c r="D50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="5" t="n">
         <v>4200</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>Finanzen</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Bargeldbezug</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>-143.5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Finanzen</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
         <is>
           <t>Spenden</t>
         </is>
       </c>
-      <c r="C44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="5" t="n">
+      <c r="C52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="E44" s="5" t="n">
+      <c r="E52" s="5" t="n">
         <v>-25</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Freizeit</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Reisen und Erleben</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n">
+      <c r="C53" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="D45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="5" t="n">
+      <c r="D53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="5" t="n">
         <v>100</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Miete und Hypothek</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>1774</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>-1774</v>
       </c>
     </row>
   </sheetData>

--- a/data/example/output/dataset.analysis.xlsx
+++ b/data/example/output/dataset.analysis.xlsx
@@ -987,7 +987,7 @@
         <v>18300</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>1888.95</v>
+        <v>2023.95</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>0</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1888.95</v>
+        <v>2023.95</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>20188.95</v>
+        <v>20323.95</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>9674.959999999999</v>
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>20638.95</v>
+        <v>20773.95</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>9674.959999999999</v>
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>1787.95</v>
+        <v>1922.95</v>
       </c>
     </row>
     <row r="53">
@@ -1293,7 +1293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1787,32 +1787,48 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>69.05</v>
+        <v>135</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>46.2</v>
+        <v>0</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>22.85</v>
+        <v>135</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>22.85</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>Freizeit</t>
         </is>
       </c>
-      <c r="B46" s="5" t="n">
+      <c r="B47" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="C46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="5" t="n">
+      <c r="C47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="5" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1827,7 +1843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2641,21 +2657,63 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Gesundheit</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Familie</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>Wohnen</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Miete und Hypothek</t>
         </is>
       </c>
-      <c r="C54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="5" t="n">
+      <c r="C56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="5" t="n">
         <v>1774</v>
       </c>
-      <c r="E54" s="5" t="n">
+      <c r="E56" s="5" t="n">
         <v>-1774</v>
       </c>
     </row>

--- a/data/example/output/dataset.analysis.xlsx
+++ b/data/example/output/dataset.analysis.xlsx
@@ -1843,7 +1843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2334,17 +2334,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Gesundheit</t>
+          <t>Krankenkasse</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
         <v>1787.95</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>101.85</v>
+        <v>77.45</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>1686.1</v>
+        <v>1710.5</v>
       </c>
     </row>
     <row r="36">
@@ -2413,43 +2413,43 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mobilität</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Öffentlicher Verkehr</t>
+          <t>Gesundheit</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>96.90000000000001</v>
+        <v>24.4</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>-96.90000000000001</v>
+        <v>-24.4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Mobilität</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Miete und Hypothek</t>
+          <t>Öffentlicher Verkehr</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>1774</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>-1774</v>
+        <v>-96.90000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -2460,17 +2460,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kommunikation</t>
+          <t>Miete und Hypothek</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>70.27</v>
+        <v>1774</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>-70.27</v>
+        <v>-1774</v>
       </c>
     </row>
     <row r="42">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Haushalt</t>
+          <t>Kommunikation</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>23.95</v>
+        <v>70.27</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>-23.95</v>
+        <v>-70.27</v>
       </c>
     </row>
     <row r="43">
@@ -2502,114 +2502,114 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>Haushalt</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>-23.95</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>Handwerk und Garten</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="5" t="n">
+      <c r="C44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="5" t="n">
         <v>10.9</v>
       </c>
-      <c r="E43" s="5" t="n">
+      <c r="E44" s="5" t="n">
         <v>-10.9</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>April 2025</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Subcategory</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>Credit in CHF</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>Debit in CHF</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>Net in CHF</t>
         </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Einkaufen</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Supermärkte</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>361.65</v>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>-361.65</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Einkommen</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Lohn</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>0</v>
+        <v>361.65</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>4200</v>
+        <v>-361.65</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Finanzen</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Bargeldbezug</t>
+          <t>Lohn</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>143.5</v>
+        <v>0</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>-143.5</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="52">
@@ -2620,59 +2620,59 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Spenden</t>
+          <t>Bargeldbezug</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>25</v>
+        <v>143.5</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>-25</v>
+        <v>-143.5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Finanzen</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Reisen und Erleben</t>
+          <t>Spenden</t>
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>100</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Gesundheit</t>
+          <t>Reisen und Erleben</t>
         </is>
       </c>
       <c r="C54" s="5" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D54" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55">
@@ -2683,37 +2683,58 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Familie</t>
+          <t>Krankenkasse</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="D55" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>15</v>
+        <v>120</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Familie</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>Wohnen</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Miete und Hypothek</t>
         </is>
       </c>
-      <c r="C56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="5" t="n">
+      <c r="C57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="5" t="n">
         <v>1774</v>
       </c>
-      <c r="E56" s="5" t="n">
+      <c r="E57" s="5" t="n">
         <v>-1774</v>
       </c>
     </row>

--- a/data/example/output/dataset.analysis.xlsx
+++ b/data/example/output/dataset.analysis.xlsx
@@ -11,15 +11,23 @@
     <sheet name="Overviews by category" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Category Analysis" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Subcategory Analysis" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Transactions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Top Payees" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Transactions'!$A$1:$K$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Top Payees'!$A$1:$H$51</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <name val="Calibri"/>
@@ -74,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -86,6 +94,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2741,4 +2751,5986 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K87"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Transaction ID</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Transaction Category</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Subcategory</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Payee</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Source File</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TX-000059</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="n">
+        <v>45660</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Mobilität</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Privater Verkehr</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>MOBILITY MUSTER GENOSSENSCHAFT 6343 ROTKREUZ</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>MUSTERBANK AG MUSTERSTRASSE 12 6002 LUZERN</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>transport_2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>export.202501.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TX-000078</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="n">
+        <v>45661</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MIGROS M RIVERSIDE (7741)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" s="5" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>supermarket_1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>export.202501.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TX-000077</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>45667</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>MIGROS MARKTHALLE (8812)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" s="5" t="n">
+        <v>118.3</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>supermarket_1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>export.202501.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TX-000057</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>45672</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Familie</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ZMITTAG 13.1.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ZMITTAG 13.1.</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>family_2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>export.202501.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TX-000076</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>45675</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>COOP-5510 RIVERSIDE REST.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" s="5" t="n">
+        <v>132.85</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>supermarket_1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>export.202501.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TX-000002</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>45676</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Haushalt</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ONLINE HAUSHALT AG</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>PAYMENT ID 250119000000000000 BESTELLNUMMER DP-P-00000000</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>home_3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>export.202501.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TX-000001</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>45682</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Refund</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Rückerstattungen</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>+41790000000 MAX MUSTER</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>MITTEILUNGEN: TEST</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>refund_1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>export.202501.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TX-000070</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>45682</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Einkommen</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lohn</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SALAER JANUAR 2025 | SALA00000000000000000000000000000001 9988776655/1XXXX 250125CH0EXMPL01</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>-4200</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>income_1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>export.202501.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TX-000075</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>45685</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MIGROS MARKTHALLE (8812)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" s="5" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>supermarket_1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>export.202501.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TX-000074</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>45688</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Miete und Hypothek</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FINANZVERWALTUNG STADT SOLOTHURN</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2025/02/01 / 7045128</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>1774</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>housing_1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>export.202501.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TX-000083</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>45689</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>MIGROS M RIVERSIDE (7741)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" s="5" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>supermarket_1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>export.202502.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TX-000082</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>45696</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MIGROS MARKTHALLE (8812)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" s="5" t="n">
+        <v>127.4</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>supermarket_1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>export.202502.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TX-000081</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>45702</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>COOP-5510 RIVERSIDE REST.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" s="5" t="n">
+        <v>88.95</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>supermarket_1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>export.202502.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TX-000080</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>45710</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MIGROS MARKTHALLE (8812)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" s="5" t="n">
+        <v>154.6</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>supermarket_1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>export.202502.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TX-000071</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="n">
+        <v>45713</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Einkommen</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lohn</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>SALAER FEBRUAR 2025 | SALA00000000000000000000000000000002 9988776655/1XXXX 250225CH0EXMPL02</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>-4200</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>income_1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>export.202502.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TX-000060</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="n">
+        <v>45715</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gastronomie</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MUSTER CAFE</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>gastronomy_6</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>export.202502.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TX-000079</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n">
+        <v>45716</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Miete und Hypothek</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>FINANZVERWALTUNG STADT SOLOTHURN</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2025/03/01 / 7045128</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>1774</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>housing_1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>export.202502.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TX-000054</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>45738</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gastronomie</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>+41790000000 MAX MUSTER</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>MITTEILUNGEN: ESSEN GESTERN ABEND</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>gastronomy_5</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TX-000055</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>45738</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>UNMATCHED TEST STORE</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" s="5" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TX-000051</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>45739</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>BÄCKEREI HUG</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" s="5" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>grocery_1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TX-000052</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="n">
+        <v>45739</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Haushalt</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>MANOR AG - 771 (CENTRA)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" s="5" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>home_2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TX-000053</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>45739</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gastronomie</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>+41796666222 KEBAB, IMBISS</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" s="5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>gastronomy_4</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TX-000045</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="n">
+        <v>45740</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>WAKARA GMBH</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" s="5" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>grocery_2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TX-000046</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n">
+        <v>45740</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Styling und Wellness</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>THE BODY SHOP</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" s="5" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>wellness_1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TX-000047</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="n">
+        <v>45740</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>COOP-5510 RIVERSIDE REST.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>supermarket_1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TX-000048</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="n">
+        <v>45740</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MIGROS MARKTHALLE (8812)</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" s="5" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>supermarket_1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TX-000049</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="n">
+        <v>45740</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Gastronomie</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>MIGROS CITY TAKE AWAY (6624)</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" s="5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>gastronomy_1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TX-000050</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="n">
+        <v>45740</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Krankenkasse</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>MEDICURA PLUS AG GESUNDHEITSWEG 8 4052 BASEL</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" s="5" t="n">
+        <v>77.45</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>health_2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TX-000039</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="n">
+        <v>45741</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>BÄCKEREI HUG</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" s="5" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>grocery_1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TX-000040</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>45741</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>BRANKOVIC BREZELSTUBE</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>grocery_1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TX-000041</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="n">
+        <v>45741</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>MIGROS M RIVERSIDE (7741)</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" s="5" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>supermarket_1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TX-000043</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n">
+        <v>45741</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Refund</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Krankenkasse</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>MEDICURA PLUS AG GESUNDHEITSWEG 8 4052 BASEL</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>LEISTUNGSABRECHNUNG NR.: 700112233445566 VERSICHERTE PERSON 445566 BETRIFFT LEISTUNGEN | MED95CB11F8253446278F81749F26F10588</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>-1787.95</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>refund_2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TX-000044</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="n">
+        <v>45741</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Kommunikation</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>CLOUDSERVICE INC SAN</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" s="5" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>communication_3</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TX-000058</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n">
+        <v>45741</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Überträge</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Account Transfer</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>EIGENES SPARKONTO KONTOUEBERTRAG TRANSFER-20250325</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>EIGENES SPARKONTO KONTOUEBERTRAG TRANSFER-20250325</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>-450</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>transfer_1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TX-000072</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="n">
+        <v>45741</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Einkommen</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Lohn</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>SALAER BONUS 2024 | SALA00000000000000000000000000000003 9988776655/1XXXX 250325CH0EXMPL03</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>-1500</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>income_1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TX-000073</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="n">
+        <v>45741</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Einkommen</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lohn</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>SALAER MAERZ 2025 | SALA80E5ED528784F48B451A4175649C112 9988776655/1XXXX 250325CH7LMNQRTS</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>-4200</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>income_1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TX-000035</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="n">
+        <v>45742</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Mobilität</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Öffentlicher Verkehr</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>TRANSPORTS PUBLICS FRIBOURGEOIS (FAIRTIQ) N/A PAYMENT ID 250326064915818975ZX BESTELLNUMMER</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" s="5" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>transport_1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TX-000036</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="n">
+        <v>45742</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Handwerk und Garten</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>JUMBO-7782 INDUSTRIEPARK</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" s="5" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>home_1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TX-000037</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="n">
+        <v>45742</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Gastronomie</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>+41796666222 KEBAB, IMBISS</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>MITTEILUNGEN: KEBAB</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>gastronomy_4</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TX-000038</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="n">
+        <v>45742</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Familie</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>FAMILIENKASSE MUSTERHAUSEN SENDER REFERENZ: FAMILIENZULAGE</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>90-33445566</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>family_1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TX-000024</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="n">
+        <v>45743</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Kommunikation</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>APPLE.COM/BILL</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>communication_2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TX-000025</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="n">
+        <v>45743</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Gastronomie</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>YOOJI'S ROSENGARTEN</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" s="5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>gastronomy_2</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TX-000026</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="n">
+        <v>45743</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>CONFISERIE SPRÜNGLI AG</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" s="5" t="n">
+        <v>22.05</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>grocery_1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TX-000027</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="n">
+        <v>45743</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Styling und Wellness</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>THE BODY SHOP</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" s="5" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>wellness_1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>TX-000028</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="n">
+        <v>45743</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Gastronomie</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>YOOJI'S ROSENGARTEN</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" s="5" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>gastronomy_2</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>TX-000029</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n">
+        <v>45743</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Gastronomie</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>YOOJI'S ROSENGARTEN</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" s="5" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>gastronomy_2</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>TX-000030</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="n">
+        <v>45743</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Gastronomie</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>COFFEE AND PLANTS</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>gastronomy_3</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>TX-000032</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="n">
+        <v>45743</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>YUMIHANA</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" s="5" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>grocery_2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TX-000033</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="n">
+        <v>45743</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>YUMI HANA</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" s="5" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>grocery_2</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TX-000034</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="n">
+        <v>45743</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>COOP - 7811 QUAI WEST</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" s="5" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>supermarket_1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TX-000018</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="n">
+        <v>45744</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Mobilität</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Öffentlicher Verkehr</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>TRANSPORTS PUBLICS FRIBOURGEOIS (FAIRTIQ) N/A PAYMENT ID 250328064754083058ZX BESTELLNUMMER</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" s="5" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>transport_1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TX-000019</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="n">
+        <v>45744</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>SUMUP *BACKEREI ZUR K</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" s="5" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>grocery_1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>TX-000020</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="n">
+        <v>45744</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Sonstiges Einkaufen</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>KKIOSK 45810</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" s="5" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>shopping_1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>TX-000021</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="n">
+        <v>45744</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Gesundheit</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>BAHNHOF APOTHEKE AG</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" s="5" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>health_1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>TX-000022</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="n">
+        <v>45744</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>BÄCKEREI HUG</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" s="5" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>grocery_1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>TX-000023</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="n">
+        <v>45744</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>MIGROS M RIVERSIDE (7741)</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" s="5" t="n">
+        <v>28.35</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>supermarket_1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>TX-000015</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="n">
+        <v>45745</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>BÄCKEREI HUG</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" s="5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>grocery_1</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>TX-000016</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="n">
+        <v>45745</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>MIGROS M RIVERSIDE (7741)</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" s="5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>supermarket_1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>TX-000017</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="n">
+        <v>45745</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Kommunikation</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>SUNRISE GMBH POSTFACH 8050 ZURICH</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" s="5" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>communication_1</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>TX-000010</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="n">
+        <v>45746</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Gastronomie</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>SIGNOR ROSSI</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>gastronomy_2</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>TX-000011</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="n">
+        <v>45746</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>MIGROS MARKTHALLE (8812)</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" s="5" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>supermarket_1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>TX-000012</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="n">
+        <v>45746</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Gastronomie</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>MIGROS CITY TAKE AWAY (6624)</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>gastronomy_1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>TX-000013</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="n">
+        <v>45746</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Kultur</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>BYRO</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>life_1</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>TX-000014</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="n">
+        <v>45746</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Sonstiges Leben</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>BYRO</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" s="5" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>life_1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>TX-000003</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="n">
+        <v>45747</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>CITY TANKSTELLE</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" s="5" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>grocery_3</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>TX-000004</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="n">
+        <v>45747</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>CITY TANKSTELLE</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" s="5" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>grocery_3</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>TX-000006</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="n">
+        <v>45747</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Sonstiges Einkaufen</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>KKIOSK 45810</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" s="5" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>shopping_1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>TX-000007</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="n">
+        <v>45747</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>MIGROS MARKTHALLE (8812)</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" s="5" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>supermarket_1</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>TX-000008</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="n">
+        <v>45747</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Finanzen</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>PREIS FÜR BANKPAKET SMART 02.2025</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>PREIS FÜR BANKPAKET SMART 02.2025</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>finance_2</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>TX-000009</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="n">
+        <v>45747</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Miete und Hypothek</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>FINANZVERWALTUNG STADT SOLOTHURN</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2025/04/01 / 7045128</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>1774</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>housing_1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>TX-000064</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="n">
+        <v>45747</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Styling und Wellness</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>SUMUP *COIFFEUR HAIRCUT</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>wellness_2</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>export.202503.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>TX-000089</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Refund</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Krankenkasse</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>MUSTER UND BEISPIEL GEMEINSCHAFTSKONTO MUSTERWEG 1 4600 OLTEN</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" s="5" t="n">
+        <v>-120</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>refund_example_amount_1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>TX-000090</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Refund</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Familie</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>MUSTER UND BEISPIEL GEMEINSCHAFTSKONTO MUSTERWEG 1 4600 OLTEN</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" s="5" t="n">
+        <v>-15</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>refund_example_counterparty_1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>TX-000061</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="n">
+        <v>45751</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Refund</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Reisen und Erleben</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>UEFA WOMEN'S EURO 2025 NYON</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>refund_3</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>TX-000084</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="n">
+        <v>45752</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>MIGROS MARKTHALLE (8812)</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" s="5" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>supermarket_1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>TX-000085</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="n">
+        <v>45759</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>COOP-5510 RIVERSIDE REST.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" s="5" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>supermarket_1</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>TX-000062</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="n">
+        <v>45763</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Einkommen</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Lohn</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>FIKTIVE LOHN AG PERSONALABTEILUNG</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>LOHNBEISPIEL APRIL 2025 | DEMO REF 001</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>-4200</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>income_example_counterparty_1</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>TX-000063</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="n">
+        <v>45764</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Finanzen</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Spenden</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>ANONYMISIERTER VEREIN MITTEILUNGEN: DEMO-ZWECK JAHRESBEITRAG</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>expense_example_counterparty_iban_1</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>TX-000065</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="n">
+        <v>45765</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>FIKTIVE DIGITAL GMBH</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>PAYMENT ID 000A00D0 BESTELLNUMMER AB00CD00</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>TX-000066</t>
+        </is>
+      </c>
+      <c r="B81" s="9" t="n">
+        <v>45766</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>FIKTIVE POST AG</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>PAYMENT ID AB0CD0EF00GH0IJ0 BESTELLNUMMER MYS_AB0CD0EF00GH0I</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>TX-000086</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="n">
+        <v>45766</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>MIGROS M RIVERSIDE (7741)</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" s="5" t="n">
+        <v>54.85</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>supermarket_1</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>TX-000067</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="n">
+        <v>45767</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>FIKTIVER SCHUHLADEN BIEL</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" s="5" t="n">
+        <v>-49.9</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>TX-000068</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="n">
+        <v>45768</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>FIKTIVER FAHRSCHEIN BERLIN DEUTSCHLAND</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" s="5" t="n">
+        <v>-19.15</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>TX-000069</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="n">
+        <v>45769</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Finanzen</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Bargeldbezug</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>BAHNHOF</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" s="5" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>finance_1</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>TX-000087</t>
+        </is>
+      </c>
+      <c r="B86" s="9" t="n">
+        <v>45773</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>MIGROS MARKTHALLE (8812)</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" s="5" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>supermarket_1</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>TX-000088</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="n">
+        <v>45777</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Miete und Hypothek</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>FINANZVERWALTUNG STADT SOLOTHURN</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2025/05/01 / 7045128</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>1774</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>housing_1</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K87"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Subcategory</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Payee</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Months</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Share</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Miete und Hypothek</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>FINANZVERWALTUNG STADT SOLOTHURN</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>7096</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MIGROS MARKTHALLE</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>823.6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>COOP-5510 RIVERSIDE REST.</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>342.1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>0.2488</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MIGROS M RIVERSIDE</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>201.4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>0.1465</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>COOP - 7811 QUAI WEST</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Familie</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>FAMILIENKASSE MUSTERHAUSEN</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>0.9804</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Familie</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ZMITTAG 13.1.</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>0.0931</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Familie</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MUSTER UND BEISPIEL GEMEINSCHAFTSKONTO MUSTERWEG 1 4600 OLTEN</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>-15</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>-0.0735</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BÄCKEREI HUG</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>0.2391</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>WAKARA GMBH</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>YUMI HANA</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>0.1602</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CONFISERIE SPRÜNGLI AG</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>22.05</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>0.1318</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>YUMIHANA</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>0.1109</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CITY TANKSTELLE</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="H15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SUMUP *BACKEREI ZUR K</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>0.0664</v>
+      </c>
+      <c r="H16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BRANKOVIC BREZELSTUBE</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>0.0257</v>
+      </c>
+      <c r="H17" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Gastronomie</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>YOOJI'S ROSENGARTEN</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>0.4059</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Gastronomie</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>+41796666222 KEBAB, IMBISS</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>0.1792</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Gastronomie</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>+41790000000 MAX MUSTER</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>0.1303</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Gastronomie</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SIGNOR ROSSI</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="10" t="n">
+        <v>0.1303</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Gastronomie</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MIGROS CITY TAKE AWAY</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="10" t="n">
+        <v>0.0697</v>
+      </c>
+      <c r="H22" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Gastronomie</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>COFFEE AND PLANTS</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="10" t="n">
+        <v>0.06510000000000001</v>
+      </c>
+      <c r="H23" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Gastronomie</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>MUSTER CAFE</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>0.0195</v>
+      </c>
+      <c r="H24" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Finanzen</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Bargeldbezug</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BAHNHOF</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Mobilität</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Öffentlicher Verkehr</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TRANSPORTS PUBLICS FRIBOURGEOIS (FAIRTIQ) N/A PAYMENT ID 250326064915818975ZX BESTELLNUMMER</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="10" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Mobilität</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Öffentlicher Verkehr</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>TRANSPORTS PUBLICS FRIBOURGEOIS (FAIRTIQ) N/A PAYMENT ID 250328064754083058ZX BESTELLNUMMER</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="10" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Styling und Wellness</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SUMUP *COIFFEUR HAIRCUT</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="10" t="n">
+        <v>0.6258</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Styling und Wellness</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>THE BODY SHOP</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Kommunikation</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SUNRISE GMBH POSTFACH 8050 ZURICH</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="10" t="n">
+        <v>0.7058</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Kommunikation</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLOUDSERVICE INC SAN</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="10" t="n">
+        <v>0.2657</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Kommunikation</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>APPLE.COM/BILL</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="10" t="n">
+        <v>0.0285</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Haushalt</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>MANOR AG - 771 (CENTRA)</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v>0.6328</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Haushalt</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ONLINE HAUSHALT AG</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="10" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sonstiges Leben</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BYRO</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Mobilität</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Privater Verkehr</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MOBILITY MUSTER GENOSSENSCHAFT 6343 ROTKREUZ</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Finanzen</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Spenden</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ANONYMISIERTER VEREIN MITTEILUNGEN: DEMO-ZWECK JAHRESBEITRAG</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Gesundheit</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>BAHNHOF APOTHEKE AG</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Kultur</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>BYRO</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sonstiges Einkaufen</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>KKIOSK 45810</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Handwerk und Garten</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>JUMBO-7782 INDUSTRIEPARK</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Finanzen</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>PREIS FÜR BANKPAKET SMART 02.2025</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Rückerstattungen</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>+41790000000 MAX MUSTER</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>FIKTIVE DIGITAL GMBH</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="10" t="n">
+        <v>-3.2249</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>FIKTIVE POST AG</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="10" t="n">
+        <v>-1.1962</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>UNMATCHED TEST STORE</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="10" t="n">
+        <v>-1.1866</v>
+      </c>
+      <c r="H46" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>FIKTIVER FAHRSCHEIN BERLIN DEUTSCHLAND</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>-19.15</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="10" t="n">
+        <v>1.8325</v>
+      </c>
+      <c r="H47" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>FIKTIVER SCHUHLADEN BIEL</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>-49.9</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="10" t="n">
+        <v>4.7751</v>
+      </c>
+      <c r="H48" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Reisen und Erleben</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>UEFA WOMEN'S EURO 2025 NYON</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Krankenkasse</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>MUSTER UND BEISPIEL GEMEINSCHAFTSKONTO MUSTERWEG 1 4600 OLTEN</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>-120</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="10" t="n">
+        <v>0.06560000000000001</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Krankenkasse</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>MEDICURA PLUS AG GESUNDHEITSWEG 8 4052 BASEL</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>-1710.5</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="10" t="n">
+        <v>0.9344</v>
+      </c>
+      <c r="H51" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H51"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/example/output/dataset.analysis.xlsx
+++ b/data/example/output/dataset.analysis.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Top Payees" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Transactions'!$A$1:$K$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Transactions'!$A$1:$N$87</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Top Payees'!$A$1:$H$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +28,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,6 +54,9 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -82,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -93,6 +96,8 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -916,7 +921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1099,6 +1104,36 @@
       </c>
       <c r="C15" s="7" t="n">
         <v>9674.959999999999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Check (Transactions)</t>
+        </is>
+      </c>
+      <c r="B17" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$D$2:$D$87, "Income") + SUMIFS(Transactions!$J$2:$J$87, Transactions!$D$2:$D$87, "Expense") + SUMIFS(Transactions!$J$2:$J$87, Transactions!$D$2:$D$87, "Refund") + SUMIFS(Transactions!$J$2:$J$87, Transactions!$D$2:$D$87, "Transfer")</f>
+        <v/>
+      </c>
+      <c r="C17" s="9">
+        <f>SUMIFS(Transactions!$K$2:$K$87, Transactions!$D$2:$D$87, "Income") + SUMIFS(Transactions!$K$2:$K$87, Transactions!$D$2:$D$87, "Expense") + SUMIFS(Transactions!$K$2:$K$87, Transactions!$D$2:$D$87, "Refund") + SUMIFS(Transactions!$K$2:$K$87, Transactions!$D$2:$D$87, "Transfer")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="B18" s="9">
+        <f>B17-B15</f>
+        <v/>
+      </c>
+      <c r="C18" s="9">
+        <f>C17-C15</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1113,7 +1148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1142,12 +1177,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Amount (CHF)</t>
         </is>
@@ -1163,6 +1198,38 @@
         <v>18300</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>18300</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Check (Transactions)</t>
+        </is>
+      </c>
+      <c r="B10" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$D$2:$D$87, "Income") - SUMIFS(Transactions!$K$2:$K$87, Transactions!$D$2:$D$87, "Income")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="B11" s="9">
+        <f>B10-B9</f>
+        <v/>
+      </c>
+    </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
@@ -1171,12 +1238,12 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>Amount (CHF)</t>
         </is>
@@ -1242,6 +1309,38 @@
         <v>123.6</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>9674.959999999999</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Check (Transactions)</t>
+        </is>
+      </c>
+      <c r="B37" s="9">
+        <f>SUMIFS(Transactions!$K$2:$K$87, Transactions!$D$2:$D$87, "Expense") - SUMIFS(Transactions!$J$2:$J$87, Transactions!$D$2:$D$87, "Expense")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="B38" s="9">
+        <f>B37-B36</f>
+        <v/>
+      </c>
+    </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
@@ -1250,12 +1349,12 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>Amount (CHF)</t>
         </is>
@@ -1289,6 +1388,38 @@
       </c>
       <c r="B54" s="5" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="n">
+        <v>2023.95</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>Check (Transactions)</t>
+        </is>
+      </c>
+      <c r="B56" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$D$2:$D$87, "Refund") - SUMIFS(Transactions!$K$2:$K$87, Transactions!$D$2:$D$87, "Refund")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="B57" s="9">
+        <f>B56-B55</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1303,7 +1434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1451,395 +1582,611 @@
         <v>1</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>4201</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>2222.35</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>1978.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Check (Transactions)</t>
+        </is>
+      </c>
+      <c r="B15" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-01", Transactions!$D$2:$D$87, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+      <c r="C15" s="9">
+        <f>SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-01", Transactions!$D$2:$D$87, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+      <c r="D15" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-01", Transactions!$D$2:$D$87, "&lt;&gt;Transfer") - SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-01", Transactions!$D$2:$D$87, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+    </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="B16" s="9">
+        <f>B15-B14</f>
+        <v/>
+      </c>
+      <c r="C16" s="9">
+        <f>C15-C14</f>
+        <v/>
+      </c>
+      <c r="D16" s="9">
+        <f>D15-D14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>February 2025</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Credit in CHF</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Debit in CHF</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Net in CHF</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Einkommen</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>4200</v>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>4200</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Wohnen</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>1774</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>-1774</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Einkaufen</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>434.7</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>-434.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Einkommen</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>4200</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>1774</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-1774</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>434.7</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>-434.7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Freizeit</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="5" t="n">
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D22" s="5" t="n">
+      <c r="D25" s="5" t="n">
         <v>-3</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>4200</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>2211.7</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>1988.3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Check (Transactions)</t>
+        </is>
+      </c>
+      <c r="B27" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-02", Transactions!$D$2:$D$87, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+      <c r="C27" s="9">
+        <f>SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-02", Transactions!$D$2:$D$87, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+      <c r="D27" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-02", Transactions!$D$2:$D$87, "&lt;&gt;Transfer") - SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-02", Transactions!$D$2:$D$87, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="B28" s="9">
+        <f>B27-B26</f>
+        <v/>
+      </c>
+      <c r="C28" s="9">
+        <f>C27-C26</f>
+        <v/>
+      </c>
+      <c r="D28" s="9">
+        <f>D27-D26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>March 2025</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Credit in CHF</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Debit in CHF</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>Net in CHF</t>
         </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Einkommen</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>5700</v>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>5700</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Leben</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>1787.95</v>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>418.55</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>1369.4</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Wohnen</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>1879.12</v>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>-1879.12</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Einkaufen</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>371.69</v>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>-371.69</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Freizeit</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="5" t="n">
-        <v>165.5</v>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>-165.5</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Mobilität</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>-96.90000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>12.4</v>
+        <v>0</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>-12.4</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Finanzen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>0</v>
+        <v>1787.95</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>5</v>
+        <v>418.55</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>-5</v>
+        <v>1369.4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>1879.12</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>-1879.12</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>371.69</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>-371.69</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>April 2025</t>
-        </is>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>165.5</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>-165.5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Mobilität</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>-96.90000000000001</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>Credit in CHF</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>Debit in CHF</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>Net in CHF</t>
-        </is>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>-12.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Finanzen</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="n">
+        <v>7487.95</v>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>2949.16</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>4538.79</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>Check (Transactions)</t>
+        </is>
+      </c>
+      <c r="B43" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-03", Transactions!$D$2:$D$87, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+      <c r="C43" s="9">
+        <f>SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-03", Transactions!$D$2:$D$87, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+      <c r="D43" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-03", Transactions!$D$2:$D$87, "&lt;&gt;Transfer") - SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-03", Transactions!$D$2:$D$87, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="B44" s="9">
+        <f>B43-B42</f>
+        <v/>
+      </c>
+      <c r="C44" s="9">
+        <f>C43-C42</f>
+        <v/>
+      </c>
+      <c r="D44" s="9">
+        <f>D43-D42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>April 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Credit in CHF</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Debit in CHF</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Net in CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>Einkommen</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n">
+      <c r="B50" s="5" t="n">
         <v>4200</v>
       </c>
-      <c r="C41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="5" t="n">
+      <c r="C50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="5" t="n">
         <v>4200</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>Wohnen</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" s="5" t="n">
+      <c r="B51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="5" t="n">
         <v>1774</v>
       </c>
-      <c r="D42" s="5" t="n">
+      <c r="D51" s="5" t="n">
         <v>-1774</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Einkaufen</t>
         </is>
       </c>
-      <c r="B43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" s="5" t="n">
+      <c r="B52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5" t="n">
         <v>361.65</v>
       </c>
-      <c r="D43" s="5" t="n">
+      <c r="D52" s="5" t="n">
         <v>-361.65</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Finanzen</t>
         </is>
       </c>
-      <c r="B44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" s="5" t="n">
+      <c r="B53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="5" t="n">
         <v>168.5</v>
       </c>
-      <c r="D44" s="5" t="n">
+      <c r="D53" s="5" t="n">
         <v>-168.5</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Leben</t>
         </is>
       </c>
-      <c r="B45" s="5" t="n">
+      <c r="B54" s="5" t="n">
         <v>135</v>
       </c>
-      <c r="C45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="5" t="n">
+      <c r="C54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="5" t="n">
         <v>135</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B46" s="5" t="n">
+      <c r="B55" s="5" t="n">
         <v>69.05</v>
       </c>
-      <c r="C46" s="5" t="n">
+      <c r="C55" s="5" t="n">
         <v>46.2</v>
       </c>
-      <c r="D46" s="5" t="n">
+      <c r="D55" s="5" t="n">
         <v>22.85</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>Freizeit</t>
         </is>
       </c>
-      <c r="B47" s="5" t="n">
+      <c r="B56" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="C47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="5" t="n">
+      <c r="C56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="5" t="n">
         <v>100</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>4504.05</v>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>2350.35</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>2153.7</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>Check (Transactions)</t>
+        </is>
+      </c>
+      <c r="B58" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-04", Transactions!$D$2:$D$87, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+      <c r="C58" s="9">
+        <f>SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-04", Transactions!$D$2:$D$87, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+      <c r="D58" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-04", Transactions!$D$2:$D$87, "&lt;&gt;Transfer") - SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-04", Transactions!$D$2:$D$87, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="B59" s="9">
+        <f>B58-B57</f>
+        <v/>
+      </c>
+      <c r="C59" s="9">
+        <f>C58-C57</f>
+        <v/>
+      </c>
+      <c r="D59" s="9">
+        <f>D58-D57</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1853,7 +2200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2037,715 +2384,931 @@
         <v>-13.9</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>4200</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>2222.35</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>1977.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Check (Transactions)</t>
+        </is>
+      </c>
+      <c r="C15" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-01", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D15" s="9">
+        <f>SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-01", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="E15" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-01", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;") - SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-01", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;")</f>
+        <v/>
+      </c>
+    </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="C16" s="9">
+        <f>C15-C14</f>
+        <v/>
+      </c>
+      <c r="D16" s="9">
+        <f>D15-D14</f>
+        <v/>
+      </c>
+      <c r="E16" s="9">
+        <f>E15-E14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>February 2025</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Subcategory</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Credit in CHF</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Debit in CHF</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Net in CHF</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Einkaufen</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Supermärkte</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>434.7</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>-434.7</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Einkommen</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Lohn</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>4200</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>4200</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Freizeit</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Gastronomie</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>-3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>434.7</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-434.7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Einkommen</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Lohn</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>4200</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Gastronomie</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Wohnen</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Miete und Hypothek</t>
         </is>
       </c>
-      <c r="C22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="5" t="n">
+      <c r="C25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="5" t="n">
         <v>1774</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="E25" s="5" t="n">
         <v>-1774</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>4200</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>2211.7</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>1988.3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Check (Transactions)</t>
+        </is>
+      </c>
+      <c r="C27" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-02", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D27" s="9">
+        <f>SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-02", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="E27" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-02", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;") - SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-02", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="C28" s="9">
+        <f>C27-C26</f>
+        <v/>
+      </c>
+      <c r="D28" s="9">
+        <f>D27-D26</f>
+        <v/>
+      </c>
+      <c r="E28" s="9">
+        <f>E27-E26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>March 2025</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Subcategory</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Credit in CHF</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>Debit in CHF</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>Net in CHF</t>
         </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Einkaufen</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Supermärkte</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>189.75</v>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>-189.75</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Einkaufen</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Detail-Lebensmittel</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>167.29</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>-167.29</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Einkaufen</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Sonstiges Einkaufen</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>14.65</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>-14.65</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Einkommen</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Lohn</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>5700</v>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>5700</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Finanzen</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Fees</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Freizeit</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Gastronomie</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>150.5</v>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>-150.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kultur</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>15</v>
+        <v>189.75</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>-15</v>
+        <v>-189.75</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Krankenkasse</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>1787.95</v>
+        <v>0</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>77.45</v>
+        <v>167.29</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>1710.5</v>
+        <v>-167.29</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Familie</t>
+          <t>Sonstiges Einkaufen</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>200</v>
+        <v>14.65</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>-200</v>
+        <v>-14.65</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Styling und Wellness</t>
+          <t>Lohn</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>79.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>-79.90000000000001</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Finanzen</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sonstiges Leben</t>
+          <t>Fees</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>36.8</v>
+        <v>5</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>-36.8</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gesundheit</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>24.4</v>
+        <v>150.5</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>-24.4</v>
+        <v>-150.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Mobilität</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Öffentlicher Verkehr</t>
+          <t>Kultur</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>96.90000000000001</v>
+        <v>15</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>-96.90000000000001</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Miete und Hypothek</t>
+          <t>Krankenkasse</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>0</v>
+        <v>1787.95</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>1774</v>
+        <v>77.45</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>-1774</v>
+        <v>1710.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kommunikation</t>
+          <t>Familie</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>70.27</v>
+        <v>200</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>-70.27</v>
+        <v>-200</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Haushalt</t>
+          <t>Styling und Wellness</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>23.95</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>-23.95</v>
+        <v>-79.90000000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Sonstiges Leben</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>-36.8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Gesundheit</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>-24.4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Mobilität</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Öffentlicher Verkehr</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>-96.90000000000001</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>Wohnen</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Handwerk und Garten</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="E44" s="5" t="n">
-        <v>-10.9</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>April 2025</t>
-        </is>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Miete und Hypothek</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>1774</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>-1774</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Kommunikation</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>70.27</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>-70.27</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Subcategory</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>Credit in CHF</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>Debit in CHF</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>Net in CHF</t>
-        </is>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Haushalt</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>-23.95</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Handwerk und Garten</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>-10.9</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>7487.95</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>2936.76</v>
+      </c>
+      <c r="E51" s="7" t="n">
+        <v>4551.19</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>Check (Transactions)</t>
+        </is>
+      </c>
+      <c r="C52" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-03", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D52" s="9">
+        <f>SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-03", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="E52" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-03", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;") - SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-03", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="C53" s="9">
+        <f>C52-C51</f>
+        <v/>
+      </c>
+      <c r="D53" s="9">
+        <f>D52-D51</f>
+        <v/>
+      </c>
+      <c r="E53" s="9">
+        <f>E52-E51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>April 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Subcategory</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Credit in CHF</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Debit in CHF</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Net in CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>Einkaufen</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Supermärkte</t>
         </is>
       </c>
-      <c r="C50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="5" t="n">
+      <c r="C59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="5" t="n">
         <v>361.65</v>
       </c>
-      <c r="E50" s="5" t="n">
+      <c r="E59" s="5" t="n">
         <v>-361.65</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>Einkommen</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>Lohn</t>
         </is>
       </c>
-      <c r="C51" s="5" t="n">
+      <c r="C60" s="5" t="n">
         <v>4200</v>
       </c>
-      <c r="D51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="5" t="n">
+      <c r="D60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="5" t="n">
         <v>4200</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>Finanzen</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Bargeldbezug</t>
         </is>
       </c>
-      <c r="C52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="5" t="n">
+      <c r="C61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="5" t="n">
         <v>143.5</v>
       </c>
-      <c r="E52" s="5" t="n">
+      <c r="E61" s="5" t="n">
         <v>-143.5</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>Finanzen</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>Spenden</t>
         </is>
       </c>
-      <c r="C53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="5" t="n">
+      <c r="C62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="E53" s="5" t="n">
+      <c r="E62" s="5" t="n">
         <v>-25</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>Freizeit</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Reisen und Erleben</t>
         </is>
       </c>
-      <c r="C54" s="5" t="n">
+      <c r="C63" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="D54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="5" t="n">
+      <c r="D63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="5" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>Leben</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>Krankenkasse</t>
         </is>
       </c>
-      <c r="C55" s="5" t="n">
+      <c r="C64" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="D55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="5" t="n">
+      <c r="D64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="5" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>Leben</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>Familie</t>
         </is>
       </c>
-      <c r="C56" s="5" t="n">
+      <c r="C65" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="D56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="5" t="n">
+      <c r="D65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="5" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>Wohnen</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>Miete und Hypothek</t>
         </is>
       </c>
-      <c r="C57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="5" t="n">
+      <c r="C66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="5" t="n">
         <v>1774</v>
       </c>
-      <c r="E57" s="5" t="n">
+      <c r="E66" s="5" t="n">
         <v>-1774</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>4435</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>2304.15</v>
+      </c>
+      <c r="E67" s="7" t="n">
+        <v>2130.85</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>Check (Transactions)</t>
+        </is>
+      </c>
+      <c r="C68" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-04", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D68" s="9">
+        <f>SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-04", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="E68" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-04", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;") - SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-04", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="C69" s="9">
+        <f>C68-C67</f>
+        <v/>
+      </c>
+      <c r="D69" s="9">
+        <f>D68-D67</f>
+        <v/>
+      </c>
+      <c r="E69" s="9">
+        <f>E68-E67</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2759,7 +3322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K87"/>
+  <dimension ref="A1:N87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2768,11 +3331,14 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="32" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="32" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2808,25 +3374,40 @@
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
+          <t>Category / Subcategory</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
           <t>Payee</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>Rule</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>Source File</t>
         </is>
@@ -2838,7 +3419,7 @@
           <t>TX-000059</t>
         </is>
       </c>
-      <c r="B2" s="9" t="n">
+      <c r="B2" s="11" t="n">
         <v>45660</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -2863,23 +3444,34 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>Mobilität / Privater Verkehr</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>MOBILITY MUSTER GENOSSENSCHAFT 6343 ROTKREUZ</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>MUSTERBANK AG MUSTERSTRASSE 12 6002 LUZERN</t>
         </is>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="J2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="5" t="n">
         <v>26.7</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" s="5" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>transport_2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>export.202501.categorized.csv</t>
         </is>
@@ -2891,7 +3483,7 @@
           <t>TX-000078</t>
         </is>
       </c>
-      <c r="B3" s="9" t="n">
+      <c r="B3" s="11" t="n">
         <v>45661</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -2916,19 +3508,29 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>Einkaufen / Supermärkte</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>MIGROS M RIVERSIDE (7741)</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" s="5" t="n">
+      <c r="J3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5" t="n">
         <v>41.2</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" s="5" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>supermarket_1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>export.202501.categorized.csv</t>
         </is>
@@ -2940,7 +3542,7 @@
           <t>TX-000077</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n">
+      <c r="B4" s="11" t="n">
         <v>45667</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -2965,19 +3567,29 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>Einkaufen / Supermärkte</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>MIGROS MARKTHALLE (8812)</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" s="5" t="n">
+      <c r="J4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5" t="n">
         <v>118.3</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" s="5" t="n">
+        <v>118.3</v>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>supermarket_1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>export.202501.categorized.csv</t>
         </is>
@@ -2989,7 +3601,7 @@
           <t>TX-000057</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="11" t="n">
         <v>45672</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -3014,23 +3626,34 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>Leben / Familie</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>ZMITTAG 13.1.</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>ZMITTAG 13.1.</t>
         </is>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="J5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>family_2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>export.202501.categorized.csv</t>
         </is>
@@ -3042,7 +3665,7 @@
           <t>TX-000076</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="11" t="n">
         <v>45675</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -3067,19 +3690,29 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>Einkaufen / Supermärkte</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>COOP-5510 RIVERSIDE REST.</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" s="5" t="n">
+      <c r="J6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5" t="n">
         <v>132.85</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" s="5" t="n">
+        <v>132.85</v>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>supermarket_1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>export.202501.categorized.csv</t>
         </is>
@@ -3091,7 +3724,7 @@
           <t>TX-000002</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B7" s="11" t="n">
         <v>45676</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -3116,23 +3749,34 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>Wohnen / Haushalt</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>ONLINE HAUSHALT AG</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>PAYMENT ID 250119000000000000 BESTELLNUMMER DP-P-00000000</t>
         </is>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="J7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5" t="n">
         <v>13.9</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" s="5" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>home_3</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>export.202501.categorized.csv</t>
         </is>
@@ -3144,7 +3788,7 @@
           <t>TX-000001</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B8" s="11" t="n">
         <v>45682</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -3162,26 +3806,36 @@
           <t>Rückerstattungen</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
+          <t>Rückerstattungen</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>+41790000000 MAX MUSTER</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>MITTEILUNGEN: TEST</t>
         </is>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="J8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5" t="n">
         <v>-1</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>refund_1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>export.202501.categorized.csv</t>
         </is>
@@ -3193,7 +3847,7 @@
           <t>TX-000070</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="11" t="n">
         <v>45682</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -3218,23 +3872,34 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>Einkommen / Lohn</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>SALAER JANUAR 2025 | SALA00000000000000000000000000000001 9988776655/1XXXX 250125CH0EXMPL01</t>
         </is>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="J9" s="5" t="n">
+        <v>4200</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5" t="n">
         <v>-4200</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>income_1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>export.202501.categorized.csv</t>
         </is>
@@ -3246,7 +3911,7 @@
           <t>TX-000075</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n">
+      <c r="B10" s="11" t="n">
         <v>45685</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -3271,19 +3936,29 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>Einkaufen / Supermärkte</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>MIGROS MARKTHALLE (8812)</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" s="5" t="n">
+      <c r="J10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5" t="n">
         <v>96.40000000000001</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" s="5" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>supermarket_1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>export.202501.categorized.csv</t>
         </is>
@@ -3295,7 +3970,7 @@
           <t>TX-000074</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" s="11" t="n">
         <v>45688</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -3320,23 +3995,34 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>Wohnen / Miete und Hypothek</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>FINANZVERWALTUNG STADT SOLOTHURN</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>2025/02/01 / 7045128</t>
         </is>
       </c>
-      <c r="I11" s="5" t="n">
+      <c r="J11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5" t="n">
         <v>1774</v>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" s="5" t="n">
+        <v>1774</v>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>housing_1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>export.202501.categorized.csv</t>
         </is>
@@ -3348,7 +4034,7 @@
           <t>TX-000083</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="11" t="n">
         <v>45689</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -3373,19 +4059,29 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>Einkaufen / Supermärkte</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>MIGROS M RIVERSIDE (7741)</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" s="5" t="n">
+      <c r="J12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5" t="n">
         <v>63.75</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" s="5" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>supermarket_1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>export.202502.categorized.csv</t>
         </is>
@@ -3397,7 +4093,7 @@
           <t>TX-000082</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n">
+      <c r="B13" s="11" t="n">
         <v>45696</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -3422,19 +4118,29 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>Einkaufen / Supermärkte</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>MIGROS MARKTHALLE (8812)</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" s="5" t="n">
+      <c r="J13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5" t="n">
         <v>127.4</v>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" s="5" t="n">
+        <v>127.4</v>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>supermarket_1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>export.202502.categorized.csv</t>
         </is>
@@ -3446,7 +4152,7 @@
           <t>TX-000081</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B14" s="11" t="n">
         <v>45702</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -3471,19 +4177,29 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>Einkaufen / Supermärkte</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>COOP-5510 RIVERSIDE REST.</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" s="5" t="n">
+      <c r="J14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5" t="n">
         <v>88.95</v>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" s="5" t="n">
+        <v>88.95</v>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>supermarket_1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>export.202502.categorized.csv</t>
         </is>
@@ -3495,7 +4211,7 @@
           <t>TX-000080</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n">
+      <c r="B15" s="11" t="n">
         <v>45710</v>
       </c>
       <c r="C15" t="inlineStr">
@@ -3520,19 +4236,29 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>Einkaufen / Supermärkte</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>MIGROS MARKTHALLE (8812)</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" s="5" t="n">
+      <c r="J15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5" t="n">
         <v>154.6</v>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" s="5" t="n">
+        <v>154.6</v>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t>supermarket_1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>export.202502.categorized.csv</t>
         </is>
@@ -3544,7 +4270,7 @@
           <t>TX-000071</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n">
+      <c r="B16" s="11" t="n">
         <v>45713</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -3569,23 +4295,34 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>Einkommen / Lohn</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>SALAER FEBRUAR 2025 | SALA00000000000000000000000000000002 9988776655/1XXXX 250225CH0EXMPL02</t>
         </is>
       </c>
-      <c r="I16" s="5" t="n">
+      <c r="J16" s="5" t="n">
+        <v>4200</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5" t="n">
         <v>-4200</v>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>income_1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>export.202502.categorized.csv</t>
         </is>
@@ -3597,7 +4334,7 @@
           <t>TX-000060</t>
         </is>
       </c>
-      <c r="B17" s="9" t="n">
+      <c r="B17" s="11" t="n">
         <v>45715</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -3622,19 +4359,29 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>Freizeit / Gastronomie</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>MUSTER CAFE</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" s="5" t="n">
+      <c r="J17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>gastronomy_6</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>export.202502.categorized.csv</t>
         </is>
@@ -3646,7 +4393,7 @@
           <t>TX-000079</t>
         </is>
       </c>
-      <c r="B18" s="9" t="n">
+      <c r="B18" s="11" t="n">
         <v>45716</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -3671,23 +4418,34 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>Wohnen / Miete und Hypothek</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>FINANZVERWALTUNG STADT SOLOTHURN</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>2025/03/01 / 7045128</t>
         </is>
       </c>
-      <c r="I18" s="5" t="n">
+      <c r="J18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5" t="n">
         <v>1774</v>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" s="5" t="n">
+        <v>1774</v>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>housing_1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>export.202502.categorized.csv</t>
         </is>
@@ -3699,7 +4457,7 @@
           <t>TX-000054</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n">
+      <c r="B19" s="11" t="n">
         <v>45738</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -3724,23 +4482,34 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>Freizeit / Gastronomie</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>+41790000000 MAX MUSTER</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>MITTEILUNGEN: ESSEN GESTERN ABEND</t>
         </is>
       </c>
-      <c r="I19" s="5" t="n">
+      <c r="J19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="L19" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>gastronomy_5</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -3752,7 +4521,7 @@
           <t>TX-000055</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B20" s="11" t="n">
         <v>45738</v>
       </c>
       <c r="C20" t="inlineStr">
@@ -3760,28 +4529,36 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>UNMATCHED TEST STORE</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" s="5" t="n">
+      <c r="J20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="5" t="n">
         <v>12.4</v>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" s="5" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -3793,7 +4570,7 @@
           <t>TX-000051</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n">
+      <c r="B21" s="11" t="n">
         <v>45739</v>
       </c>
       <c r="C21" t="inlineStr">
@@ -3818,19 +4595,29 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>Einkaufen / Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>BÄCKEREI HUG</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" s="5" t="n">
+      <c r="J21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="5" t="n">
         <v>17.3</v>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="L21" s="5" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>grocery_1</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -3842,7 +4629,7 @@
           <t>TX-000052</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n">
+      <c r="B22" s="11" t="n">
         <v>45739</v>
       </c>
       <c r="C22" t="inlineStr">
@@ -3867,19 +4654,29 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>Wohnen / Haushalt</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>MANOR AG - 771 (CENTRA)</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" s="5" t="n">
+      <c r="J22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="5" t="n">
         <v>23.95</v>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" s="5" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>home_2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -3891,7 +4688,7 @@
           <t>TX-000053</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n">
+      <c r="B23" s="11" t="n">
         <v>45739</v>
       </c>
       <c r="C23" t="inlineStr">
@@ -3916,19 +4713,29 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>Freizeit / Gastronomie</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>+41796666222 KEBAB, IMBISS</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" s="5" t="n">
+      <c r="J23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="5" t="n">
         <v>13.5</v>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="L23" s="5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t>gastronomy_4</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -3940,7 +4747,7 @@
           <t>TX-000045</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n">
+      <c r="B24" s="11" t="n">
         <v>45740</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -3965,19 +4772,29 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>Einkaufen / Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>WAKARA GMBH</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" s="5" t="n">
+      <c r="J24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="5" t="n">
         <v>27.6</v>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="L24" s="5" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t>grocery_2</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -3989,7 +4806,7 @@
           <t>TX-000046</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n">
+      <c r="B25" s="11" t="n">
         <v>45740</v>
       </c>
       <c r="C25" t="inlineStr">
@@ -4014,19 +4831,29 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
+          <t>Leben / Styling und Wellness</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>THE BODY SHOP</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" s="5" t="n">
+      <c r="J25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="5" t="n">
         <v>4.95</v>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="L25" s="5" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>wellness_1</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -4038,7 +4865,7 @@
           <t>TX-000047</t>
         </is>
       </c>
-      <c r="B26" s="9" t="n">
+      <c r="B26" s="11" t="n">
         <v>45740</v>
       </c>
       <c r="C26" t="inlineStr">
@@ -4063,19 +4890,29 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
+          <t>Einkaufen / Supermärkte</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>COOP-5510 RIVERSIDE REST.</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" s="5" t="n">
+      <c r="J26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="L26" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>supermarket_1</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -4087,7 +4924,7 @@
           <t>TX-000048</t>
         </is>
       </c>
-      <c r="B27" s="9" t="n">
+      <c r="B27" s="11" t="n">
         <v>45740</v>
       </c>
       <c r="C27" t="inlineStr">
@@ -4112,19 +4949,29 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
+          <t>Einkaufen / Supermärkte</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
           <t>MIGROS MARKTHALLE (8812)</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" s="5" t="n">
+      <c r="J27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="5" t="n">
         <v>53.5</v>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="L27" s="5" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t>supermarket_1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -4136,7 +4983,7 @@
           <t>TX-000049</t>
         </is>
       </c>
-      <c r="B28" s="9" t="n">
+      <c r="B28" s="11" t="n">
         <v>45740</v>
       </c>
       <c r="C28" t="inlineStr">
@@ -4161,19 +5008,29 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>Freizeit / Gastronomie</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>MIGROS CITY TAKE AWAY (6624)</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" s="5" t="n">
+      <c r="J28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="5" t="n">
         <v>6.8</v>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="L28" s="5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>gastronomy_1</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -4185,7 +5042,7 @@
           <t>TX-000050</t>
         </is>
       </c>
-      <c r="B29" s="9" t="n">
+      <c r="B29" s="11" t="n">
         <v>45740</v>
       </c>
       <c r="C29" t="inlineStr">
@@ -4210,19 +5067,29 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
+          <t>Leben / Krankenkasse</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>MEDICURA PLUS AG GESUNDHEITSWEG 8 4052 BASEL</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" s="5" t="n">
+      <c r="J29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="5" t="n">
         <v>77.45</v>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="L29" s="5" t="n">
+        <v>77.45</v>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t>health_2</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -4234,7 +5101,7 @@
           <t>TX-000039</t>
         </is>
       </c>
-      <c r="B30" s="9" t="n">
+      <c r="B30" s="11" t="n">
         <v>45741</v>
       </c>
       <c r="C30" t="inlineStr">
@@ -4259,19 +5126,29 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
+          <t>Einkaufen / Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
           <t>BÄCKEREI HUG</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" s="5" t="n">
+      <c r="J30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="5" t="n">
         <v>6.1</v>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="L30" s="5" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t>grocery_1</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -4283,7 +5160,7 @@
           <t>TX-000040</t>
         </is>
       </c>
-      <c r="B31" s="9" t="n">
+      <c r="B31" s="11" t="n">
         <v>45741</v>
       </c>
       <c r="C31" t="inlineStr">
@@ -4308,19 +5185,29 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>Einkaufen / Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
           <t>BRANKOVIC BREZELSTUBE</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" s="5" t="n">
+      <c r="J31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="5" t="n">
         <v>4.3</v>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="L31" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t>grocery_1</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -4332,7 +5219,7 @@
           <t>TX-000041</t>
         </is>
       </c>
-      <c r="B32" s="9" t="n">
+      <c r="B32" s="11" t="n">
         <v>45741</v>
       </c>
       <c r="C32" t="inlineStr">
@@ -4357,19 +5244,29 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
+          <t>Einkaufen / Supermärkte</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>MIGROS M RIVERSIDE (7741)</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" s="5" t="n">
+      <c r="J32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="5" t="n">
         <v>10.35</v>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="L32" s="5" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t>supermarket_1</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -4381,7 +5278,7 @@
           <t>TX-000043</t>
         </is>
       </c>
-      <c r="B33" s="9" t="n">
+      <c r="B33" s="11" t="n">
         <v>45741</v>
       </c>
       <c r="C33" t="inlineStr">
@@ -4406,23 +5303,34 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
+          <t>Leben / Krankenkasse</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
           <t>MEDICURA PLUS AG GESUNDHEITSWEG 8 4052 BASEL</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>LEISTUNGSABRECHNUNG NR.: 700112233445566 VERSICHERTE PERSON 445566 BETRIFFT LEISTUNGEN | MED95CB11F8253446278F81749F26F10588</t>
         </is>
       </c>
-      <c r="I33" s="5" t="n">
+      <c r="J33" s="5" t="n">
+        <v>1787.95</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="5" t="n">
         <v>-1787.95</v>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>refund_2</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -4434,7 +5342,7 @@
           <t>TX-000044</t>
         </is>
       </c>
-      <c r="B34" s="9" t="n">
+      <c r="B34" s="11" t="n">
         <v>45741</v>
       </c>
       <c r="C34" t="inlineStr">
@@ -4459,19 +5367,29 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
+          <t>Wohnen / Kommunikation</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
           <t>CLOUDSERVICE INC SAN</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" s="5" t="n">
+      <c r="J34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5" t="n">
         <v>18.67</v>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="L34" s="5" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t>communication_3</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -4483,7 +5401,7 @@
           <t>TX-000058</t>
         </is>
       </c>
-      <c r="B35" s="9" t="n">
+      <c r="B35" s="11" t="n">
         <v>45741</v>
       </c>
       <c r="C35" t="inlineStr">
@@ -4508,23 +5426,34 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
+          <t>Überträge / Account Transfer</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
           <t>EIGENES SPARKONTO KONTOUEBERTRAG TRANSFER-20250325</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>EIGENES SPARKONTO KONTOUEBERTRAG TRANSFER-20250325</t>
         </is>
       </c>
-      <c r="I35" s="5" t="n">
+      <c r="J35" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="5" t="n">
         <v>-450</v>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>transfer_1</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -4536,7 +5465,7 @@
           <t>TX-000072</t>
         </is>
       </c>
-      <c r="B36" s="9" t="n">
+      <c r="B36" s="11" t="n">
         <v>45741</v>
       </c>
       <c r="C36" t="inlineStr">
@@ -4561,23 +5490,34 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
+          <t>Einkommen / Lohn</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
           <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>SALAER BONUS 2024 | SALA00000000000000000000000000000003 9988776655/1XXXX 250325CH0EXMPL03</t>
         </is>
       </c>
-      <c r="I36" s="5" t="n">
+      <c r="J36" s="5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="5" t="n">
         <v>-1500</v>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>income_1</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -4589,7 +5529,7 @@
           <t>TX-000073</t>
         </is>
       </c>
-      <c r="B37" s="9" t="n">
+      <c r="B37" s="11" t="n">
         <v>45741</v>
       </c>
       <c r="C37" t="inlineStr">
@@ -4614,23 +5554,34 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
+          <t>Einkommen / Lohn</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
           <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>SALAER MAERZ 2025 | SALA80E5ED528784F48B451A4175649C112 9988776655/1XXXX 250325CH7LMNQRTS</t>
         </is>
       </c>
-      <c r="I37" s="5" t="n">
+      <c r="J37" s="5" t="n">
+        <v>4200</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="5" t="n">
         <v>-4200</v>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>income_1</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -4642,7 +5593,7 @@
           <t>TX-000035</t>
         </is>
       </c>
-      <c r="B38" s="9" t="n">
+      <c r="B38" s="11" t="n">
         <v>45742</v>
       </c>
       <c r="C38" t="inlineStr">
@@ -4667,19 +5618,29 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
+          <t>Mobilität / Öffentlicher Verkehr</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
           <t>TRANSPORTS PUBLICS FRIBOURGEOIS (FAIRTIQ) N/A PAYMENT ID 250326064915818975ZX BESTELLNUMMER</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" s="5" t="n">
+      <c r="J38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="5" t="n">
         <v>62.6</v>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="L38" s="5" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t>transport_1</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -4691,7 +5652,7 @@
           <t>TX-000036</t>
         </is>
       </c>
-      <c r="B39" s="9" t="n">
+      <c r="B39" s="11" t="n">
         <v>45742</v>
       </c>
       <c r="C39" t="inlineStr">
@@ -4716,19 +5677,29 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
+          <t>Wohnen / Handwerk und Garten</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>JUMBO-7782 INDUSTRIEPARK</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" s="5" t="n">
+      <c r="J39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="5" t="n">
         <v>10.9</v>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="L39" s="5" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t>home_1</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -4740,7 +5711,7 @@
           <t>TX-000037</t>
         </is>
       </c>
-      <c r="B40" s="9" t="n">
+      <c r="B40" s="11" t="n">
         <v>45742</v>
       </c>
       <c r="C40" t="inlineStr">
@@ -4765,23 +5736,34 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
+          <t>Freizeit / Gastronomie</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
           <t>+41796666222 KEBAB, IMBISS</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>MITTEILUNGEN: KEBAB</t>
         </is>
       </c>
-      <c r="I40" s="5" t="n">
+      <c r="J40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="L40" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t>gastronomy_4</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -4793,7 +5775,7 @@
           <t>TX-000038</t>
         </is>
       </c>
-      <c r="B41" s="9" t="n">
+      <c r="B41" s="11" t="n">
         <v>45742</v>
       </c>
       <c r="C41" t="inlineStr">
@@ -4818,23 +5800,34 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
+          <t>Leben / Familie</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
           <t>FAMILIENKASSE MUSTERHAUSEN SENDER REFERENZ: FAMILIENZULAGE</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>90-33445566</t>
         </is>
       </c>
-      <c r="I41" s="5" t="n">
+      <c r="J41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="L41" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t>family_1</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -4846,7 +5839,7 @@
           <t>TX-000024</t>
         </is>
       </c>
-      <c r="B42" s="9" t="n">
+      <c r="B42" s="11" t="n">
         <v>45743</v>
       </c>
       <c r="C42" t="inlineStr">
@@ -4871,19 +5864,29 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
+          <t>Wohnen / Kommunikation</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
           <t>APPLE.COM/BILL</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" s="5" t="n">
+      <c r="J42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="L42" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t>communication_2</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -4895,7 +5898,7 @@
           <t>TX-000025</t>
         </is>
       </c>
-      <c r="B43" s="9" t="n">
+      <c r="B43" s="11" t="n">
         <v>45743</v>
       </c>
       <c r="C43" t="inlineStr">
@@ -4920,19 +5923,29 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
+          <t>Freizeit / Gastronomie</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>YOOJI'S ROSENGARTEN</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" s="5" t="n">
+      <c r="J43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="5" t="n">
         <v>6.9</v>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="L43" s="5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t>gastronomy_2</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -4944,7 +5957,7 @@
           <t>TX-000026</t>
         </is>
       </c>
-      <c r="B44" s="9" t="n">
+      <c r="B44" s="11" t="n">
         <v>45743</v>
       </c>
       <c r="C44" t="inlineStr">
@@ -4969,19 +5982,29 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
+          <t>Einkaufen / Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
           <t>CONFISERIE SPRÜNGLI AG</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" s="5" t="n">
+      <c r="J44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="5" t="n">
         <v>22.05</v>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="L44" s="5" t="n">
+        <v>22.05</v>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t>grocery_1</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -4993,7 +6016,7 @@
           <t>TX-000027</t>
         </is>
       </c>
-      <c r="B45" s="9" t="n">
+      <c r="B45" s="11" t="n">
         <v>45743</v>
       </c>
       <c r="C45" t="inlineStr">
@@ -5018,19 +6041,29 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
+          <t>Leben / Styling und Wellness</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>THE BODY SHOP</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" s="5" t="n">
+      <c r="J45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="5" t="n">
         <v>24.95</v>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="L45" s="5" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t>wellness_1</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -5042,7 +6075,7 @@
           <t>TX-000028</t>
         </is>
       </c>
-      <c r="B46" s="9" t="n">
+      <c r="B46" s="11" t="n">
         <v>45743</v>
       </c>
       <c r="C46" t="inlineStr">
@@ -5067,19 +6100,29 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
+          <t>Freizeit / Gastronomie</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
           <t>YOOJI'S ROSENGARTEN</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" s="5" t="n">
+      <c r="J46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="5" t="n">
         <v>11.9</v>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="L46" s="5" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t>gastronomy_2</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -5091,7 +6134,7 @@
           <t>TX-000029</t>
         </is>
       </c>
-      <c r="B47" s="9" t="n">
+      <c r="B47" s="11" t="n">
         <v>45743</v>
       </c>
       <c r="C47" t="inlineStr">
@@ -5116,19 +6159,29 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
+          <t>Freizeit / Gastronomie</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
           <t>YOOJI'S ROSENGARTEN</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" s="5" t="n">
+      <c r="J47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="5" t="n">
         <v>43.5</v>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="L47" s="5" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t>gastronomy_2</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -5140,7 +6193,7 @@
           <t>TX-000030</t>
         </is>
       </c>
-      <c r="B48" s="9" t="n">
+      <c r="B48" s="11" t="n">
         <v>45743</v>
       </c>
       <c r="C48" t="inlineStr">
@@ -5165,19 +6218,29 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
+          <t>Freizeit / Gastronomie</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
           <t>COFFEE AND PLANTS</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" s="5" t="n">
+      <c r="J48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="L48" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t>gastronomy_3</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -5189,7 +6252,7 @@
           <t>TX-000032</t>
         </is>
       </c>
-      <c r="B49" s="9" t="n">
+      <c r="B49" s="11" t="n">
         <v>45743</v>
       </c>
       <c r="C49" t="inlineStr">
@@ -5214,19 +6277,29 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
+          <t>Einkaufen / Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
           <t>YUMIHANA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" s="5" t="n">
+      <c r="J49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="5" t="n">
         <v>18.55</v>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="L49" s="5" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t>grocery_2</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -5238,7 +6311,7 @@
           <t>TX-000033</t>
         </is>
       </c>
-      <c r="B50" s="9" t="n">
+      <c r="B50" s="11" t="n">
         <v>45743</v>
       </c>
       <c r="C50" t="inlineStr">
@@ -5263,19 +6336,29 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
+          <t>Einkaufen / Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
           <t>YUMI HANA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" s="5" t="n">
+      <c r="J50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="5" t="n">
         <v>26.8</v>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="L50" s="5" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t>grocery_2</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -5287,7 +6370,7 @@
           <t>TX-000034</t>
         </is>
       </c>
-      <c r="B51" s="9" t="n">
+      <c r="B51" s="11" t="n">
         <v>45743</v>
       </c>
       <c r="C51" t="inlineStr">
@@ -5312,19 +6395,29 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
+          <t>Einkaufen / Supermärkte</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
           <t>COOP - 7811 QUAI WEST</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" s="5" t="n">
+      <c r="J51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="5" t="n">
         <v>7.75</v>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="L51" s="5" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t>supermarket_1</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -5336,7 +6429,7 @@
           <t>TX-000018</t>
         </is>
       </c>
-      <c r="B52" s="9" t="n">
+      <c r="B52" s="11" t="n">
         <v>45744</v>
       </c>
       <c r="C52" t="inlineStr">
@@ -5361,19 +6454,29 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
+          <t>Mobilität / Öffentlicher Verkehr</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
           <t>TRANSPORTS PUBLICS FRIBOURGEOIS (FAIRTIQ) N/A PAYMENT ID 250328064754083058ZX BESTELLNUMMER</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" s="5" t="n">
+      <c r="J52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="5" t="n">
         <v>34.3</v>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="L52" s="5" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t>transport_1</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -5385,7 +6488,7 @@
           <t>TX-000019</t>
         </is>
       </c>
-      <c r="B53" s="9" t="n">
+      <c r="B53" s="11" t="n">
         <v>45744</v>
       </c>
       <c r="C53" t="inlineStr">
@@ -5410,19 +6513,29 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
+          <t>Einkaufen / Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
           <t>SUMUP *BACKEREI ZUR K</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" s="5" t="n">
+      <c r="J53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="5" t="n">
         <v>11.1</v>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="L53" s="5" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t>grocery_1</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -5434,7 +6547,7 @@
           <t>TX-000020</t>
         </is>
       </c>
-      <c r="B54" s="9" t="n">
+      <c r="B54" s="11" t="n">
         <v>45744</v>
       </c>
       <c r="C54" t="inlineStr">
@@ -5459,19 +6572,29 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
+          <t>Einkaufen / Sonstiges Einkaufen</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
           <t>KKIOSK 45810</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" s="5" t="n">
+      <c r="J54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="5" t="n">
         <v>7.1</v>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="L54" s="5" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t>shopping_1</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -5483,7 +6606,7 @@
           <t>TX-000021</t>
         </is>
       </c>
-      <c r="B55" s="9" t="n">
+      <c r="B55" s="11" t="n">
         <v>45744</v>
       </c>
       <c r="C55" t="inlineStr">
@@ -5508,19 +6631,29 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
+          <t>Leben / Gesundheit</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
           <t>BAHNHOF APOTHEKE AG</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" s="5" t="n">
+      <c r="J55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="5" t="n">
         <v>24.4</v>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="L55" s="5" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t>health_1</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -5532,7 +6665,7 @@
           <t>TX-000022</t>
         </is>
       </c>
-      <c r="B56" s="9" t="n">
+      <c r="B56" s="11" t="n">
         <v>45744</v>
       </c>
       <c r="C56" t="inlineStr">
@@ -5557,19 +6690,29 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
+          <t>Einkaufen / Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
           <t>BÄCKEREI HUG</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" s="5" t="n">
+      <c r="J56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="5" t="n">
         <v>8.1</v>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="L56" s="5" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t>grocery_1</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -5581,7 +6724,7 @@
           <t>TX-000023</t>
         </is>
       </c>
-      <c r="B57" s="9" t="n">
+      <c r="B57" s="11" t="n">
         <v>45744</v>
       </c>
       <c r="C57" t="inlineStr">
@@ -5606,19 +6749,29 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
+          <t>Einkaufen / Supermärkte</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
           <t>MIGROS M RIVERSIDE (7741)</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" s="5" t="n">
+      <c r="J57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="5" t="n">
         <v>28.35</v>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="L57" s="5" t="n">
+        <v>28.35</v>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t>supermarket_1</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -5630,7 +6783,7 @@
           <t>TX-000015</t>
         </is>
       </c>
-      <c r="B58" s="9" t="n">
+      <c r="B58" s="11" t="n">
         <v>45745</v>
       </c>
       <c r="C58" t="inlineStr">
@@ -5655,19 +6808,29 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
+          <t>Einkaufen / Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
           <t>BÄCKEREI HUG</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" s="5" t="n">
+      <c r="J58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="5" t="n">
         <v>8.5</v>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="L58" s="5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t>grocery_1</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -5679,7 +6842,7 @@
           <t>TX-000016</t>
         </is>
       </c>
-      <c r="B59" s="9" t="n">
+      <c r="B59" s="11" t="n">
         <v>45745</v>
       </c>
       <c r="C59" t="inlineStr">
@@ -5704,19 +6867,29 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
+          <t>Einkaufen / Supermärkte</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
           <t>MIGROS M RIVERSIDE (7741)</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" s="5" t="n">
+      <c r="J59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="5" t="n">
         <v>2.9</v>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="L59" s="5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t>supermarket_1</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -5728,7 +6901,7 @@
           <t>TX-000017</t>
         </is>
       </c>
-      <c r="B60" s="9" t="n">
+      <c r="B60" s="11" t="n">
         <v>45745</v>
       </c>
       <c r="C60" t="inlineStr">
@@ -5753,19 +6926,29 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
+          <t>Wohnen / Kommunikation</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
           <t>SUNRISE GMBH POSTFACH 8050 ZURICH</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" s="5" t="n">
+      <c r="J60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="5" t="n">
         <v>49.6</v>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="L60" s="5" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t>communication_1</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -5777,7 +6960,7 @@
           <t>TX-000010</t>
         </is>
       </c>
-      <c r="B61" s="9" t="n">
+      <c r="B61" s="11" t="n">
         <v>45746</v>
       </c>
       <c r="C61" t="inlineStr">
@@ -5802,19 +6985,29 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
+          <t>Freizeit / Gastronomie</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
           <t>SIGNOR ROSSI</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" s="5" t="n">
+      <c r="J61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="L61" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t>gastronomy_2</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -5826,7 +7019,7 @@
           <t>TX-000011</t>
         </is>
       </c>
-      <c r="B62" s="9" t="n">
+      <c r="B62" s="11" t="n">
         <v>45746</v>
       </c>
       <c r="C62" t="inlineStr">
@@ -5851,19 +7044,29 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
+          <t>Einkaufen / Supermärkte</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
           <t>MIGROS MARKTHALLE (8812)</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" s="5" t="n">
+      <c r="J62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="5" t="n">
         <v>20.7</v>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="L62" s="5" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t>supermarket_1</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -5875,7 +7078,7 @@
           <t>TX-000012</t>
         </is>
       </c>
-      <c r="B63" s="9" t="n">
+      <c r="B63" s="11" t="n">
         <v>45746</v>
       </c>
       <c r="C63" t="inlineStr">
@@ -5900,19 +7103,29 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
+          <t>Freizeit / Gastronomie</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
           <t>MIGROS CITY TAKE AWAY (6624)</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" s="5" t="n">
+      <c r="J63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="5" t="n">
         <v>3.9</v>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="L63" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t>gastronomy_1</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -5924,7 +7137,7 @@
           <t>TX-000013</t>
         </is>
       </c>
-      <c r="B64" s="9" t="n">
+      <c r="B64" s="11" t="n">
         <v>45746</v>
       </c>
       <c r="C64" t="inlineStr">
@@ -5949,19 +7162,29 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
+          <t>Freizeit / Kultur</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
           <t>BYRO</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" s="5" t="n">
+      <c r="J64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="L64" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t>life_1</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -5973,7 +7196,7 @@
           <t>TX-000014</t>
         </is>
       </c>
-      <c r="B65" s="9" t="n">
+      <c r="B65" s="11" t="n">
         <v>45746</v>
       </c>
       <c r="C65" t="inlineStr">
@@ -5998,19 +7221,29 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
+          <t>Leben / Sonstiges Leben</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
           <t>BYRO</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" s="5" t="n">
+      <c r="J65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="5" t="n">
         <v>36.8</v>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="L65" s="5" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t>life_1</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -6022,7 +7255,7 @@
           <t>TX-000003</t>
         </is>
       </c>
-      <c r="B66" s="9" t="n">
+      <c r="B66" s="11" t="n">
         <v>45747</v>
       </c>
       <c r="C66" t="inlineStr">
@@ -6047,19 +7280,29 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
+          <t>Einkaufen / Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
           <t>CITY TANKSTELLE</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" s="5" t="n">
+      <c r="J66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="5" t="n">
         <v>10.34</v>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="L66" s="5" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t>grocery_3</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -6071,7 +7314,7 @@
           <t>TX-000004</t>
         </is>
       </c>
-      <c r="B67" s="9" t="n">
+      <c r="B67" s="11" t="n">
         <v>45747</v>
       </c>
       <c r="C67" t="inlineStr">
@@ -6096,19 +7339,29 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
+          <t>Einkaufen / Detail-Lebensmittel</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
           <t>CITY TANKSTELLE</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" s="5" t="n">
+      <c r="J67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="5" t="n">
         <v>6.55</v>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="L67" s="5" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t>grocery_3</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -6120,7 +7373,7 @@
           <t>TX-000006</t>
         </is>
       </c>
-      <c r="B68" s="9" t="n">
+      <c r="B68" s="11" t="n">
         <v>45747</v>
       </c>
       <c r="C68" t="inlineStr">
@@ -6145,19 +7398,29 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
+          <t>Einkaufen / Sonstiges Einkaufen</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
           <t>KKIOSK 45810</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" s="5" t="n">
+      <c r="J68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="5" t="n">
         <v>7.55</v>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="L68" s="5" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t>shopping_1</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -6169,7 +7432,7 @@
           <t>TX-000007</t>
         </is>
       </c>
-      <c r="B69" s="9" t="n">
+      <c r="B69" s="11" t="n">
         <v>45747</v>
       </c>
       <c r="C69" t="inlineStr">
@@ -6194,19 +7457,29 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
+          <t>Einkaufen / Supermärkte</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
           <t>MIGROS MARKTHALLE (8812)</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" s="5" t="n">
+      <c r="J69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="5" t="n">
         <v>22.2</v>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="L69" s="5" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t>supermarket_1</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -6218,7 +7491,7 @@
           <t>TX-000008</t>
         </is>
       </c>
-      <c r="B70" s="9" t="n">
+      <c r="B70" s="11" t="n">
         <v>45747</v>
       </c>
       <c r="C70" t="inlineStr">
@@ -6243,23 +7516,34 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
+          <t>Finanzen / Fees</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
           <t>PREIS FÜR BANKPAKET SMART 02.2025</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>PREIS FÜR BANKPAKET SMART 02.2025</t>
         </is>
       </c>
-      <c r="I70" s="5" t="n">
+      <c r="J70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="L70" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t>finance_2</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -6271,7 +7555,7 @@
           <t>TX-000009</t>
         </is>
       </c>
-      <c r="B71" s="9" t="n">
+      <c r="B71" s="11" t="n">
         <v>45747</v>
       </c>
       <c r="C71" t="inlineStr">
@@ -6296,23 +7580,34 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
+          <t>Wohnen / Miete und Hypothek</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
           <t>FINANZVERWALTUNG STADT SOLOTHURN</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>2025/04/01 / 7045128</t>
         </is>
       </c>
-      <c r="I71" s="5" t="n">
+      <c r="J71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="5" t="n">
         <v>1774</v>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="L71" s="5" t="n">
+        <v>1774</v>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t>housing_1</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -6324,7 +7619,7 @@
           <t>TX-000064</t>
         </is>
       </c>
-      <c r="B72" s="9" t="n">
+      <c r="B72" s="11" t="n">
         <v>45747</v>
       </c>
       <c r="C72" t="inlineStr">
@@ -6349,19 +7644,29 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
+          <t>Leben / Styling und Wellness</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
           <t>SUMUP *COIFFEUR HAIRCUT</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" s="5" t="n">
+      <c r="J72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="L72" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t>wellness_2</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>export.202503.categorized.csv</t>
         </is>
@@ -6373,7 +7678,7 @@
           <t>TX-000089</t>
         </is>
       </c>
-      <c r="B73" s="9" t="n">
+      <c r="B73" s="11" t="n">
         <v>45748</v>
       </c>
       <c r="C73" t="inlineStr">
@@ -6398,19 +7703,29 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
+          <t>Leben / Krankenkasse</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
           <t>MUSTER UND BEISPIEL GEMEINSCHAFTSKONTO MUSTERWEG 1 4600 OLTEN</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" s="5" t="n">
+      <c r="J73" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="5" t="n">
         <v>-120</v>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>refund_example_amount_1</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>export.202504.categorized.csv</t>
         </is>
@@ -6422,7 +7737,7 @@
           <t>TX-000090</t>
         </is>
       </c>
-      <c r="B74" s="9" t="n">
+      <c r="B74" s="11" t="n">
         <v>45748</v>
       </c>
       <c r="C74" t="inlineStr">
@@ -6447,19 +7762,29 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
+          <t>Leben / Familie</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
           <t>MUSTER UND BEISPIEL GEMEINSCHAFTSKONTO MUSTERWEG 1 4600 OLTEN</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" s="5" t="n">
+      <c r="J74" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="5" t="n">
         <v>-15</v>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>refund_example_counterparty_1</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>export.202504.categorized.csv</t>
         </is>
@@ -6471,7 +7796,7 @@
           <t>TX-000061</t>
         </is>
       </c>
-      <c r="B75" s="9" t="n">
+      <c r="B75" s="11" t="n">
         <v>45751</v>
       </c>
       <c r="C75" t="inlineStr">
@@ -6496,19 +7821,29 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
+          <t>Freizeit / Reisen und Erleben</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
           <t>UEFA WOMEN'S EURO 2025 NYON</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" s="5" t="n">
+      <c r="J75" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="5" t="n">
         <v>-100</v>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>refund_3</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>export.202504.categorized.csv</t>
         </is>
@@ -6520,7 +7855,7 @@
           <t>TX-000084</t>
         </is>
       </c>
-      <c r="B76" s="9" t="n">
+      <c r="B76" s="11" t="n">
         <v>45752</v>
       </c>
       <c r="C76" t="inlineStr">
@@ -6545,19 +7880,29 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
+          <t>Einkaufen / Supermärkte</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
           <t>MIGROS MARKTHALLE (8812)</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" s="5" t="n">
+      <c r="J76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="5" t="n">
         <v>108.9</v>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="L76" s="5" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t>supermarket_1</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>export.202504.categorized.csv</t>
         </is>
@@ -6569,7 +7914,7 @@
           <t>TX-000085</t>
         </is>
       </c>
-      <c r="B77" s="9" t="n">
+      <c r="B77" s="11" t="n">
         <v>45759</v>
       </c>
       <c r="C77" t="inlineStr">
@@ -6594,19 +7939,29 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
+          <t>Einkaufen / Supermärkte</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
           <t>COOP-5510 RIVERSIDE REST.</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" s="5" t="n">
+      <c r="J77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="5" t="n">
         <v>76.3</v>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="L77" s="5" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t>supermarket_1</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>export.202504.categorized.csv</t>
         </is>
@@ -6618,7 +7973,7 @@
           <t>TX-000062</t>
         </is>
       </c>
-      <c r="B78" s="9" t="n">
+      <c r="B78" s="11" t="n">
         <v>45763</v>
       </c>
       <c r="C78" t="inlineStr">
@@ -6643,23 +7998,34 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
+          <t>Einkommen / Lohn</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
           <t>FIKTIVE LOHN AG PERSONALABTEILUNG</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>LOHNBEISPIEL APRIL 2025 | DEMO REF 001</t>
         </is>
       </c>
-      <c r="I78" s="5" t="n">
+      <c r="J78" s="5" t="n">
+        <v>4200</v>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="5" t="n">
         <v>-4200</v>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>income_example_counterparty_1</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>export.202504.categorized.csv</t>
         </is>
@@ -6671,7 +8037,7 @@
           <t>TX-000063</t>
         </is>
       </c>
-      <c r="B79" s="9" t="n">
+      <c r="B79" s="11" t="n">
         <v>45764</v>
       </c>
       <c r="C79" t="inlineStr">
@@ -6696,19 +8062,29 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
+          <t>Finanzen / Spenden</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
           <t>ANONYMISIERTER VEREIN MITTEILUNGEN: DEMO-ZWECK JAHRESBEITRAG</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" s="5" t="n">
+      <c r="J79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="L79" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t>expense_example_counterparty_iban_1</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>export.202504.categorized.csv</t>
         </is>
@@ -6720,7 +8096,7 @@
           <t>TX-000065</t>
         </is>
       </c>
-      <c r="B80" s="9" t="n">
+      <c r="B80" s="11" t="n">
         <v>45765</v>
       </c>
       <c r="C80" t="inlineStr">
@@ -6728,32 +8104,41 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
           <t>FIKTIVE DIGITAL GMBH</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>PAYMENT ID 000A00D0 BESTELLNUMMER AB00CD00</t>
         </is>
       </c>
-      <c r="I80" s="5" t="n">
+      <c r="J80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="5" t="n">
         <v>33.7</v>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="L80" s="5" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>export.202504.categorized.csv</t>
         </is>
@@ -6765,7 +8150,7 @@
           <t>TX-000066</t>
         </is>
       </c>
-      <c r="B81" s="9" t="n">
+      <c r="B81" s="11" t="n">
         <v>45766</v>
       </c>
       <c r="C81" t="inlineStr">
@@ -6773,32 +8158,41 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
           <t>FIKTIVE POST AG</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>PAYMENT ID AB0CD0EF00GH0IJ0 BESTELLNUMMER MYS_AB0CD0EF00GH0I</t>
         </is>
       </c>
-      <c r="I81" s="5" t="n">
+      <c r="J81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="5" t="n">
         <v>12.5</v>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="L81" s="5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>export.202504.categorized.csv</t>
         </is>
@@ -6810,7 +8204,7 @@
           <t>TX-000086</t>
         </is>
       </c>
-      <c r="B82" s="9" t="n">
+      <c r="B82" s="11" t="n">
         <v>45766</v>
       </c>
       <c r="C82" t="inlineStr">
@@ -6835,19 +8229,29 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
+          <t>Einkaufen / Supermärkte</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
           <t>MIGROS M RIVERSIDE (7741)</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" s="5" t="n">
+      <c r="J82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="5" t="n">
         <v>54.85</v>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="L82" s="5" t="n">
+        <v>54.85</v>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t>supermarket_1</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>export.202504.categorized.csv</t>
         </is>
@@ -6859,7 +8263,7 @@
           <t>TX-000067</t>
         </is>
       </c>
-      <c r="B83" s="9" t="n">
+      <c r="B83" s="11" t="n">
         <v>45767</v>
       </c>
       <c r="C83" t="inlineStr">
@@ -6867,28 +8271,36 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
           <t>FIKTIVER SCHUHLADEN BIEL</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" s="5" t="n">
+      <c r="J83" s="5" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="5" t="n">
         <v>-49.9</v>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>export.202504.categorized.csv</t>
         </is>
@@ -6900,7 +8312,7 @@
           <t>TX-000068</t>
         </is>
       </c>
-      <c r="B84" s="9" t="n">
+      <c r="B84" s="11" t="n">
         <v>45768</v>
       </c>
       <c r="C84" t="inlineStr">
@@ -6908,28 +8320,36 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
           <t>FIKTIVER FAHRSCHEIN BERLIN DEUTSCHLAND</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" s="5" t="n">
+      <c r="J84" s="5" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="5" t="n">
         <v>-19.15</v>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>export.202504.categorized.csv</t>
         </is>
@@ -6941,7 +8361,7 @@
           <t>TX-000069</t>
         </is>
       </c>
-      <c r="B85" s="9" t="n">
+      <c r="B85" s="11" t="n">
         <v>45769</v>
       </c>
       <c r="C85" t="inlineStr">
@@ -6966,19 +8386,29 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
+          <t>Finanzen / Bargeldbezug</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
           <t>BAHNHOF</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" s="5" t="n">
+      <c r="J85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="5" t="n">
         <v>143.5</v>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="L85" s="5" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t>finance_1</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t>export.202504.categorized.csv</t>
         </is>
@@ -6990,7 +8420,7 @@
           <t>TX-000087</t>
         </is>
       </c>
-      <c r="B86" s="9" t="n">
+      <c r="B86" s="11" t="n">
         <v>45773</v>
       </c>
       <c r="C86" t="inlineStr">
@@ -7015,19 +8445,29 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
+          <t>Einkaufen / Supermärkte</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
           <t>MIGROS MARKTHALLE (8812)</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" s="5" t="n">
+      <c r="J86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="5" t="n">
         <v>121.6</v>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="L86" s="5" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t>supermarket_1</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t>export.202504.categorized.csv</t>
         </is>
@@ -7039,7 +8479,7 @@
           <t>TX-000088</t>
         </is>
       </c>
-      <c r="B87" s="9" t="n">
+      <c r="B87" s="11" t="n">
         <v>45777</v>
       </c>
       <c r="C87" t="inlineStr">
@@ -7064,30 +8504,41 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
+          <t>Wohnen / Miete und Hypothek</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
           <t>FINANZVERWALTUNG STADT SOLOTHURN</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>2025/05/01 / 7045128</t>
         </is>
       </c>
-      <c r="I87" s="5" t="n">
+      <c r="J87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="5" t="n">
         <v>1774</v>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="L87" s="5" t="n">
+        <v>1774</v>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t>housing_1</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="N87" t="inlineStr">
         <is>
           <t>export.202504.categorized.csv</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K87"/>
+  <autoFilter ref="A1:N87"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7178,7 +8629,7 @@
       <c r="F2" t="n">
         <v>4</v>
       </c>
-      <c r="G2" s="10" t="n">
+      <c r="G2" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
@@ -7210,7 +8661,7 @@
       <c r="F3" t="n">
         <v>4</v>
       </c>
-      <c r="G3" s="10" t="n">
+      <c r="G3" s="12" t="n">
         <v>0.599</v>
       </c>
       <c r="H3" t="n">
@@ -7242,7 +8693,7 @@
       <c r="F4" t="n">
         <v>4</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="G4" s="12" t="n">
         <v>0.2488</v>
       </c>
       <c r="H4" t="n">
@@ -7274,7 +8725,7 @@
       <c r="F5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" s="12" t="n">
         <v>0.1465</v>
       </c>
       <c r="H5" t="n">
@@ -7306,7 +8757,7 @@
       <c r="F6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="G6" s="12" t="n">
         <v>0.0056</v>
       </c>
       <c r="H6" t="n">
@@ -7338,7 +8789,7 @@
       <c r="F7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="10" t="n">
+      <c r="G7" s="12" t="n">
         <v>0.9804</v>
       </c>
       <c r="H7" t="n">
@@ -7370,7 +8821,7 @@
       <c r="F8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G8" s="12" t="n">
         <v>0.0931</v>
       </c>
       <c r="H8" t="n">
@@ -7402,7 +8853,7 @@
       <c r="F9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="10" t="n">
+      <c r="G9" s="12" t="n">
         <v>-0.0735</v>
       </c>
       <c r="H9" t="n">
@@ -7434,7 +8885,7 @@
       <c r="F10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G10" s="12" t="n">
         <v>0.2391</v>
       </c>
       <c r="H10" t="n">
@@ -7466,7 +8917,7 @@
       <c r="F11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="10" t="n">
+      <c r="G11" s="12" t="n">
         <v>0.165</v>
       </c>
       <c r="H11" t="n">
@@ -7498,7 +8949,7 @@
       <c r="F12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="G12" s="12" t="n">
         <v>0.1602</v>
       </c>
       <c r="H12" t="n">
@@ -7530,7 +8981,7 @@
       <c r="F13" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="10" t="n">
+      <c r="G13" s="12" t="n">
         <v>0.1318</v>
       </c>
       <c r="H13" t="n">
@@ -7562,7 +9013,7 @@
       <c r="F14" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="10" t="n">
+      <c r="G14" s="12" t="n">
         <v>0.1109</v>
       </c>
       <c r="H14" t="n">
@@ -7594,7 +9045,7 @@
       <c r="F15" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="10" t="n">
+      <c r="G15" s="12" t="n">
         <v>0.101</v>
       </c>
       <c r="H15" t="n">
@@ -7626,7 +9077,7 @@
       <c r="F16" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="10" t="n">
+      <c r="G16" s="12" t="n">
         <v>0.0664</v>
       </c>
       <c r="H16" t="n">
@@ -7658,7 +9109,7 @@
       <c r="F17" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="10" t="n">
+      <c r="G17" s="12" t="n">
         <v>0.0257</v>
       </c>
       <c r="H17" t="n">
@@ -7690,7 +9141,7 @@
       <c r="F18" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="10" t="n">
+      <c r="G18" s="12" t="n">
         <v>0.4059</v>
       </c>
       <c r="H18" t="n">
@@ -7722,7 +9173,7 @@
       <c r="F19" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="10" t="n">
+      <c r="G19" s="12" t="n">
         <v>0.1792</v>
       </c>
       <c r="H19" t="n">
@@ -7754,7 +9205,7 @@
       <c r="F20" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="10" t="n">
+      <c r="G20" s="12" t="n">
         <v>0.1303</v>
       </c>
       <c r="H20" t="n">
@@ -7786,7 +9237,7 @@
       <c r="F21" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="10" t="n">
+      <c r="G21" s="12" t="n">
         <v>0.1303</v>
       </c>
       <c r="H21" t="n">
@@ -7818,7 +9269,7 @@
       <c r="F22" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="10" t="n">
+      <c r="G22" s="12" t="n">
         <v>0.0697</v>
       </c>
       <c r="H22" t="n">
@@ -7850,7 +9301,7 @@
       <c r="F23" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="10" t="n">
+      <c r="G23" s="12" t="n">
         <v>0.06510000000000001</v>
       </c>
       <c r="H23" t="n">
@@ -7882,7 +9333,7 @@
       <c r="F24" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="10" t="n">
+      <c r="G24" s="12" t="n">
         <v>0.0195</v>
       </c>
       <c r="H24" t="n">
@@ -7914,7 +9365,7 @@
       <c r="F25" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="10" t="n">
+      <c r="G25" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="n">
@@ -7946,7 +9397,7 @@
       <c r="F26" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="10" t="n">
+      <c r="G26" s="12" t="n">
         <v>0.646</v>
       </c>
       <c r="H26" t="n">
@@ -7978,7 +9429,7 @@
       <c r="F27" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="10" t="n">
+      <c r="G27" s="12" t="n">
         <v>0.354</v>
       </c>
       <c r="H27" t="n">
@@ -8010,7 +9461,7 @@
       <c r="F28" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="10" t="n">
+      <c r="G28" s="12" t="n">
         <v>0.6258</v>
       </c>
       <c r="H28" t="n">
@@ -8042,7 +9493,7 @@
       <c r="F29" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="10" t="n">
+      <c r="G29" s="12" t="n">
         <v>0.3742</v>
       </c>
       <c r="H29" t="n">
@@ -8074,7 +9525,7 @@
       <c r="F30" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="10" t="n">
+      <c r="G30" s="12" t="n">
         <v>0.7058</v>
       </c>
       <c r="H30" t="n">
@@ -8106,7 +9557,7 @@
       <c r="F31" t="n">
         <v>1</v>
       </c>
-      <c r="G31" s="10" t="n">
+      <c r="G31" s="12" t="n">
         <v>0.2657</v>
       </c>
       <c r="H31" t="n">
@@ -8138,7 +9589,7 @@
       <c r="F32" t="n">
         <v>1</v>
       </c>
-      <c r="G32" s="10" t="n">
+      <c r="G32" s="12" t="n">
         <v>0.0285</v>
       </c>
       <c r="H32" t="n">
@@ -8170,7 +9621,7 @@
       <c r="F33" t="n">
         <v>1</v>
       </c>
-      <c r="G33" s="10" t="n">
+      <c r="G33" s="12" t="n">
         <v>0.6328</v>
       </c>
       <c r="H33" t="n">
@@ -8202,7 +9653,7 @@
       <c r="F34" t="n">
         <v>1</v>
       </c>
-      <c r="G34" s="10" t="n">
+      <c r="G34" s="12" t="n">
         <v>0.3672</v>
       </c>
       <c r="H34" t="n">
@@ -8234,7 +9685,7 @@
       <c r="F35" t="n">
         <v>1</v>
       </c>
-      <c r="G35" s="10" t="n">
+      <c r="G35" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H35" t="n">
@@ -8266,7 +9717,7 @@
       <c r="F36" t="n">
         <v>1</v>
       </c>
-      <c r="G36" s="10" t="n">
+      <c r="G36" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H36" t="n">
@@ -8298,7 +9749,7 @@
       <c r="F37" t="n">
         <v>1</v>
       </c>
-      <c r="G37" s="10" t="n">
+      <c r="G37" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H37" t="n">
@@ -8330,7 +9781,7 @@
       <c r="F38" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="10" t="n">
+      <c r="G38" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H38" t="n">
@@ -8362,7 +9813,7 @@
       <c r="F39" t="n">
         <v>1</v>
       </c>
-      <c r="G39" s="10" t="n">
+      <c r="G39" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H39" t="n">
@@ -8394,7 +9845,7 @@
       <c r="F40" t="n">
         <v>1</v>
       </c>
-      <c r="G40" s="10" t="n">
+      <c r="G40" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H40" t="n">
@@ -8426,7 +9877,7 @@
       <c r="F41" t="n">
         <v>1</v>
       </c>
-      <c r="G41" s="10" t="n">
+      <c r="G41" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H41" t="n">
@@ -8458,7 +9909,7 @@
       <c r="F42" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="10" t="n">
+      <c r="G42" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H42" t="n">
@@ -8471,7 +9922,6 @@
           <t>Rückerstattungen</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
           <t>+41790000000 MAX MUSTER</t>
@@ -8486,7 +9936,7 @@
       <c r="F43" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="10" t="n">
+      <c r="G43" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H43" t="n">
@@ -8499,7 +9949,6 @@
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>FIKTIVE DIGITAL GMBH</t>
@@ -8514,7 +9963,7 @@
       <c r="F44" t="n">
         <v>1</v>
       </c>
-      <c r="G44" s="10" t="n">
+      <c r="G44" s="12" t="n">
         <v>-3.2249</v>
       </c>
       <c r="H44" t="n">
@@ -8527,7 +9976,6 @@
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>FIKTIVE POST AG</t>
@@ -8542,7 +9990,7 @@
       <c r="F45" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="10" t="n">
+      <c r="G45" s="12" t="n">
         <v>-1.1962</v>
       </c>
       <c r="H45" t="n">
@@ -8555,7 +10003,6 @@
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
           <t>UNMATCHED TEST STORE</t>
@@ -8570,7 +10017,7 @@
       <c r="F46" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="10" t="n">
+      <c r="G46" s="12" t="n">
         <v>-1.1866</v>
       </c>
       <c r="H46" t="n">
@@ -8583,7 +10030,6 @@
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
           <t>FIKTIVER FAHRSCHEIN BERLIN DEUTSCHLAND</t>
@@ -8598,7 +10044,7 @@
       <c r="F47" t="n">
         <v>1</v>
       </c>
-      <c r="G47" s="10" t="n">
+      <c r="G47" s="12" t="n">
         <v>1.8325</v>
       </c>
       <c r="H47" t="n">
@@ -8611,7 +10057,6 @@
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>FIKTIVER SCHUHLADEN BIEL</t>
@@ -8626,7 +10071,7 @@
       <c r="F48" t="n">
         <v>1</v>
       </c>
-      <c r="G48" s="10" t="n">
+      <c r="G48" s="12" t="n">
         <v>4.7751</v>
       </c>
       <c r="H48" t="n">
@@ -8658,7 +10103,7 @@
       <c r="F49" t="n">
         <v>1</v>
       </c>
-      <c r="G49" s="10" t="n">
+      <c r="G49" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H49" t="n">
@@ -8690,7 +10135,7 @@
       <c r="F50" t="n">
         <v>1</v>
       </c>
-      <c r="G50" s="10" t="n">
+      <c r="G50" s="12" t="n">
         <v>0.06560000000000001</v>
       </c>
       <c r="H50" t="n">
@@ -8722,7 +10167,7 @@
       <c r="F51" t="n">
         <v>1</v>
       </c>
-      <c r="G51" s="10" t="n">
+      <c r="G51" s="12" t="n">
         <v>0.9344</v>
       </c>
       <c r="H51" t="n">

--- a/data/example/output/dataset.analysis.xlsx
+++ b/data/example/output/dataset.analysis.xlsx
@@ -15,8 +15,8 @@
     <sheet name="Top Payees" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Transactions'!$A$1:$N$87</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Top Payees'!$A$1:$H$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Transactions'!$A$1:$N$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Top Payees'!$A$1:$H$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1113,11 +1113,11 @@
         </is>
       </c>
       <c r="B17" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$D$2:$D$87, "Income") + SUMIFS(Transactions!$J$2:$J$87, Transactions!$D$2:$D$87, "Expense") + SUMIFS(Transactions!$J$2:$J$87, Transactions!$D$2:$D$87, "Refund") + SUMIFS(Transactions!$J$2:$J$87, Transactions!$D$2:$D$87, "Transfer")</f>
+        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$D$2:$D$90, "Income") + SUMIFS(Transactions!$J$2:$J$90, Transactions!$D$2:$D$90, "Expense") + SUMIFS(Transactions!$J$2:$J$90, Transactions!$D$2:$D$90, "Refund") + SUMIFS(Transactions!$J$2:$J$90, Transactions!$D$2:$D$90, "Transfer")</f>
         <v/>
       </c>
       <c r="C17" s="9">
-        <f>SUMIFS(Transactions!$K$2:$K$87, Transactions!$D$2:$D$87, "Income") + SUMIFS(Transactions!$K$2:$K$87, Transactions!$D$2:$D$87, "Expense") + SUMIFS(Transactions!$K$2:$K$87, Transactions!$D$2:$D$87, "Refund") + SUMIFS(Transactions!$K$2:$K$87, Transactions!$D$2:$D$87, "Transfer")</f>
+        <f>SUMIFS(Transactions!$K$2:$K$90, Transactions!$D$2:$D$90, "Income") + SUMIFS(Transactions!$K$2:$K$90, Transactions!$D$2:$D$90, "Expense") + SUMIFS(Transactions!$K$2:$K$90, Transactions!$D$2:$D$90, "Refund") + SUMIFS(Transactions!$K$2:$K$90, Transactions!$D$2:$D$90, "Transfer")</f>
         <v/>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="B10" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$D$2:$D$87, "Income") - SUMIFS(Transactions!$K$2:$K$87, Transactions!$D$2:$D$87, "Income")</f>
+        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$D$2:$D$90, "Income") - SUMIFS(Transactions!$K$2:$K$90, Transactions!$D$2:$D$90, "Income")</f>
         <v/>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>7215.02</v>
+        <v>7265.12</v>
       </c>
     </row>
     <row r="31">
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1556.79</v>
+        <v>1482.19</v>
       </c>
     </row>
     <row r="32">
@@ -1282,21 +1282,21 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Finanzen</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>173.5</v>
+        <v>193</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Finanzen</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>168.5</v>
+        <v>173.5</v>
       </c>
     </row>
     <row r="35">
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="B37" s="9">
-        <f>SUMIFS(Transactions!$K$2:$K$87, Transactions!$D$2:$D$87, "Expense") - SUMIFS(Transactions!$J$2:$J$87, Transactions!$D$2:$D$87, "Expense")</f>
+        <f>SUMIFS(Transactions!$K$2:$K$90, Transactions!$D$2:$D$90, "Expense") - SUMIFS(Transactions!$J$2:$J$90, Transactions!$D$2:$D$90, "Expense")</f>
         <v/>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="B56" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$D$2:$D$87, "Refund") - SUMIFS(Transactions!$K$2:$K$87, Transactions!$D$2:$D$87, "Refund")</f>
+        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$D$2:$D$90, "Refund") - SUMIFS(Transactions!$K$2:$K$90, Transactions!$D$2:$D$90, "Refund")</f>
         <v/>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1512,10 +1512,10 @@
         <v>0</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1787.9</v>
+        <v>1819.1</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>-1787.9</v>
+        <v>-1819.1</v>
       </c>
     </row>
     <row r="10">
@@ -1528,10 +1528,10 @@
         <v>0</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>388.75</v>
+        <v>333.05</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>-388.75</v>
+        <v>-333.05</v>
       </c>
     </row>
     <row r="11">
@@ -1553,639 +1553,655 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>19</v>
+        <v>24.5</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>-19</v>
+        <v>-24.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-19</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Rückerstattungen</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="B14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B15" s="7" t="n">
         <v>4201</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C15" s="7" t="n">
         <v>2222.35</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D15" s="7" t="n">
         <v>1978.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Check (Transactions)</t>
-        </is>
-      </c>
-      <c r="B15" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-01", Transactions!$D$2:$D$87, "&lt;&gt;Transfer")</f>
-        <v/>
-      </c>
-      <c r="C15" s="9">
-        <f>SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-01", Transactions!$D$2:$D$87, "&lt;&gt;Transfer")</f>
-        <v/>
-      </c>
-      <c r="D15" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-01", Transactions!$D$2:$D$87, "&lt;&gt;Transfer") - SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-01", Transactions!$D$2:$D$87, "&lt;&gt;Transfer")</f>
-        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
+          <t>Check (Transactions)</t>
+        </is>
+      </c>
+      <c r="B16" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-01", Transactions!$D$2:$D$90, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+      <c r="C16" s="9">
+        <f>SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-01", Transactions!$D$2:$D$90, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+      <c r="D16" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-01", Transactions!$D$2:$D$90, "&lt;&gt;Transfer") - SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-01", Transactions!$D$2:$D$90, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
           <t>Difference</t>
         </is>
       </c>
-      <c r="B16" s="9">
-        <f>B15-B14</f>
+      <c r="B17" s="9">
+        <f>B16-B15</f>
         <v/>
       </c>
-      <c r="C16" s="9">
-        <f>C15-C14</f>
+      <c r="C17" s="9">
+        <f>C16-C15</f>
         <v/>
       </c>
-      <c r="D16" s="9">
-        <f>D15-D14</f>
+      <c r="D17" s="9">
+        <f>D16-D15</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>February 2025</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Credit in CHF</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Debit in CHF</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Net in CHF</t>
         </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Einkommen</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>4200</v>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>4200</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>1774</v>
+        <v>0</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>-1774</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>434.7</v>
+        <v>1774</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>-434.7</v>
+        <v>-1774</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>434.7</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>-434.7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Freizeit</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="5" t="n">
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D25" s="5" t="n">
+      <c r="D26" s="5" t="n">
         <v>-3</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n">
+      <c r="B27" s="7" t="n">
         <v>4200</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C27" s="7" t="n">
         <v>2211.7</v>
       </c>
-      <c r="D26" s="7" t="n">
+      <c r="D27" s="7" t="n">
         <v>1988.3</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>Check (Transactions)</t>
-        </is>
-      </c>
-      <c r="B27" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-02", Transactions!$D$2:$D$87, "&lt;&gt;Transfer")</f>
-        <v/>
-      </c>
-      <c r="C27" s="9">
-        <f>SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-02", Transactions!$D$2:$D$87, "&lt;&gt;Transfer")</f>
-        <v/>
-      </c>
-      <c r="D27" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-02", Transactions!$D$2:$D$87, "&lt;&gt;Transfer") - SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-02", Transactions!$D$2:$D$87, "&lt;&gt;Transfer")</f>
-        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
+          <t>Check (Transactions)</t>
+        </is>
+      </c>
+      <c r="B28" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-02", Transactions!$D$2:$D$90, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+      <c r="C28" s="9">
+        <f>SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-02", Transactions!$D$2:$D$90, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+      <c r="D28" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-02", Transactions!$D$2:$D$90, "&lt;&gt;Transfer") - SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-02", Transactions!$D$2:$D$90, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
           <t>Difference</t>
         </is>
       </c>
-      <c r="B28" s="9">
-        <f>B27-B26</f>
+      <c r="B29" s="9">
+        <f>B28-B27</f>
         <v/>
       </c>
-      <c r="C28" s="9">
-        <f>C27-C26</f>
+      <c r="C29" s="9">
+        <f>C28-C27</f>
         <v/>
       </c>
-      <c r="D28" s="9">
-        <f>D27-D26</f>
+      <c r="D29" s="9">
+        <f>D28-D27</f>
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>March 2025</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Credit in CHF</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>Debit in CHF</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>Net in CHF</t>
         </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Einkommen</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="n">
-        <v>5700</v>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>5700</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1787.95</v>
+        <v>5700</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>418.55</v>
+        <v>0</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>1369.4</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>0</v>
+        <v>1787.95</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>1879.12</v>
+        <v>418.55</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>-1879.12</v>
+        <v>1369.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>371.69</v>
+        <v>1898.02</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>-371.69</v>
+        <v>-1898.02</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>165.5</v>
+        <v>352.79</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>-165.5</v>
+        <v>-352.79</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mobilität</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>96.90000000000001</v>
+        <v>165.5</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>-96.90000000000001</v>
+        <v>-165.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Mobilität</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>12.4</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>-12.4</v>
+        <v>-96.90000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>-12.4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Finanzen</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="5" t="n">
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D41" s="5" t="n">
+      <c r="D42" s="5" t="n">
         <v>-5</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B42" s="7" t="n">
+      <c r="B43" s="7" t="n">
         <v>7487.95</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C43" s="7" t="n">
         <v>2949.16</v>
       </c>
-      <c r="D42" s="7" t="n">
+      <c r="D43" s="7" t="n">
         <v>4538.79</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>Check (Transactions)</t>
-        </is>
-      </c>
-      <c r="B43" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-03", Transactions!$D$2:$D$87, "&lt;&gt;Transfer")</f>
-        <v/>
-      </c>
-      <c r="C43" s="9">
-        <f>SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-03", Transactions!$D$2:$D$87, "&lt;&gt;Transfer")</f>
-        <v/>
-      </c>
-      <c r="D43" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-03", Transactions!$D$2:$D$87, "&lt;&gt;Transfer") - SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-03", Transactions!$D$2:$D$87, "&lt;&gt;Transfer")</f>
-        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
+          <t>Check (Transactions)</t>
+        </is>
+      </c>
+      <c r="B44" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-03", Transactions!$D$2:$D$90, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+      <c r="C44" s="9">
+        <f>SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-03", Transactions!$D$2:$D$90, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+      <c r="D44" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-03", Transactions!$D$2:$D$90, "&lt;&gt;Transfer") - SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-03", Transactions!$D$2:$D$90, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
           <t>Difference</t>
         </is>
       </c>
-      <c r="B44" s="9">
-        <f>B43-B42</f>
+      <c r="B45" s="9">
+        <f>B44-B43</f>
         <v/>
       </c>
-      <c r="C44" s="9">
-        <f>C43-C42</f>
+      <c r="C45" s="9">
+        <f>C44-C43</f>
         <v/>
       </c>
-      <c r="D44" s="9">
-        <f>D43-D42</f>
+      <c r="D45" s="9">
+        <f>D44-D43</f>
         <v/>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>April 2025</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>Credit in CHF</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>Debit in CHF</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>Net in CHF</t>
         </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Einkommen</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="n">
-        <v>4200</v>
-      </c>
-      <c r="C50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="5" t="n">
-        <v>4200</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1774</v>
+        <v>0</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>-1774</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>361.65</v>
+        <v>1774</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>-361.65</v>
+        <v>-1774</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Finanzen</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B53" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>168.5</v>
+        <v>361.65</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>-168.5</v>
+        <v>-361.65</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Finanzen</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>0</v>
+        <v>168.5</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>135</v>
+        <v>-168.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>69.05</v>
+        <v>135</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>46.2</v>
+        <v>0</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>22.85</v>
+        <v>135</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>22.85</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>Freizeit</t>
         </is>
       </c>
-      <c r="B56" s="5" t="n">
+      <c r="B57" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="C56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="5" t="n">
+      <c r="C57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="5" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B57" s="7" t="n">
+      <c r="B58" s="7" t="n">
         <v>4504.05</v>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C58" s="7" t="n">
         <v>2350.35</v>
       </c>
-      <c r="D57" s="7" t="n">
+      <c r="D58" s="7" t="n">
         <v>2153.7</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>Check (Transactions)</t>
-        </is>
-      </c>
-      <c r="B58" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-04", Transactions!$D$2:$D$87, "&lt;&gt;Transfer")</f>
-        <v/>
-      </c>
-      <c r="C58" s="9">
-        <f>SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-04", Transactions!$D$2:$D$87, "&lt;&gt;Transfer")</f>
-        <v/>
-      </c>
-      <c r="D58" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-04", Transactions!$D$2:$D$87, "&lt;&gt;Transfer") - SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-04", Transactions!$D$2:$D$87, "&lt;&gt;Transfer")</f>
-        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
+          <t>Check (Transactions)</t>
+        </is>
+      </c>
+      <c r="B59" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-04", Transactions!$D$2:$D$90, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+      <c r="C59" s="9">
+        <f>SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-04", Transactions!$D$2:$D$90, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+      <c r="D59" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-04", Transactions!$D$2:$D$90, "&lt;&gt;Transfer") - SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-04", Transactions!$D$2:$D$90, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
           <t>Difference</t>
         </is>
       </c>
-      <c r="B59" s="9">
-        <f>B58-B57</f>
+      <c r="B60" s="9">
+        <f>B59-B58</f>
         <v/>
       </c>
-      <c r="C59" s="9">
-        <f>C58-C57</f>
+      <c r="C60" s="9">
+        <f>C59-C58</f>
         <v/>
       </c>
-      <c r="D59" s="9">
-        <f>D58-D57</f>
+      <c r="D60" s="9">
+        <f>D59-D58</f>
         <v/>
       </c>
     </row>
@@ -2200,7 +2216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2273,10 +2289,10 @@
         <v>0</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>388.75</v>
+        <v>333.05</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-388.75</v>
+        <v>-333.05</v>
       </c>
     </row>
     <row r="9">
@@ -2303,64 +2319,64 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Familie</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>19</v>
+        <v>24.5</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-19</v>
+        <v>-24.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mobilität</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Privater Verkehr</t>
+          <t>Familie</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>26.7</v>
+        <v>19</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-26.7</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Mobilität</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Miete und Hypothek</t>
+          <t>Privater Verkehr</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1774</v>
+        <v>26.7</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-1774</v>
+        <v>-26.7</v>
       </c>
     </row>
     <row r="13">
@@ -2371,298 +2387,298 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>Miete und Hypothek</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1774</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-1774</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>Haushalt</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>-13.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="C14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-45.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C15" s="7" t="n">
         <v>4200</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D15" s="7" t="n">
         <v>2222.35</v>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="E15" s="7" t="n">
         <v>1977.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Check (Transactions)</t>
-        </is>
-      </c>
-      <c r="C15" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-01", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;")</f>
-        <v/>
-      </c>
-      <c r="D15" s="9">
-        <f>SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-01", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;")</f>
-        <v/>
-      </c>
-      <c r="E15" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-01", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;") - SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-01", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;")</f>
-        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
+          <t>Check (Transactions)</t>
+        </is>
+      </c>
+      <c r="C16" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-01", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D16" s="9">
+        <f>SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-01", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="E16" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-01", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;") - SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-01", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
           <t>Difference</t>
         </is>
       </c>
-      <c r="C16" s="9">
-        <f>C15-C14</f>
+      <c r="C17" s="9">
+        <f>C16-C15</f>
         <v/>
       </c>
-      <c r="D16" s="9">
-        <f>D15-D14</f>
+      <c r="D17" s="9">
+        <f>D16-D15</f>
         <v/>
       </c>
-      <c r="E16" s="9">
-        <f>E15-E14</f>
+      <c r="E17" s="9">
+        <f>E16-E15</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>February 2025</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Subcategory</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Credit in CHF</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Debit in CHF</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Net in CHF</t>
         </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Einkaufen</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Supermärkte</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>434.7</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>-434.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Einkommen</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lohn</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0</v>
+        <v>434.7</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>4200</v>
+        <v>-434.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Lohn</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>-3</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Gastronomie</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Wohnen</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Miete und Hypothek</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="5" t="n">
+      <c r="C26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="5" t="n">
         <v>1774</v>
       </c>
-      <c r="E25" s="5" t="n">
+      <c r="E26" s="5" t="n">
         <v>-1774</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C27" s="7" t="n">
         <v>4200</v>
       </c>
-      <c r="D26" s="7" t="n">
+      <c r="D27" s="7" t="n">
         <v>2211.7</v>
       </c>
-      <c r="E26" s="7" t="n">
+      <c r="E27" s="7" t="n">
         <v>1988.3</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>Check (Transactions)</t>
-        </is>
-      </c>
-      <c r="C27" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-02", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;")</f>
-        <v/>
-      </c>
-      <c r="D27" s="9">
-        <f>SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-02", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;")</f>
-        <v/>
-      </c>
-      <c r="E27" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-02", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;") - SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-02", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;")</f>
-        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
+          <t>Check (Transactions)</t>
+        </is>
+      </c>
+      <c r="C28" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-02", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D28" s="9">
+        <f>SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-02", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="E28" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-02", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;") - SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-02", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
           <t>Difference</t>
         </is>
       </c>
-      <c r="C28" s="9">
-        <f>C27-C26</f>
+      <c r="C29" s="9">
+        <f>C28-C27</f>
         <v/>
       </c>
-      <c r="D28" s="9">
-        <f>D27-D26</f>
+      <c r="D29" s="9">
+        <f>D28-D27</f>
         <v/>
       </c>
-      <c r="E28" s="9">
-        <f>E27-E26</f>
+      <c r="E29" s="9">
+        <f>E28-E27</f>
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>March 2025</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Subcategory</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>Credit in CHF</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>Debit in CHF</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>Net in CHF</t>
         </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Einkaufen</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Supermärkte</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>189.75</v>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>-189.75</v>
       </c>
     </row>
     <row r="35">
@@ -2673,17 +2689,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Detail-Lebensmittel</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>167.29</v>
+        <v>170.85</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>-167.29</v>
+        <v>-170.85</v>
       </c>
     </row>
     <row r="36">
@@ -2694,80 +2710,80 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sonstiges Einkaufen</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>14.65</v>
+        <v>167.29</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>-14.65</v>
+        <v>-167.29</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Einkommen</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lohn</t>
+          <t>Sonstiges Einkaufen</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>5700</v>
+        <v>0</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>0</v>
+        <v>14.65</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>5700</v>
+        <v>-14.65</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Finanzen</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>Lohn</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>-5</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Finanzen</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Fees</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>150.5</v>
+        <v>5</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>-150.5</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="40">
@@ -2778,38 +2794,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kultur</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>15</v>
+        <v>150.5</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>-15</v>
+        <v>-150.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Krankenkasse</t>
+          <t>Kultur</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1787.95</v>
+        <v>0</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>77.45</v>
+        <v>15</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>1710.5</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="42">
@@ -2820,17 +2836,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Familie</t>
+          <t>Krankenkasse</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>0</v>
+        <v>1787.95</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>200</v>
+        <v>77.45</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>-200</v>
+        <v>1710.5</v>
       </c>
     </row>
     <row r="43">
@@ -2841,17 +2857,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Styling und Wellness</t>
+          <t>Familie</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>79.90000000000001</v>
+        <v>200</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>-79.90000000000001</v>
+        <v>-200</v>
       </c>
     </row>
     <row r="44">
@@ -2862,17 +2878,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sonstiges Leben</t>
+          <t>Styling und Wellness</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>36.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>-36.8</v>
+        <v>-79.90000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -2883,59 +2899,59 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Gesundheit</t>
+          <t>Sonstiges Leben</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>24.4</v>
+        <v>36.8</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>-24.4</v>
+        <v>-36.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Mobilität</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Öffentlicher Verkehr</t>
+          <t>Gesundheit</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>96.90000000000001</v>
+        <v>24.4</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>-96.90000000000001</v>
+        <v>-24.4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Mobilität</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Miete und Hypothek</t>
+          <t>Öffentlicher Verkehr</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>1774</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>-1774</v>
+        <v>-96.90000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2946,17 +2962,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kommunikation</t>
+          <t>Miete und Hypothek</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>70.27</v>
+        <v>1774</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>-70.27</v>
+        <v>-1774</v>
       </c>
     </row>
     <row r="49">
@@ -2967,17 +2983,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Haushalt</t>
+          <t>Kommunikation</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>23.95</v>
+        <v>70.27</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>-23.95</v>
+        <v>-70.27</v>
       </c>
     </row>
     <row r="50">
@@ -2988,168 +3004,168 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>Haushalt</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>42.85</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>-42.85</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>Handwerk und Garten</t>
         </is>
       </c>
-      <c r="C50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="5" t="n">
+      <c r="C51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="5" t="n">
         <v>10.9</v>
       </c>
-      <c r="E50" s="5" t="n">
+      <c r="E51" s="5" t="n">
         <v>-10.9</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C51" s="7" t="n">
+      <c r="C52" s="7" t="n">
         <v>7487.95</v>
       </c>
-      <c r="D51" s="7" t="n">
+      <c r="D52" s="7" t="n">
         <v>2936.76</v>
       </c>
-      <c r="E51" s="7" t="n">
+      <c r="E52" s="7" t="n">
         <v>4551.19</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>Check (Transactions)</t>
-        </is>
-      </c>
-      <c r="C52" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-03", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;")</f>
-        <v/>
-      </c>
-      <c r="D52" s="9">
-        <f>SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-03", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;")</f>
-        <v/>
-      </c>
-      <c r="E52" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-03", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;") - SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-03", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;")</f>
-        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
+          <t>Check (Transactions)</t>
+        </is>
+      </c>
+      <c r="C53" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-03", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D53" s="9">
+        <f>SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-03", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="E53" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-03", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;") - SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-03", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
           <t>Difference</t>
         </is>
       </c>
-      <c r="C53" s="9">
-        <f>C52-C51</f>
+      <c r="C54" s="9">
+        <f>C53-C52</f>
         <v/>
       </c>
-      <c r="D53" s="9">
-        <f>D52-D51</f>
+      <c r="D54" s="9">
+        <f>D53-D52</f>
         <v/>
       </c>
-      <c r="E53" s="9">
-        <f>E52-E51</f>
+      <c r="E54" s="9">
+        <f>E53-E52</f>
         <v/>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>April 2025</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>Subcategory</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>Credit in CHF</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>Debit in CHF</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="E59" s="4" t="inlineStr">
         <is>
           <t>Net in CHF</t>
         </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Einkaufen</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Supermärkte</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="5" t="n">
-        <v>361.65</v>
-      </c>
-      <c r="E59" s="5" t="n">
-        <v>-361.65</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Einkommen</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Lohn</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="C60" s="5" t="n">
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>0</v>
+        <v>361.65</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>4200</v>
+        <v>-361.65</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Finanzen</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bargeldbezug</t>
+          <t>Lohn</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>143.5</v>
+        <v>0</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>-143.5</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="62">
@@ -3160,59 +3176,59 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Spenden</t>
+          <t>Bargeldbezug</t>
         </is>
       </c>
       <c r="C62" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>25</v>
+        <v>143.5</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>-25</v>
+        <v>-143.5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Finanzen</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Reisen und Erleben</t>
+          <t>Spenden</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>100</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Krankenkasse</t>
+          <t>Reisen und Erleben</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D64" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="65">
@@ -3223,91 +3239,112 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Familie</t>
+          <t>Krankenkasse</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="D65" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>15</v>
+        <v>120</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Familie</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>Wohnen</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Miete und Hypothek</t>
         </is>
       </c>
-      <c r="C66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" s="5" t="n">
+      <c r="C67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="5" t="n">
         <v>1774</v>
       </c>
-      <c r="E66" s="5" t="n">
+      <c r="E67" s="5" t="n">
         <v>-1774</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C67" s="7" t="n">
+      <c r="C68" s="7" t="n">
         <v>4435</v>
       </c>
-      <c r="D67" s="7" t="n">
+      <c r="D68" s="7" t="n">
         <v>2304.15</v>
       </c>
-      <c r="E67" s="7" t="n">
+      <c r="E68" s="7" t="n">
         <v>2130.85</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="8" t="inlineStr">
-        <is>
-          <t>Check (Transactions)</t>
-        </is>
-      </c>
-      <c r="C68" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-04", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;")</f>
-        <v/>
-      </c>
-      <c r="D68" s="9">
-        <f>SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-04", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;")</f>
-        <v/>
-      </c>
-      <c r="E68" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$87, Transactions!$C$2:$C$87, "2025-04", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;") - SUMIFS(Transactions!$K$2:$K$87, Transactions!$C$2:$C$87, "2025-04", Transactions!$D$2:$D$87, "&lt;&gt;Transfer", Transactions!$F$2:$F$87, "&lt;&gt;")</f>
-        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
+          <t>Check (Transactions)</t>
+        </is>
+      </c>
+      <c r="C69" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-04", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D69" s="9">
+        <f>SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-04", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="E69" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-04", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;") - SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-04", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
           <t>Difference</t>
         </is>
       </c>
-      <c r="C69" s="9">
-        <f>C68-C67</f>
+      <c r="C70" s="9">
+        <f>C69-C68</f>
         <v/>
       </c>
-      <c r="D69" s="9">
-        <f>D68-D67</f>
+      <c r="D70" s="9">
+        <f>D69-D68</f>
         <v/>
       </c>
-      <c r="E69" s="9">
-        <f>E68-E67</f>
+      <c r="E70" s="9">
+        <f>E69-E68</f>
         <v/>
       </c>
     </row>
@@ -3322,7 +3359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N87"/>
+  <dimension ref="A1:N90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3662,7 +3699,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TX-000076</t>
+          <t>TX-000076.1</t>
         </is>
       </c>
       <c r="B6" s="11" t="n">
@@ -3680,17 +3717,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Supermärkte</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Einkaufen / Supermärkte</t>
+          <t>Freizeit / Gastronomie</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -3702,10 +3739,10 @@
         <v>0</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>132.85</v>
+        <v>24.5</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>132.85</v>
+        <v>24.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -3721,11 +3758,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TX-000002</t>
+          <t>TX-000076.2</t>
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>45676</v>
+        <v>45675</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3754,26 +3791,21 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ONLINE HAUSHALT AG</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>PAYMENT ID 250119000000000000 BESTELLNUMMER DP-P-00000000</t>
+          <t>COOP-5510 RIVERSIDE REST.</t>
         </is>
       </c>
       <c r="J7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>13.9</v>
+        <v>31.2</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>13.9</v>
+        <v>31.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>home_3</t>
+          <t>supermarket_1</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -3785,11 +3817,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TX-000001</t>
+          <t>TX-000076.3</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>45682</v>
+        <v>45675</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3798,41 +3830,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Refund</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rückerstattungen</t>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rückerstattungen</t>
+          <t>Einkaufen / Supermärkte</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>+41790000000 MAX MUSTER</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>MITTEILUNGEN: TEST</t>
+          <t>COOP-5510 RIVERSIDE REST.</t>
         </is>
       </c>
       <c r="J8" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>-1</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>refund_1</t>
+          <t>supermarket_1</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -3844,11 +3876,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TX-000070</t>
+          <t>TX-000002</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>45682</v>
+        <v>45676</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3857,46 +3889,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Einkommen</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lohn</t>
+          <t>Haushalt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Einkommen / Lohn</t>
+          <t>Wohnen / Haushalt</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
+          <t>ONLINE HAUSHALT AG</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SALAER JANUAR 2025 | SALA00000000000000000000000000000001 9988776655/1XXXX 250125CH0EXMPL01</t>
+          <t>PAYMENT ID 250119000000000000 BESTELLNUMMER DP-P-00000000</t>
         </is>
       </c>
       <c r="J9" s="5" t="n">
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0</v>
+        <v>13.9</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>-4200</v>
+        <v>13.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>income_1</t>
+          <t>home_3</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -3908,11 +3940,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TX-000075</t>
+          <t>TX-000001</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>45685</v>
+        <v>45682</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3921,41 +3953,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Refund</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Supermärkte</t>
+          <t>Rückerstattungen</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Einkaufen / Supermärkte</t>
+          <t>Rückerstattungen</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>MIGROS MARKTHALLE (8812)</t>
+          <t>+41790000000 MAX MUSTER</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MITTEILUNGEN: TEST</t>
         </is>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>96.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>96.40000000000001</v>
+        <v>-1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>supermarket_1</t>
+          <t>refund_1</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -3967,11 +3999,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TX-000074</t>
+          <t>TX-000070</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>45688</v>
+        <v>45682</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -3980,46 +4012,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Miete und Hypothek</t>
+          <t>Lohn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Wohnen / Miete und Hypothek</t>
+          <t>Einkommen / Lohn</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>FINANZVERWALTUNG STADT SOLOTHURN</t>
+          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2025/02/01 / 7045128</t>
+          <t>SALAER JANUAR 2025 | SALA00000000000000000000000000000001 9988776655/1XXXX 250125CH0EXMPL01</t>
         </is>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>1774</v>
+        <v>0</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>1774</v>
+        <v>-4200</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>housing_1</t>
+          <t>income_1</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -4031,15 +4063,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TX-000083</t>
+          <t>TX-000075</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>45689</v>
+        <v>45685</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4064,17 +4096,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>MIGROS M RIVERSIDE (7741)</t>
+          <t>MIGROS MARKTHALLE (8812)</t>
         </is>
       </c>
       <c r="J12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>63.75</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>63.75</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4083,22 +4115,22 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>export.202502.categorized.csv</t>
+          <t>export.202501.categorized.csv</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TX-000082</t>
+          <t>TX-000074</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
-        <v>45696</v>
+        <v>45688</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4108,52 +4140,57 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Supermärkte</t>
+          <t>Miete und Hypothek</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Einkaufen / Supermärkte</t>
+          <t>Wohnen / Miete und Hypothek</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>MIGROS MARKTHALLE (8812)</t>
+          <t>FINANZVERWALTUNG STADT SOLOTHURN</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2025/02/01 / 7045128</t>
         </is>
       </c>
       <c r="J13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>127.4</v>
+        <v>1774</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>127.4</v>
+        <v>1774</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>supermarket_1</t>
+          <t>housing_1</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>export.202502.categorized.csv</t>
+          <t>export.202501.categorized.csv</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TX-000081</t>
+          <t>TX-000083</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
-        <v>45702</v>
+        <v>45689</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -4182,17 +4219,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>COOP-5510 RIVERSIDE REST.</t>
+          <t>MIGROS M RIVERSIDE (7741)</t>
         </is>
       </c>
       <c r="J14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>88.95</v>
+        <v>63.75</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>88.95</v>
+        <v>63.75</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4208,11 +4245,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TX-000080</t>
+          <t>TX-000082</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>45710</v>
+        <v>45696</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -4248,10 +4285,10 @@
         <v>0</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>154.6</v>
+        <v>127.4</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>154.6</v>
+        <v>127.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4267,11 +4304,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TX-000071</t>
+          <t>TX-000081</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
-        <v>45713</v>
+        <v>45702</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -4280,46 +4317,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Einkommen</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lohn</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Einkommen / Lohn</t>
+          <t>Einkaufen / Supermärkte</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>SALAER FEBRUAR 2025 | SALA00000000000000000000000000000002 9988776655/1XXXX 250225CH0EXMPL02</t>
+          <t>COOP-5510 RIVERSIDE REST.</t>
         </is>
       </c>
       <c r="J16" s="5" t="n">
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0</v>
+        <v>88.95</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>-4200</v>
+        <v>88.95</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>income_1</t>
+          <t>supermarket_1</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -4331,11 +4363,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TX-000060</t>
+          <t>TX-000080</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
-        <v>45715</v>
+        <v>45710</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -4349,36 +4381,36 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Freizeit / Gastronomie</t>
+          <t>Einkaufen / Supermärkte</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>MUSTER CAFE</t>
+          <t>MIGROS MARKTHALLE (8812)</t>
         </is>
       </c>
       <c r="J17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>3</v>
+        <v>154.6</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>3</v>
+        <v>154.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>gastronomy_6</t>
+          <t>supermarket_1</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -4390,11 +4422,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TX-000079</t>
+          <t>TX-000071</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
-        <v>45716</v>
+        <v>45713</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -4403,46 +4435,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Miete und Hypothek</t>
+          <t>Lohn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Wohnen / Miete und Hypothek</t>
+          <t>Einkommen / Lohn</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>FINANZVERWALTUNG STADT SOLOTHURN</t>
+          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2025/03/01 / 7045128</t>
+          <t>SALAER FEBRUAR 2025 | SALA00000000000000000000000000000002 9988776655/1XXXX 250225CH0EXMPL02</t>
         </is>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>1774</v>
+        <v>0</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>1774</v>
+        <v>-4200</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>housing_1</t>
+          <t>income_1</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -4454,15 +4486,15 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TX-000054</t>
+          <t>TX-000060</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
-        <v>45738</v>
+        <v>45715</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4487,91 +4519,101 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>+41790000000 MAX MUSTER</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>MITTEILUNGEN: ESSEN GESTERN ABEND</t>
+          <t>MUSTER CAFE</t>
         </is>
       </c>
       <c r="J19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>gastronomy_5</t>
+          <t>gastronomy_6</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>export.202503.categorized.csv</t>
+          <t>export.202502.categorized.csv</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TX-000055</t>
+          <t>TX-000079</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
-        <v>45738</v>
+        <v>45716</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Miete und Hypothek</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Wohnen / Miete und Hypothek</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>UNMATCHED TEST STORE</t>
+          <t>FINANZVERWALTUNG STADT SOLOTHURN</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2025/03/01 / 7045128</t>
         </is>
       </c>
       <c r="J20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>12.4</v>
+        <v>1774</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>12.4</v>
+        <v>1774</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>housing_1</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>export.202503.categorized.csv</t>
+          <t>export.202502.categorized.csv</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TX-000051</t>
+          <t>TX-000054</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
-        <v>45739</v>
+        <v>45738</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -4585,36 +4627,41 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Detail-Lebensmittel</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Einkaufen / Detail-Lebensmittel</t>
+          <t>Freizeit / Gastronomie</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>BÄCKEREI HUG</t>
+          <t>+41790000000 MAX MUSTER</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MITTEILUNGEN: ESSEN GESTERN ABEND</t>
         </is>
       </c>
       <c r="J21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>17.3</v>
+        <v>20</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>17.3</v>
+        <v>20</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>grocery_1</t>
+          <t>gastronomy_5</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -4626,54 +4673,44 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TX-000052</t>
+          <t>TX-000055</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
-        <v>45739</v>
+        <v>45738</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wohnen</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Haushalt</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Wohnen / Haushalt</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>MANOR AG - 771 (CENTRA)</t>
+          <t>UNMATCHED TEST STORE</t>
         </is>
       </c>
       <c r="J22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>23.95</v>
+        <v>12.4</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>23.95</v>
+        <v>12.4</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>home_2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -4685,7 +4722,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TX-000053</t>
+          <t>TX-000051</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
@@ -4703,36 +4740,36 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Freizeit / Gastronomie</t>
+          <t>Einkaufen / Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>+41796666222 KEBAB, IMBISS</t>
+          <t>BÄCKEREI HUG</t>
         </is>
       </c>
       <c r="J23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>13.5</v>
+        <v>17.3</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>13.5</v>
+        <v>17.3</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>gastronomy_4</t>
+          <t>grocery_1</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -4744,11 +4781,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TX-000045</t>
+          <t>TX-000052</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
-        <v>45740</v>
+        <v>45739</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -4762,36 +4799,36 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Detail-Lebensmittel</t>
+          <t>Haushalt</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Einkaufen / Detail-Lebensmittel</t>
+          <t>Wohnen / Haushalt</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>WAKARA GMBH</t>
+          <t>MANOR AG - 771 (CENTRA)</t>
         </is>
       </c>
       <c r="J24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>27.6</v>
+        <v>23.95</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>27.6</v>
+        <v>23.95</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>grocery_2</t>
+          <t>home_2</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -4803,11 +4840,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TX-000046</t>
+          <t>TX-000053</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
-        <v>45740</v>
+        <v>45739</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -4821,36 +4858,36 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Styling und Wellness</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leben / Styling und Wellness</t>
+          <t>Freizeit / Gastronomie</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>THE BODY SHOP</t>
+          <t>+41796666222 KEBAB, IMBISS</t>
         </is>
       </c>
       <c r="J25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>4.95</v>
+        <v>13.5</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>4.95</v>
+        <v>13.5</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>wellness_1</t>
+          <t>gastronomy_4</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -4862,7 +4899,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TX-000047</t>
+          <t>TX-000045</t>
         </is>
       </c>
       <c r="B26" s="11" t="n">
@@ -4885,31 +4922,31 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Supermärkte</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Einkaufen / Supermärkte</t>
+          <t>Einkaufen / Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>COOP-5510 RIVERSIDE REST.</t>
+          <t>WAKARA GMBH</t>
         </is>
       </c>
       <c r="J26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>44</v>
+        <v>27.6</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>44</v>
+        <v>27.6</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>supermarket_1</t>
+          <t>grocery_2</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -4921,7 +4958,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TX-000048</t>
+          <t>TX-000046</t>
         </is>
       </c>
       <c r="B27" s="11" t="n">
@@ -4939,36 +4976,36 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Supermärkte</t>
+          <t>Styling und Wellness</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Einkaufen / Supermärkte</t>
+          <t>Leben / Styling und Wellness</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>MIGROS MARKTHALLE (8812)</t>
+          <t>THE BODY SHOP</t>
         </is>
       </c>
       <c r="J27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>53.5</v>
+        <v>4.95</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>53.5</v>
+        <v>4.95</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>supermarket_1</t>
+          <t>wellness_1</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4980,7 +5017,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TX-000049</t>
+          <t>TX-000047</t>
         </is>
       </c>
       <c r="B28" s="11" t="n">
@@ -4998,36 +5035,36 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Freizeit / Gastronomie</t>
+          <t>Einkaufen / Supermärkte</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>MIGROS CITY TAKE AWAY (6624)</t>
+          <t>COOP-5510 RIVERSIDE REST.</t>
         </is>
       </c>
       <c r="J28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>6.8</v>
+        <v>44</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>6.8</v>
+        <v>44</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>gastronomy_1</t>
+          <t>supermarket_1</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -5039,7 +5076,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TX-000050</t>
+          <t>TX-000048.1</t>
         </is>
       </c>
       <c r="B29" s="11" t="n">
@@ -5057,36 +5094,36 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Krankenkasse</t>
+          <t>Haushalt</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leben / Krankenkasse</t>
+          <t>Wohnen / Haushalt</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>MEDICURA PLUS AG GESUNDHEITSWEG 8 4052 BASEL</t>
+          <t>MIGROS MARKTHALLE (8812)</t>
         </is>
       </c>
       <c r="J29" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>77.45</v>
+        <v>18.9</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>77.45</v>
+        <v>18.9</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>health_2</t>
+          <t>supermarket_1</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -5098,11 +5135,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TX-000039</t>
+          <t>TX-000048.2</t>
         </is>
       </c>
       <c r="B30" s="11" t="n">
-        <v>45741</v>
+        <v>45740</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -5121,31 +5158,31 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Detail-Lebensmittel</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Einkaufen / Detail-Lebensmittel</t>
+          <t>Einkaufen / Supermärkte</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>BÄCKEREI HUG</t>
+          <t>MIGROS MARKTHALLE (8812)</t>
         </is>
       </c>
       <c r="J30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>6.1</v>
+        <v>34.6</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>6.1</v>
+        <v>34.6</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>grocery_1</t>
+          <t>supermarket_1</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -5157,11 +5194,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TX-000040</t>
+          <t>TX-000049</t>
         </is>
       </c>
       <c r="B31" s="11" t="n">
-        <v>45741</v>
+        <v>45740</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -5175,36 +5212,36 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Detail-Lebensmittel</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Einkaufen / Detail-Lebensmittel</t>
+          <t>Freizeit / Gastronomie</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>BRANKOVIC BREZELSTUBE</t>
+          <t>MIGROS CITY TAKE AWAY (6624)</t>
         </is>
       </c>
       <c r="J31" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>grocery_1</t>
+          <t>gastronomy_1</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -5216,11 +5253,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TX-000041</t>
+          <t>TX-000050</t>
         </is>
       </c>
       <c r="B32" s="11" t="n">
-        <v>45741</v>
+        <v>45740</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -5234,36 +5271,36 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Supermärkte</t>
+          <t>Krankenkasse</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Einkaufen / Supermärkte</t>
+          <t>Leben / Krankenkasse</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>MIGROS M RIVERSIDE (7741)</t>
+          <t>MEDICURA PLUS AG GESUNDHEITSWEG 8 4052 BASEL</t>
         </is>
       </c>
       <c r="J32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>10.35</v>
+        <v>77.45</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>10.35</v>
+        <v>77.45</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>supermarket_1</t>
+          <t>health_2</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -5275,7 +5312,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TX-000043</t>
+          <t>TX-000039</t>
         </is>
       </c>
       <c r="B33" s="11" t="n">
@@ -5288,46 +5325,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Refund</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Krankenkasse</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leben / Krankenkasse</t>
+          <t>Einkaufen / Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>MEDICURA PLUS AG GESUNDHEITSWEG 8 4052 BASEL</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>LEISTUNGSABRECHNUNG NR.: 700112233445566 VERSICHERTE PERSON 445566 BETRIFFT LEISTUNGEN | MED95CB11F8253446278F81749F26F10588</t>
+          <t>BÄCKEREI HUG</t>
         </is>
       </c>
       <c r="J33" s="5" t="n">
-        <v>1787.95</v>
+        <v>0</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>-1787.95</v>
+        <v>6.1</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>refund_2</t>
+          <t>grocery_1</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5339,7 +5371,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TX-000044</t>
+          <t>TX-000040</t>
         </is>
       </c>
       <c r="B34" s="11" t="n">
@@ -5357,36 +5389,36 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kommunikation</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Wohnen / Kommunikation</t>
+          <t>Einkaufen / Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>CLOUDSERVICE INC SAN</t>
+          <t>BRANKOVIC BREZELSTUBE</t>
         </is>
       </c>
       <c r="J34" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>18.67</v>
+        <v>4.3</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>18.67</v>
+        <v>4.3</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>communication_3</t>
+          <t>grocery_1</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5398,7 +5430,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TX-000058</t>
+          <t>TX-000041</t>
         </is>
       </c>
       <c r="B35" s="11" t="n">
@@ -5411,46 +5443,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Transfer</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Überträge</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Account Transfer</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Überträge / Account Transfer</t>
+          <t>Einkaufen / Supermärkte</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>EIGENES SPARKONTO KONTOUEBERTRAG TRANSFER-20250325</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>EIGENES SPARKONTO KONTOUEBERTRAG TRANSFER-20250325</t>
+          <t>MIGROS M RIVERSIDE (7741)</t>
         </is>
       </c>
       <c r="J35" s="5" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>0</v>
+        <v>10.35</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>-450</v>
+        <v>10.35</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>transfer_1</t>
+          <t>supermarket_1</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5462,7 +5489,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TX-000072</t>
+          <t>TX-000043</t>
         </is>
       </c>
       <c r="B36" s="11" t="n">
@@ -5475,46 +5502,46 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Refund</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Einkommen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lohn</t>
+          <t>Krankenkasse</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Einkommen / Lohn</t>
+          <t>Leben / Krankenkasse</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
+          <t>MEDICURA PLUS AG GESUNDHEITSWEG 8 4052 BASEL</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SALAER BONUS 2024 | SALA00000000000000000000000000000003 9988776655/1XXXX 250325CH0EXMPL03</t>
+          <t>LEISTUNGSABRECHNUNG NR.: 700112233445566 VERSICHERTE PERSON 445566 BETRIFFT LEISTUNGEN | MED95CB11F8253446278F81749F26F10588</t>
         </is>
       </c>
       <c r="J36" s="5" t="n">
-        <v>1500</v>
+        <v>1787.95</v>
       </c>
       <c r="K36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>-1500</v>
+        <v>-1787.95</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>income_1</t>
+          <t>refund_2</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5526,7 +5553,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TX-000073</t>
+          <t>TX-000044</t>
         </is>
       </c>
       <c r="B37" s="11" t="n">
@@ -5539,46 +5566,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Einkommen</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lohn</t>
+          <t>Kommunikation</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Einkommen / Lohn</t>
+          <t>Wohnen / Kommunikation</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>SALAER MAERZ 2025 | SALA80E5ED528784F48B451A4175649C112 9988776655/1XXXX 250325CH7LMNQRTS</t>
+          <t>CLOUDSERVICE INC SAN</t>
         </is>
       </c>
       <c r="J37" s="5" t="n">
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>0</v>
+        <v>18.67</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>-4200</v>
+        <v>18.67</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>income_1</t>
+          <t>communication_3</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5590,11 +5612,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TX-000035</t>
+          <t>TX-000058</t>
         </is>
       </c>
       <c r="B38" s="11" t="n">
-        <v>45742</v>
+        <v>45741</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5603,41 +5625,46 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Transfer</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mobilität</t>
+          <t>Überträge</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Öffentlicher Verkehr</t>
+          <t>Account Transfer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Mobilität / Öffentlicher Verkehr</t>
+          <t>Überträge / Account Transfer</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>TRANSPORTS PUBLICS FRIBOURGEOIS (FAIRTIQ) N/A PAYMENT ID 250326064915818975ZX BESTELLNUMMER</t>
+          <t>EIGENES SPARKONTO KONTOUEBERTRAG TRANSFER-20250325</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>EIGENES SPARKONTO KONTOUEBERTRAG TRANSFER-20250325</t>
         </is>
       </c>
       <c r="J38" s="5" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>62.6</v>
+        <v>0</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>62.6</v>
+        <v>-450</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>transport_1</t>
+          <t>transfer_1</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5649,11 +5676,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TX-000036</t>
+          <t>TX-000072</t>
         </is>
       </c>
       <c r="B39" s="11" t="n">
-        <v>45742</v>
+        <v>45741</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5662,41 +5689,46 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Handwerk und Garten</t>
+          <t>Lohn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Wohnen / Handwerk und Garten</t>
+          <t>Einkommen / Lohn</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>JUMBO-7782 INDUSTRIEPARK</t>
+          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>SALAER BONUS 2024 | SALA00000000000000000000000000000003 9988776655/1XXXX 250325CH0EXMPL03</t>
         </is>
       </c>
       <c r="J39" s="5" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>10.9</v>
+        <v>0</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>10.9</v>
+        <v>-1500</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>home_1</t>
+          <t>income_1</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5708,11 +5740,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TX-000037</t>
+          <t>TX-000073</t>
         </is>
       </c>
       <c r="B40" s="11" t="n">
-        <v>45742</v>
+        <v>45741</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5721,46 +5753,46 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Lohn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Freizeit / Gastronomie</t>
+          <t>Einkommen / Lohn</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>+41796666222 KEBAB, IMBISS</t>
+          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>MITTEILUNGEN: KEBAB</t>
+          <t>SALAER MAERZ 2025 | SALA80E5ED528784F48B451A4175649C112 9988776655/1XXXX 250325CH7LMNQRTS</t>
         </is>
       </c>
       <c r="J40" s="5" t="n">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>14</v>
+        <v>-4200</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>gastronomy_4</t>
+          <t>income_1</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5772,7 +5804,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TX-000038</t>
+          <t>TX-000035</t>
         </is>
       </c>
       <c r="B41" s="11" t="n">
@@ -5790,41 +5822,36 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Mobilität</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Familie</t>
+          <t>Öffentlicher Verkehr</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leben / Familie</t>
+          <t>Mobilität / Öffentlicher Verkehr</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>FAMILIENKASSE MUSTERHAUSEN SENDER REFERENZ: FAMILIENZULAGE</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>90-33445566</t>
+          <t>TRANSPORTS PUBLICS FRIBOURGEOIS (FAIRTIQ) N/A PAYMENT ID 250326064915818975ZX BESTELLNUMMER</t>
         </is>
       </c>
       <c r="J41" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>200</v>
+        <v>62.6</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>200</v>
+        <v>62.6</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>family_1</t>
+          <t>transport_1</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -5836,11 +5863,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TX-000024</t>
+          <t>TX-000036</t>
         </is>
       </c>
       <c r="B42" s="11" t="n">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5859,31 +5886,31 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kommunikation</t>
+          <t>Handwerk und Garten</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Wohnen / Kommunikation</t>
+          <t>Wohnen / Handwerk und Garten</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>APPLE.COM/BILL</t>
+          <t>JUMBO-7782 INDUSTRIEPARK</t>
         </is>
       </c>
       <c r="J42" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>2</v>
+        <v>10.9</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>2</v>
+        <v>10.9</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>communication_2</t>
+          <t>home_1</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -5895,11 +5922,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TX-000025</t>
+          <t>TX-000037</t>
         </is>
       </c>
       <c r="B43" s="11" t="n">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5928,21 +5955,26 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>YOOJI'S ROSENGARTEN</t>
+          <t>+41796666222 KEBAB, IMBISS</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>MITTEILUNGEN: KEBAB</t>
         </is>
       </c>
       <c r="J43" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>6.9</v>
+        <v>14</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>6.9</v>
+        <v>14</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>gastronomy_2</t>
+          <t>gastronomy_4</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5954,11 +5986,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TX-000026</t>
+          <t>TX-000038</t>
         </is>
       </c>
       <c r="B44" s="11" t="n">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5972,36 +6004,41 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Detail-Lebensmittel</t>
+          <t>Familie</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Einkaufen / Detail-Lebensmittel</t>
+          <t>Leben / Familie</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>CONFISERIE SPRÜNGLI AG</t>
+          <t>FAMILIENKASSE MUSTERHAUSEN SENDER REFERENZ: FAMILIENZULAGE</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>90-33445566</t>
         </is>
       </c>
       <c r="J44" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>22.05</v>
+        <v>200</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>22.05</v>
+        <v>200</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>grocery_1</t>
+          <t>family_1</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6013,7 +6050,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TX-000027</t>
+          <t>TX-000024</t>
         </is>
       </c>
       <c r="B45" s="11" t="n">
@@ -6031,36 +6068,36 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Styling und Wellness</t>
+          <t>Kommunikation</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leben / Styling und Wellness</t>
+          <t>Wohnen / Kommunikation</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>THE BODY SHOP</t>
+          <t>APPLE.COM/BILL</t>
         </is>
       </c>
       <c r="J45" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>24.95</v>
+        <v>2</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>24.95</v>
+        <v>2</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>wellness_1</t>
+          <t>communication_2</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6072,7 +6109,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TX-000028</t>
+          <t>TX-000025</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
@@ -6112,10 +6149,10 @@
         <v>0</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>11.9</v>
+        <v>6.9</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>11.9</v>
+        <v>6.9</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -6131,7 +6168,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TX-000029</t>
+          <t>TX-000026</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
@@ -6149,36 +6186,36 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Freizeit / Gastronomie</t>
+          <t>Einkaufen / Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>YOOJI'S ROSENGARTEN</t>
+          <t>CONFISERIE SPRÜNGLI AG</t>
         </is>
       </c>
       <c r="J47" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>43.5</v>
+        <v>22.05</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>43.5</v>
+        <v>22.05</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>gastronomy_2</t>
+          <t>grocery_1</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6190,7 +6227,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TX-000030</t>
+          <t>TX-000027</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
@@ -6208,36 +6245,36 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Styling und Wellness</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Freizeit / Gastronomie</t>
+          <t>Leben / Styling und Wellness</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>COFFEE AND PLANTS</t>
+          <t>THE BODY SHOP</t>
         </is>
       </c>
       <c r="J48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>10</v>
+        <v>24.95</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>10</v>
+        <v>24.95</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>gastronomy_3</t>
+          <t>wellness_1</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -6249,7 +6286,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TX-000032</t>
+          <t>TX-000028</t>
         </is>
       </c>
       <c r="B49" s="11" t="n">
@@ -6267,36 +6304,36 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Detail-Lebensmittel</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Einkaufen / Detail-Lebensmittel</t>
+          <t>Freizeit / Gastronomie</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>YUMIHANA</t>
+          <t>YOOJI'S ROSENGARTEN</t>
         </is>
       </c>
       <c r="J49" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>18.55</v>
+        <v>11.9</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>18.55</v>
+        <v>11.9</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>grocery_2</t>
+          <t>gastronomy_2</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -6308,7 +6345,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TX-000033</t>
+          <t>TX-000029</t>
         </is>
       </c>
       <c r="B50" s="11" t="n">
@@ -6326,36 +6363,36 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Detail-Lebensmittel</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Einkaufen / Detail-Lebensmittel</t>
+          <t>Freizeit / Gastronomie</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>YUMI HANA</t>
+          <t>YOOJI'S ROSENGARTEN</t>
         </is>
       </c>
       <c r="J50" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>26.8</v>
+        <v>43.5</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>26.8</v>
+        <v>43.5</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>grocery_2</t>
+          <t>gastronomy_2</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -6367,7 +6404,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TX-000034</t>
+          <t>TX-000030</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
@@ -6385,36 +6422,36 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Supermärkte</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Einkaufen / Supermärkte</t>
+          <t>Freizeit / Gastronomie</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>COOP - 7811 QUAI WEST</t>
+          <t>COFFEE AND PLANTS</t>
         </is>
       </c>
       <c r="J51" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>7.75</v>
+        <v>10</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>7.75</v>
+        <v>10</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>supermarket_1</t>
+          <t>gastronomy_3</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -6426,11 +6463,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TX-000018</t>
+          <t>TX-000032</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
-        <v>45744</v>
+        <v>45743</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6444,36 +6481,36 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Mobilität</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Öffentlicher Verkehr</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Mobilität / Öffentlicher Verkehr</t>
+          <t>Einkaufen / Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>TRANSPORTS PUBLICS FRIBOURGEOIS (FAIRTIQ) N/A PAYMENT ID 250328064754083058ZX BESTELLNUMMER</t>
+          <t>YUMIHANA</t>
         </is>
       </c>
       <c r="J52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>34.3</v>
+        <v>18.55</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>34.3</v>
+        <v>18.55</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>transport_1</t>
+          <t>grocery_2</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6485,11 +6522,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TX-000019</t>
+          <t>TX-000033</t>
         </is>
       </c>
       <c r="B53" s="11" t="n">
-        <v>45744</v>
+        <v>45743</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6518,21 +6555,21 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>SUMUP *BACKEREI ZUR K</t>
+          <t>YUMI HANA</t>
         </is>
       </c>
       <c r="J53" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>11.1</v>
+        <v>26.8</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>11.1</v>
+        <v>26.8</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>grocery_1</t>
+          <t>grocery_2</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6544,11 +6581,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TX-000020</t>
+          <t>TX-000034</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
-        <v>45744</v>
+        <v>45743</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6567,31 +6604,31 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sonstiges Einkaufen</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Einkaufen / Sonstiges Einkaufen</t>
+          <t>Einkaufen / Supermärkte</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>KKIOSK 45810</t>
+          <t>COOP - 7811 QUAI WEST</t>
         </is>
       </c>
       <c r="J54" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>7.1</v>
+        <v>7.75</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>7.1</v>
+        <v>7.75</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>shopping_1</t>
+          <t>supermarket_1</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6603,7 +6640,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TX-000021</t>
+          <t>TX-000018</t>
         </is>
       </c>
       <c r="B55" s="11" t="n">
@@ -6621,36 +6658,36 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Mobilität</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gesundheit</t>
+          <t>Öffentlicher Verkehr</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leben / Gesundheit</t>
+          <t>Mobilität / Öffentlicher Verkehr</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>BAHNHOF APOTHEKE AG</t>
+          <t>TRANSPORTS PUBLICS FRIBOURGEOIS (FAIRTIQ) N/A PAYMENT ID 250328064754083058ZX BESTELLNUMMER</t>
         </is>
       </c>
       <c r="J55" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>24.4</v>
+        <v>34.3</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>24.4</v>
+        <v>34.3</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>health_1</t>
+          <t>transport_1</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6662,7 +6699,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TX-000022</t>
+          <t>TX-000019</t>
         </is>
       </c>
       <c r="B56" s="11" t="n">
@@ -6695,17 +6732,17 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>BÄCKEREI HUG</t>
+          <t>SUMUP *BACKEREI ZUR K</t>
         </is>
       </c>
       <c r="J56" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>8.1</v>
+        <v>11.1</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>8.1</v>
+        <v>11.1</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -6721,7 +6758,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TX-000023</t>
+          <t>TX-000020</t>
         </is>
       </c>
       <c r="B57" s="11" t="n">
@@ -6744,31 +6781,31 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Supermärkte</t>
+          <t>Sonstiges Einkaufen</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Einkaufen / Supermärkte</t>
+          <t>Einkaufen / Sonstiges Einkaufen</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>MIGROS M RIVERSIDE (7741)</t>
+          <t>KKIOSK 45810</t>
         </is>
       </c>
       <c r="J57" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>28.35</v>
+        <v>7.1</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>28.35</v>
+        <v>7.1</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>supermarket_1</t>
+          <t>shopping_1</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6780,11 +6817,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TX-000015</t>
+          <t>TX-000021</t>
         </is>
       </c>
       <c r="B58" s="11" t="n">
-        <v>45745</v>
+        <v>45744</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6798,36 +6835,36 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Detail-Lebensmittel</t>
+          <t>Gesundheit</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Einkaufen / Detail-Lebensmittel</t>
+          <t>Leben / Gesundheit</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>BÄCKEREI HUG</t>
+          <t>BAHNHOF APOTHEKE AG</t>
         </is>
       </c>
       <c r="J58" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>8.5</v>
+        <v>24.4</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>8.5</v>
+        <v>24.4</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>grocery_1</t>
+          <t>health_1</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6839,11 +6876,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TX-000016</t>
+          <t>TX-000022</t>
         </is>
       </c>
       <c r="B59" s="11" t="n">
-        <v>45745</v>
+        <v>45744</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6862,31 +6899,31 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Supermärkte</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Einkaufen / Supermärkte</t>
+          <t>Einkaufen / Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>MIGROS M RIVERSIDE (7741)</t>
+          <t>BÄCKEREI HUG</t>
         </is>
       </c>
       <c r="J59" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>2.9</v>
+        <v>8.1</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>2.9</v>
+        <v>8.1</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>supermarket_1</t>
+          <t>grocery_1</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6898,11 +6935,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TX-000017</t>
+          <t>TX-000023</t>
         </is>
       </c>
       <c r="B60" s="11" t="n">
-        <v>45745</v>
+        <v>45744</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6916,36 +6953,36 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kommunikation</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Wohnen / Kommunikation</t>
+          <t>Einkaufen / Supermärkte</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>SUNRISE GMBH POSTFACH 8050 ZURICH</t>
+          <t>MIGROS M RIVERSIDE (7741)</t>
         </is>
       </c>
       <c r="J60" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>49.6</v>
+        <v>28.35</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>49.6</v>
+        <v>28.35</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>communication_1</t>
+          <t>supermarket_1</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6957,11 +6994,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TX-000010</t>
+          <t>TX-000015</t>
         </is>
       </c>
       <c r="B61" s="11" t="n">
-        <v>45746</v>
+        <v>45745</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6975,36 +7012,36 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Freizeit / Gastronomie</t>
+          <t>Einkaufen / Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>SIGNOR ROSSI</t>
+          <t>BÄCKEREI HUG</t>
         </is>
       </c>
       <c r="J61" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>20</v>
+        <v>8.5</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>20</v>
+        <v>8.5</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>gastronomy_2</t>
+          <t>grocery_1</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -7016,11 +7053,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TX-000011</t>
+          <t>TX-000016</t>
         </is>
       </c>
       <c r="B62" s="11" t="n">
-        <v>45746</v>
+        <v>45745</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7049,17 +7086,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>MIGROS MARKTHALLE (8812)</t>
+          <t>MIGROS M RIVERSIDE (7741)</t>
         </is>
       </c>
       <c r="J62" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>20.7</v>
+        <v>2.9</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>20.7</v>
+        <v>2.9</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -7075,11 +7112,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TX-000012</t>
+          <t>TX-000017</t>
         </is>
       </c>
       <c r="B63" s="11" t="n">
-        <v>45746</v>
+        <v>45745</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7093,36 +7130,36 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Kommunikation</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Freizeit / Gastronomie</t>
+          <t>Wohnen / Kommunikation</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>MIGROS CITY TAKE AWAY (6624)</t>
+          <t>SUNRISE GMBH POSTFACH 8050 ZURICH</t>
         </is>
       </c>
       <c r="J63" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>3.9</v>
+        <v>49.6</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>3.9</v>
+        <v>49.6</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>gastronomy_1</t>
+          <t>communication_1</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7134,7 +7171,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TX-000013</t>
+          <t>TX-000010</t>
         </is>
       </c>
       <c r="B64" s="11" t="n">
@@ -7157,31 +7194,31 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kultur</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Freizeit / Kultur</t>
+          <t>Freizeit / Gastronomie</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>BYRO</t>
+          <t>SIGNOR ROSSI</t>
         </is>
       </c>
       <c r="J64" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>life_1</t>
+          <t>gastronomy_2</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7193,7 +7230,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TX-000014</t>
+          <t>TX-000011</t>
         </is>
       </c>
       <c r="B65" s="11" t="n">
@@ -7211,36 +7248,36 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sonstiges Leben</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leben / Sonstiges Leben</t>
+          <t>Einkaufen / Supermärkte</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>BYRO</t>
+          <t>MIGROS MARKTHALLE (8812)</t>
         </is>
       </c>
       <c r="J65" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>36.8</v>
+        <v>20.7</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>36.8</v>
+        <v>20.7</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>life_1</t>
+          <t>supermarket_1</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7252,11 +7289,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TX-000003</t>
+          <t>TX-000012</t>
         </is>
       </c>
       <c r="B66" s="11" t="n">
-        <v>45747</v>
+        <v>45746</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7270,36 +7307,36 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Detail-Lebensmittel</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Einkaufen / Detail-Lebensmittel</t>
+          <t>Freizeit / Gastronomie</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>CITY TANKSTELLE</t>
+          <t>MIGROS CITY TAKE AWAY (6624)</t>
         </is>
       </c>
       <c r="J66" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>10.34</v>
+        <v>3.9</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>10.34</v>
+        <v>3.9</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>grocery_3</t>
+          <t>gastronomy_1</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7311,11 +7348,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TX-000004</t>
+          <t>TX-000013</t>
         </is>
       </c>
       <c r="B67" s="11" t="n">
-        <v>45747</v>
+        <v>45746</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7329,36 +7366,36 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Detail-Lebensmittel</t>
+          <t>Kultur</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Einkaufen / Detail-Lebensmittel</t>
+          <t>Freizeit / Kultur</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>CITY TANKSTELLE</t>
+          <t>BYRO</t>
         </is>
       </c>
       <c r="J67" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>6.55</v>
+        <v>15</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>6.55</v>
+        <v>15</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>grocery_3</t>
+          <t>life_1</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7370,11 +7407,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TX-000006</t>
+          <t>TX-000014</t>
         </is>
       </c>
       <c r="B68" s="11" t="n">
-        <v>45747</v>
+        <v>45746</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7388,36 +7425,36 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sonstiges Einkaufen</t>
+          <t>Sonstiges Leben</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Einkaufen / Sonstiges Einkaufen</t>
+          <t>Leben / Sonstiges Leben</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>KKIOSK 45810</t>
+          <t>BYRO</t>
         </is>
       </c>
       <c r="J68" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>7.55</v>
+        <v>36.8</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>7.55</v>
+        <v>36.8</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>shopping_1</t>
+          <t>life_1</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7429,7 +7466,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TX-000007</t>
+          <t>TX-000003</t>
         </is>
       </c>
       <c r="B69" s="11" t="n">
@@ -7452,31 +7489,31 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Supermärkte</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Einkaufen / Supermärkte</t>
+          <t>Einkaufen / Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>MIGROS MARKTHALLE (8812)</t>
+          <t>CITY TANKSTELLE</t>
         </is>
       </c>
       <c r="J69" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>22.2</v>
+        <v>10.34</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>22.2</v>
+        <v>10.34</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>supermarket_1</t>
+          <t>grocery_3</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -7488,7 +7525,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TX-000008</t>
+          <t>TX-000004</t>
         </is>
       </c>
       <c r="B70" s="11" t="n">
@@ -7506,41 +7543,36 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Finanzen</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Finanzen / Fees</t>
+          <t>Einkaufen / Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>PREIS FÜR BANKPAKET SMART 02.2025</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>PREIS FÜR BANKPAKET SMART 02.2025</t>
+          <t>CITY TANKSTELLE</t>
         </is>
       </c>
       <c r="J70" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>5</v>
+        <v>6.55</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>5</v>
+        <v>6.55</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>finance_2</t>
+          <t>grocery_3</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -7552,7 +7584,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TX-000009</t>
+          <t>TX-000006</t>
         </is>
       </c>
       <c r="B71" s="11" t="n">
@@ -7570,41 +7602,36 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Miete und Hypothek</t>
+          <t>Sonstiges Einkaufen</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Wohnen / Miete und Hypothek</t>
+          <t>Einkaufen / Sonstiges Einkaufen</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>FINANZVERWALTUNG STADT SOLOTHURN</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2025/04/01 / 7045128</t>
+          <t>KKIOSK 45810</t>
         </is>
       </c>
       <c r="J71" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>1774</v>
+        <v>7.55</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>1774</v>
+        <v>7.55</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>housing_1</t>
+          <t>shopping_1</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -7616,7 +7643,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TX-000064</t>
+          <t>TX-000007</t>
         </is>
       </c>
       <c r="B72" s="11" t="n">
@@ -7634,36 +7661,36 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Styling und Wellness</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Leben / Styling und Wellness</t>
+          <t>Einkaufen / Supermärkte</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>SUMUP *COIFFEUR HAIRCUT</t>
+          <t>MIGROS MARKTHALLE (8812)</t>
         </is>
       </c>
       <c r="J72" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>50</v>
+        <v>22.2</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>50</v>
+        <v>22.2</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>wellness_2</t>
+          <t>supermarket_1</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -7675,188 +7702,198 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TX-000089</t>
+          <t>TX-000008</t>
         </is>
       </c>
       <c r="B73" s="11" t="n">
-        <v>45748</v>
+        <v>45747</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Refund</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Finanzen</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Krankenkasse</t>
+          <t>Fees</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Leben / Krankenkasse</t>
+          <t>Finanzen / Fees</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>MUSTER UND BEISPIEL GEMEINSCHAFTSKONTO MUSTERWEG 1 4600 OLTEN</t>
+          <t>PREIS FÜR BANKPAKET SMART 02.2025</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>PREIS FÜR BANKPAKET SMART 02.2025</t>
         </is>
       </c>
       <c r="J73" s="5" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>-120</v>
+        <v>5</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>refund_example_amount_1</t>
+          <t>finance_2</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>export.202504.categorized.csv</t>
+          <t>export.202503.categorized.csv</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TX-000090</t>
+          <t>TX-000009</t>
         </is>
       </c>
       <c r="B74" s="11" t="n">
-        <v>45748</v>
+        <v>45747</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Refund</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Familie</t>
+          <t>Miete und Hypothek</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Leben / Familie</t>
+          <t>Wohnen / Miete und Hypothek</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>MUSTER UND BEISPIEL GEMEINSCHAFTSKONTO MUSTERWEG 1 4600 OLTEN</t>
+          <t>FINANZVERWALTUNG STADT SOLOTHURN</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2025/04/01 / 7045128</t>
         </is>
       </c>
       <c r="J74" s="5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>0</v>
+        <v>1774</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>-15</v>
+        <v>1774</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>refund_example_counterparty_1</t>
+          <t>housing_1</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>export.202504.categorized.csv</t>
+          <t>export.202503.categorized.csv</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TX-000061</t>
+          <t>TX-000064</t>
         </is>
       </c>
       <c r="B75" s="11" t="n">
-        <v>45751</v>
+        <v>45747</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Refund</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Reisen und Erleben</t>
+          <t>Styling und Wellness</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Freizeit / Reisen und Erleben</t>
+          <t>Leben / Styling und Wellness</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>UEFA WOMEN'S EURO 2025 NYON</t>
+          <t>SUMUP *COIFFEUR HAIRCUT</t>
         </is>
       </c>
       <c r="J75" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>-100</v>
+        <v>50</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>refund_3</t>
+          <t>wellness_2</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>export.202504.categorized.csv</t>
+          <t>export.202503.categorized.csv</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TX-000084</t>
+          <t>TX-000089</t>
         </is>
       </c>
       <c r="B76" s="11" t="n">
-        <v>45752</v>
+        <v>45748</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -7865,41 +7902,41 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Refund</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Supermärkte</t>
+          <t>Krankenkasse</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Einkaufen / Supermärkte</t>
+          <t>Leben / Krankenkasse</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>MIGROS MARKTHALLE (8812)</t>
+          <t>MUSTER UND BEISPIEL GEMEINSCHAFTSKONTO MUSTERWEG 1 4600 OLTEN</t>
         </is>
       </c>
       <c r="J76" s="5" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>108.9</v>
+        <v>0</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>108.9</v>
+        <v>-120</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>supermarket_1</t>
+          <t>refund_example_amount_1</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -7911,11 +7948,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TX-000085</t>
+          <t>TX-000090</t>
         </is>
       </c>
       <c r="B77" s="11" t="n">
-        <v>45759</v>
+        <v>45748</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -7924,41 +7961,41 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Refund</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Supermärkte</t>
+          <t>Familie</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Einkaufen / Supermärkte</t>
+          <t>Leben / Familie</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>COOP-5510 RIVERSIDE REST.</t>
+          <t>MUSTER UND BEISPIEL GEMEINSCHAFTSKONTO MUSTERWEG 1 4600 OLTEN</t>
         </is>
       </c>
       <c r="J77" s="5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>76.3</v>
+        <v>0</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>76.3</v>
+        <v>-15</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>supermarket_1</t>
+          <t>refund_example_counterparty_1</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -7970,11 +8007,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TX-000062</t>
+          <t>TX-000061</t>
         </is>
       </c>
       <c r="B78" s="11" t="n">
-        <v>45763</v>
+        <v>45751</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -7983,46 +8020,41 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Refund</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Einkommen</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lohn</t>
+          <t>Reisen und Erleben</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Einkommen / Lohn</t>
+          <t>Freizeit / Reisen und Erleben</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>FIKTIVE LOHN AG PERSONALABTEILUNG</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>LOHNBEISPIEL APRIL 2025 | DEMO REF 001</t>
+          <t>UEFA WOMEN'S EURO 2025 NYON</t>
         </is>
       </c>
       <c r="J78" s="5" t="n">
-        <v>4200</v>
+        <v>100</v>
       </c>
       <c r="K78" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>-4200</v>
+        <v>-100</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>income_example_counterparty_1</t>
+          <t>refund_3</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -8034,11 +8066,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TX-000063</t>
+          <t>TX-000084</t>
         </is>
       </c>
       <c r="B79" s="11" t="n">
-        <v>45764</v>
+        <v>45752</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8052,36 +8084,36 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Finanzen</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spenden</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Finanzen / Spenden</t>
+          <t>Einkaufen / Supermärkte</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>ANONYMISIERTER VEREIN MITTEILUNGEN: DEMO-ZWECK JAHRESBEITRAG</t>
+          <t>MIGROS MARKTHALLE (8812)</t>
         </is>
       </c>
       <c r="J79" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>25</v>
+        <v>108.9</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>25</v>
+        <v>108.9</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>expense_example_counterparty_iban_1</t>
+          <t>supermarket_1</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -8093,49 +8125,54 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TX-000065</t>
+          <t>TX-000085</t>
         </is>
       </c>
       <c r="B80" s="11" t="n">
-        <v>45765</v>
+        <v>45759</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
           <t>2025-04</t>
         </is>
       </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Einkaufen / Supermärkte</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>FIKTIVE DIGITAL GMBH</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>PAYMENT ID 000A00D0 BESTELLNUMMER AB00CD00</t>
+          <t>COOP-5510 RIVERSIDE REST.</t>
         </is>
       </c>
       <c r="J80" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>33.7</v>
+        <v>76.3</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>33.7</v>
+        <v>76.3</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>supermarket_1</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -8147,49 +8184,59 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TX-000066</t>
+          <t>TX-000062</t>
         </is>
       </c>
       <c r="B81" s="11" t="n">
-        <v>45766</v>
+        <v>45763</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
           <t>2025-04</t>
         </is>
       </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Einkommen</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Lohn</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Einkommen / Lohn</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>FIKTIVE POST AG</t>
+          <t>FIKTIVE LOHN AG PERSONALABTEILUNG</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>PAYMENT ID AB0CD0EF00GH0IJ0 BESTELLNUMMER MYS_AB0CD0EF00GH0I</t>
+          <t>LOHNBEISPIEL APRIL 2025 | DEMO REF 001</t>
         </is>
       </c>
       <c r="J81" s="5" t="n">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>12.5</v>
+        <v>-4200</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>income_example_counterparty_1</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -8201,11 +8248,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TX-000086</t>
+          <t>TX-000063</t>
         </is>
       </c>
       <c r="B82" s="11" t="n">
-        <v>45766</v>
+        <v>45764</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8219,36 +8266,36 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Finanzen</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Supermärkte</t>
+          <t>Spenden</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Einkaufen / Supermärkte</t>
+          <t>Finanzen / Spenden</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>MIGROS M RIVERSIDE (7741)</t>
+          <t>ANONYMISIERTER VEREIN MITTEILUNGEN: DEMO-ZWECK JAHRESBEITRAG</t>
         </is>
       </c>
       <c r="J82" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>54.85</v>
+        <v>25</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>54.85</v>
+        <v>25</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>supermarket_1</t>
+          <t>expense_example_counterparty_iban_1</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -8260,11 +8307,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TX-000067</t>
+          <t>TX-000065</t>
         </is>
       </c>
       <c r="B83" s="11" t="n">
-        <v>45767</v>
+        <v>45765</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8283,17 +8330,22 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>FIKTIVER SCHUHLADEN BIEL</t>
+          <t>FIKTIVE DIGITAL GMBH</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>PAYMENT ID 000A00D0 BESTELLNUMMER AB00CD00</t>
         </is>
       </c>
       <c r="J83" s="5" t="n">
-        <v>49.9</v>
+        <v>0</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>0</v>
+        <v>33.7</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>-49.9</v>
+        <v>33.7</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -8309,11 +8361,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TX-000068</t>
+          <t>TX-000066</t>
         </is>
       </c>
       <c r="B84" s="11" t="n">
-        <v>45768</v>
+        <v>45766</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -8332,17 +8384,22 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>FIKTIVER FAHRSCHEIN BERLIN DEUTSCHLAND</t>
+          <t>FIKTIVE POST AG</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>PAYMENT ID AB0CD0EF00GH0IJ0 BESTELLNUMMER MYS_AB0CD0EF00GH0I</t>
         </is>
       </c>
       <c r="J84" s="5" t="n">
-        <v>19.15</v>
+        <v>0</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>-19.15</v>
+        <v>12.5</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -8358,11 +8415,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TX-000069</t>
+          <t>TX-000086</t>
         </is>
       </c>
       <c r="B85" s="11" t="n">
-        <v>45769</v>
+        <v>45766</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -8376,36 +8433,36 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Finanzen</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bargeldbezug</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Finanzen / Bargeldbezug</t>
+          <t>Einkaufen / Supermärkte</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>BAHNHOF</t>
+          <t>MIGROS M RIVERSIDE (7741)</t>
         </is>
       </c>
       <c r="J85" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>143.5</v>
+        <v>54.85</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>143.5</v>
+        <v>54.85</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>finance_1</t>
+          <t>supermarket_1</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -8417,54 +8474,44 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TX-000087</t>
+          <t>TX-000067</t>
         </is>
       </c>
       <c r="B86" s="11" t="n">
-        <v>45773</v>
+        <v>45767</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Supermärkte</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Einkaufen / Supermärkte</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>MIGROS MARKTHALLE (8812)</t>
+          <t>FIKTIVER SCHUHLADEN BIEL</t>
         </is>
       </c>
       <c r="J86" s="5" t="n">
-        <v>0</v>
+        <v>49.9</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>121.6</v>
+        <v>0</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>121.6</v>
+        <v>-49.9</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>supermarket_1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -8476,69 +8523,236 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>TX-000068</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="n">
+        <v>45768</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>FIKTIVER FAHRSCHEIN BERLIN DEUTSCHLAND</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>-19.15</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>TX-000069</t>
+        </is>
+      </c>
+      <c r="B88" s="11" t="n">
+        <v>45769</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Finanzen</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Bargeldbezug</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Finanzen / Bargeldbezug</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>BAHNHOF</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>finance_1</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>TX-000087</t>
+        </is>
+      </c>
+      <c r="B89" s="11" t="n">
+        <v>45773</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Einkaufen / Supermärkte</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>MIGROS MARKTHALLE (8812)</t>
+        </is>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>supermarket_1</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t>TX-000088</t>
         </is>
       </c>
-      <c r="B87" s="11" t="n">
+      <c r="B90" s="11" t="n">
         <v>45777</v>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>Wohnen</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>Miete und Hypothek</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>Wohnen / Miete und Hypothek</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>FINANZVERWALTUNG STADT SOLOTHURN</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>2025/05/01 / 7045128</t>
         </is>
       </c>
-      <c r="J87" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="5" t="n">
+      <c r="J90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="5" t="n">
         <v>1774</v>
       </c>
-      <c r="L87" s="5" t="n">
+      <c r="L90" s="5" t="n">
         <v>1774</v>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>housing_1</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t>export.202504.categorized.csv</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N87"/>
+  <autoFilter ref="A1:N90"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8549,7 +8763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8653,7 +8867,7 @@
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>823.6</v>
+        <v>804.7</v>
       </c>
       <c r="E3" t="n">
         <v>9</v>
@@ -8662,7 +8876,7 @@
         <v>4</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.599</v>
+        <v>0.6189</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -8685,7 +8899,7 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>342.1</v>
+        <v>286.4</v>
       </c>
       <c r="E4" t="n">
         <v>4</v>
@@ -8694,7 +8908,7 @@
         <v>4</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.2488</v>
+        <v>0.2203</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -8726,7 +8940,7 @@
         <v>4</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.1465</v>
+        <v>0.1549</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
@@ -8758,7 +8972,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.0056</v>
+        <v>0.006</v>
       </c>
       <c r="H6" t="n">
         <v>4</v>
@@ -8863,30 +9077,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Detail-Lebensmittel</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BÄCKEREI HUG</t>
+          <t>YOOJI'S ROSENGARTEN</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>40</v>
+        <v>62.3</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.2391</v>
+        <v>0.35</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -8895,30 +9109,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Detail-Lebensmittel</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WAKARA GMBH</t>
+          <t>+41796666222 KEBAB, IMBISS</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.165</v>
+        <v>0.1545</v>
       </c>
       <c r="H11" t="n">
         <v>2</v>
@@ -8927,21 +9141,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Detail-Lebensmittel</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>YUMI HANA</t>
+          <t>COOP-5510 RIVERSIDE REST.</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>26.8</v>
+        <v>24.5</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -8950,7 +9164,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.1602</v>
+        <v>0.1376</v>
       </c>
       <c r="H12" t="n">
         <v>3</v>
@@ -8959,21 +9173,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Detail-Lebensmittel</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CONFISERIE SPRÜNGLI AG</t>
+          <t>+41790000000 MAX MUSTER</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>22.05</v>
+        <v>20</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -8982,7 +9196,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.1318</v>
+        <v>0.1124</v>
       </c>
       <c r="H13" t="n">
         <v>4</v>
@@ -8991,21 +9205,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Detail-Lebensmittel</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>YUMIHANA</t>
+          <t>SIGNOR ROSSI</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>18.55</v>
+        <v>20</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -9014,7 +9228,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.1109</v>
+        <v>0.1124</v>
       </c>
       <c r="H14" t="n">
         <v>5</v>
@@ -9023,21 +9237,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Detail-Lebensmittel</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CITY TANKSTELLE</t>
+          <t>MIGROS CITY TAKE AWAY</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>16.89</v>
+        <v>10.7</v>
       </c>
       <c r="E15" t="n">
         <v>2</v>
@@ -9046,7 +9260,7 @@
         <v>1</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.101</v>
+        <v>0.0601</v>
       </c>
       <c r="H15" t="n">
         <v>6</v>
@@ -9055,21 +9269,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Detail-Lebensmittel</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SUMUP *BACKEREI ZUR K</t>
+          <t>COFFEE AND PLANTS</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -9078,7 +9292,7 @@
         <v>1</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.0664</v>
+        <v>0.0562</v>
       </c>
       <c r="H16" t="n">
         <v>7</v>
@@ -9087,21 +9301,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Detail-Lebensmittel</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BRANKOVIC BREZELSTUBE</t>
+          <t>MUSTER CAFE</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -9110,7 +9324,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.0257</v>
+        <v>0.0169</v>
       </c>
       <c r="H17" t="n">
         <v>8</v>
@@ -9119,30 +9333,30 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>YOOJI'S ROSENGARTEN</t>
+          <t>BÄCKEREI HUG</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>62.3</v>
+        <v>40</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.4059</v>
+        <v>0.2391</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
@@ -9151,30 +9365,30 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+41796666222 KEBAB, IMBISS</t>
+          <t>WAKARA GMBH</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.1792</v>
+        <v>0.165</v>
       </c>
       <c r="H19" t="n">
         <v>2</v>
@@ -9183,21 +9397,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>+41790000000 MAX MUSTER</t>
+          <t>YUMI HANA</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>20</v>
+        <v>26.8</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -9206,7 +9420,7 @@
         <v>1</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.1303</v>
+        <v>0.1602</v>
       </c>
       <c r="H20" t="n">
         <v>3</v>
@@ -9215,21 +9429,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SIGNOR ROSSI</t>
+          <t>CONFISERIE SPRÜNGLI AG</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>20</v>
+        <v>22.05</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -9238,7 +9452,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.1303</v>
+        <v>0.1318</v>
       </c>
       <c r="H21" t="n">
         <v>4</v>
@@ -9247,30 +9461,30 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MIGROS CITY TAKE AWAY</t>
+          <t>YUMIHANA</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>10.7</v>
+        <v>18.55</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.0697</v>
+        <v>0.1109</v>
       </c>
       <c r="H22" t="n">
         <v>5</v>
@@ -9279,30 +9493,30 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>COFFEE AND PLANTS</t>
+          <t>CITY TANKSTELLE</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>10</v>
+        <v>16.89</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="H23" t="n">
         <v>6</v>
@@ -9311,21 +9525,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MUSTER CAFE</t>
+          <t>SUMUP *BACKEREI ZUR K</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>3</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -9334,7 +9548,7 @@
         <v>1</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.0195</v>
+        <v>0.0664</v>
       </c>
       <c r="H24" t="n">
         <v>7</v>
@@ -9343,21 +9557,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Finanzen</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bargeldbezug</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BAHNHOF</t>
+          <t>BRANKOVIC BREZELSTUBE</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>143.5</v>
+        <v>4.3</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -9366,30 +9580,30 @@
         <v>1</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1</v>
+        <v>0.0257</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mobilität</t>
+          <t>Finanzen</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Öffentlicher Verkehr</t>
+          <t>Bargeldbezug</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TRANSPORTS PUBLICS FRIBOURGEOIS (FAIRTIQ) N/A PAYMENT ID 250326064915818975ZX BESTELLNUMMER</t>
+          <t>BAHNHOF</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>62.6</v>
+        <v>143.5</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -9398,7 +9612,7 @@
         <v>1</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.646</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
@@ -9417,11 +9631,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TRANSPORTS PUBLICS FRIBOURGEOIS (FAIRTIQ) N/A PAYMENT ID 250328064754083058ZX BESTELLNUMMER</t>
+          <t>TRANSPORTS PUBLICS FRIBOURGEOIS (FAIRTIQ) N/A PAYMENT ID 250326064915818975ZX BESTELLNUMMER</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>34.3</v>
+        <v>62.6</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -9430,30 +9644,30 @@
         <v>1</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.354</v>
+        <v>0.646</v>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Mobilität</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Styling und Wellness</t>
+          <t>Öffentlicher Verkehr</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SUMUP *COIFFEUR HAIRCUT</t>
+          <t>TRANSPORTS PUBLICS FRIBOURGEOIS (FAIRTIQ) N/A PAYMENT ID 250328064754083058ZX BESTELLNUMMER</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>50</v>
+        <v>34.3</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -9462,42 +9676,42 @@
         <v>1</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.6258</v>
+        <v>0.354</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Styling und Wellness</t>
+          <t>Haushalt</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>THE BODY SHOP</t>
+          <t>COOP-5510 RIVERSIDE REST.</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>29.9</v>
+        <v>31.2</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.3742</v>
+        <v>0.3547</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -9508,16 +9722,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kommunikation</t>
+          <t>Haushalt</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SUNRISE GMBH POSTFACH 8050 ZURICH</t>
+          <t>MANOR AG - 771 (CENTRA)</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>49.6</v>
+        <v>23.95</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -9526,10 +9740,10 @@
         <v>1</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.7058</v>
+        <v>0.2723</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -9540,16 +9754,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kommunikation</t>
+          <t>Haushalt</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLOUDSERVICE INC SAN</t>
+          <t>MIGROS MARKTHALLE</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>18.67</v>
+        <v>18.9</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -9558,10 +9772,10 @@
         <v>1</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.2657</v>
+        <v>0.2149</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -9572,16 +9786,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kommunikation</t>
+          <t>Haushalt</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>APPLE.COM/BILL</t>
+          <t>ONLINE HAUSHALT AG</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -9590,30 +9804,30 @@
         <v>1</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.0285</v>
+        <v>0.158</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Haushalt</t>
+          <t>Styling und Wellness</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MANOR AG - 771 (CENTRA)</t>
+          <t>SUMUP *COIFFEUR HAIRCUT</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>23.95</v>
+        <v>50</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -9622,7 +9836,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.6328</v>
+        <v>0.6258</v>
       </c>
       <c r="H33" t="n">
         <v>1</v>
@@ -9631,30 +9845,30 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Haushalt</t>
+          <t>Styling und Wellness</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ONLINE HAUSHALT AG</t>
+          <t>THE BODY SHOP</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>13.9</v>
+        <v>29.9</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.3672</v>
+        <v>0.3742</v>
       </c>
       <c r="H34" t="n">
         <v>2</v>
@@ -9663,21 +9877,21 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sonstiges Leben</t>
+          <t>Kommunikation</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BYRO</t>
+          <t>SUNRISE GMBH POSTFACH 8050 ZURICH</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>36.8</v>
+        <v>49.6</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -9686,7 +9900,7 @@
         <v>1</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>1</v>
+        <v>0.7058</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
@@ -9695,21 +9909,21 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Mobilität</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Privater Verkehr</t>
+          <t>Kommunikation</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MOBILITY MUSTER GENOSSENSCHAFT 6343 ROTKREUZ</t>
+          <t>CLOUDSERVICE INC SAN</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>26.7</v>
+        <v>18.67</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
@@ -9718,30 +9932,30 @@
         <v>1</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>1</v>
+        <v>0.2657</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Finanzen</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Spenden</t>
+          <t>Kommunikation</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ANONYMISIERTER VEREIN MITTEILUNGEN: DEMO-ZWECK JAHRESBEITRAG</t>
+          <t>APPLE.COM/BILL</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -9750,10 +9964,10 @@
         <v>1</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>1</v>
+        <v>0.0285</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -9764,16 +9978,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Gesundheit</t>
+          <t>Sonstiges Leben</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BAHNHOF APOTHEKE AG</t>
+          <t>BYRO</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>24.4</v>
+        <v>36.8</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
@@ -9791,21 +10005,21 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Mobilität</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kultur</t>
+          <t>Privater Verkehr</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BYRO</t>
+          <t>MOBILITY MUSTER GENOSSENSCHAFT 6343 ROTKREUZ</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>15</v>
+        <v>26.7</v>
       </c>
       <c r="E39" t="n">
         <v>1</v>
@@ -9823,24 +10037,24 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Finanzen</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sonstiges Einkaufen</t>
+          <t>Spenden</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>KKIOSK 45810</t>
+          <t>ANONYMISIERTER VEREIN MITTEILUNGEN: DEMO-ZWECK JAHRESBEITRAG</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>14.65</v>
+        <v>25</v>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
         <v>1</v>
@@ -9855,21 +10069,21 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Handwerk und Garten</t>
+          <t>Gesundheit</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>JUMBO-7782 INDUSTRIEPARK</t>
+          <t>BAHNHOF APOTHEKE AG</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>10.9</v>
+        <v>24.4</v>
       </c>
       <c r="E41" t="n">
         <v>1</v>
@@ -9887,21 +10101,21 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Finanzen</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>Kultur</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PREIS FÜR BANKPAKET SMART 02.2025</t>
+          <t>BYRO</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>
@@ -9919,19 +10133,24 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Rückerstattungen</t>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Sonstiges Einkaufen</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>+41790000000 MAX MUSTER</t>
+          <t>KKIOSK 45810</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>-1</v>
+        <v>14.65</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
         <v>1</v>
@@ -9946,16 +10165,21 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Handwerk und Garten</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FIKTIVE DIGITAL GMBH</t>
+          <t>JUMBO-7782 INDUSTRIEPARK</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>33.7</v>
+        <v>10.9</v>
       </c>
       <c r="E44" t="n">
         <v>1</v>
@@ -9964,7 +10188,7 @@
         <v>1</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>-3.2249</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
         <v>1</v>
@@ -9973,16 +10197,21 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Finanzen</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Fees</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FIKTIVE POST AG</t>
+          <t>PREIS FÜR BANKPAKET SMART 02.2025</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="E45" t="n">
         <v>1</v>
@@ -9991,25 +10220,25 @@
         <v>1</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>-1.1962</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Rückerstattungen</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>UNMATCHED TEST STORE</t>
+          <t>+41790000000 MAX MUSTER</t>
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>12.4</v>
+        <v>-1</v>
       </c>
       <c r="E46" t="n">
         <v>1</v>
@@ -10018,10 +10247,10 @@
         <v>1</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>-1.1866</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -10032,11 +10261,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FIKTIVER FAHRSCHEIN BERLIN DEUTSCHLAND</t>
+          <t>FIKTIVE DIGITAL GMBH</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>-19.15</v>
+        <v>33.7</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
@@ -10045,10 +10274,10 @@
         <v>1</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>1.8325</v>
+        <v>-3.2249</v>
       </c>
       <c r="H47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -10059,11 +10288,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FIKTIVER SCHUHLADEN BIEL</t>
+          <t>FIKTIVE POST AG</t>
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>-49.9</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="n">
         <v>1</v>
@@ -10072,30 +10301,25 @@
         <v>1</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>4.7751</v>
+        <v>-1.1962</v>
       </c>
       <c r="H48" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Freizeit</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Reisen und Erleben</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>UEFA WOMEN'S EURO 2025 NYON</t>
+          <t>UNMATCHED TEST STORE</t>
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>-100</v>
+        <v>12.4</v>
       </c>
       <c r="E49" t="n">
         <v>1</v>
@@ -10104,30 +10328,25 @@
         <v>1</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>1</v>
+        <v>-1.1866</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Leben</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Krankenkasse</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MUSTER UND BEISPIEL GEMEINSCHAFTSKONTO MUSTERWEG 1 4600 OLTEN</t>
+          <t>FIKTIVER FAHRSCHEIN BERLIN DEUTSCHLAND</t>
         </is>
       </c>
       <c r="D50" s="5" t="n">
-        <v>-120</v>
+        <v>-19.15</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
@@ -10136,46 +10355,137 @@
         <v>1</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.06560000000000001</v>
+        <v>1.8325</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>FIKTIVER SCHUHLADEN BIEL</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>-49.9</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>4.7751</v>
+      </c>
+      <c r="H51" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Reisen und Erleben</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>UEFA WOMEN'S EURO 2025 NYON</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>Leben</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Krankenkasse</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>MUSTER UND BEISPIEL GEMEINSCHAFTSKONTO MUSTERWEG 1 4600 OLTEN</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>-120</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="12" t="n">
+        <v>0.06560000000000001</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Krankenkasse</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
         <is>
           <t>MEDICURA PLUS AG GESUNDHEITSWEG 8 4052 BASEL</t>
         </is>
       </c>
-      <c r="D51" s="5" t="n">
+      <c r="D54" s="5" t="n">
         <v>-1710.5</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E54" t="n">
         <v>2</v>
       </c>
-      <c r="F51" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="12" t="n">
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="12" t="n">
         <v>0.9344</v>
       </c>
-      <c r="H51" t="n">
+      <c r="H54" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H51"/>
+  <autoFilter ref="A1:H54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/example/output/dataset.analysis.xlsx
+++ b/data/example/output/dataset.analysis.xlsx
@@ -15,8 +15,8 @@
     <sheet name="Top Payees" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Transactions'!$A$1:$N$90</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Top Payees'!$A$1:$H$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Transactions'!$A$1:$N$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Top Payees'!$A$1:$H$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,12 +513,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overviews by category'!$A$52:$A$54</f>
+              <f>'Overviews by category'!$A$52:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overviews by category'!$B$52:$B$54</f>
+              <f>'Overviews by category'!$B$52:$B$55</f>
             </numRef>
           </val>
         </ser>
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>18300</v>
+        <v>23500</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>2023.95</v>
+        <v>2394.75</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>0</v>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>18300</v>
+        <v>23500</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>0</v>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>2023.95</v>
+        <v>2394.75</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>0</v>
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>20323.95</v>
+        <v>25894.75</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>9674.959999999999</v>
@@ -1090,7 +1090,7 @@
         <v>450</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
     </row>
     <row r="15">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>20773.95</v>
+        <v>26344.75</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>9674.959999999999</v>
+        <v>10474.96</v>
       </c>
     </row>
     <row r="17">
@@ -1113,11 +1113,11 @@
         </is>
       </c>
       <c r="B17" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$D$2:$D$90, "Income") + SUMIFS(Transactions!$J$2:$J$90, Transactions!$D$2:$D$90, "Expense") + SUMIFS(Transactions!$J$2:$J$90, Transactions!$D$2:$D$90, "Refund") + SUMIFS(Transactions!$J$2:$J$90, Transactions!$D$2:$D$90, "Transfer")</f>
+        <f>SUMIFS(Transactions!$J$2:$J$104, Transactions!$D$2:$D$104, "Income") + SUMIFS(Transactions!$J$2:$J$104, Transactions!$D$2:$D$104, "Expense") + SUMIFS(Transactions!$J$2:$J$104, Transactions!$D$2:$D$104, "Refund") + SUMIFS(Transactions!$J$2:$J$104, Transactions!$D$2:$D$104, "Transfer")</f>
         <v/>
       </c>
       <c r="C17" s="9">
-        <f>SUMIFS(Transactions!$K$2:$K$90, Transactions!$D$2:$D$90, "Income") + SUMIFS(Transactions!$K$2:$K$90, Transactions!$D$2:$D$90, "Expense") + SUMIFS(Transactions!$K$2:$K$90, Transactions!$D$2:$D$90, "Refund") + SUMIFS(Transactions!$K$2:$K$90, Transactions!$D$2:$D$90, "Transfer")</f>
+        <f>SUMIFS(Transactions!$K$2:$K$104, Transactions!$D$2:$D$104, "Income") + SUMIFS(Transactions!$K$2:$K$104, Transactions!$D$2:$D$104, "Expense") + SUMIFS(Transactions!$K$2:$K$104, Transactions!$D$2:$D$104, "Refund") + SUMIFS(Transactions!$K$2:$K$104, Transactions!$D$2:$D$104, "Transfer")</f>
         <v/>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B57"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>18300</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="9">
@@ -1205,7 +1205,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>18300</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="10">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="B10" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$D$2:$D$90, "Income") - SUMIFS(Transactions!$K$2:$K$90, Transactions!$D$2:$D$90, "Income")</f>
+        <f>SUMIFS(Transactions!$J$2:$J$104, Transactions!$D$2:$D$104, "Income") - SUMIFS(Transactions!$K$2:$K$104, Transactions!$D$2:$D$104, "Income")</f>
         <v/>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="B37" s="9">
-        <f>SUMIFS(Transactions!$K$2:$K$90, Transactions!$D$2:$D$90, "Expense") - SUMIFS(Transactions!$J$2:$J$90, Transactions!$D$2:$D$90, "Expense")</f>
+        <f>SUMIFS(Transactions!$K$2:$K$104, Transactions!$D$2:$D$104, "Expense") - SUMIFS(Transactions!$J$2:$J$104, Transactions!$D$2:$D$104, "Expense")</f>
         <v/>
       </c>
     </row>
@@ -1377,48 +1377,58 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>100</v>
+        <v>280</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>Mobilität</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>190.8</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>Rückerstattungen</t>
         </is>
       </c>
-      <c r="B54" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="B55" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B55" s="7" t="n">
-        <v>2023.95</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>Check (Transactions)</t>
-        </is>
-      </c>
-      <c r="B56" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$D$2:$D$90, "Refund") - SUMIFS(Transactions!$K$2:$K$90, Transactions!$D$2:$D$90, "Refund")</f>
-        <v/>
+      <c r="B56" s="7" t="n">
+        <v>2394.75</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
+          <t>Check (Transactions)</t>
+        </is>
+      </c>
+      <c r="B57" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$104, Transactions!$D$2:$D$104, "Refund") - SUMIFS(Transactions!$K$2:$K$104, Transactions!$D$2:$D$104, "Refund")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
           <t>Difference</t>
         </is>
       </c>
-      <c r="B57" s="9">
-        <f>B56-B55</f>
+      <c r="B58" s="9">
+        <f>B57-B56</f>
         <v/>
       </c>
     </row>
@@ -1434,7 +1444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1621,15 +1631,15 @@
         </is>
       </c>
       <c r="B16" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-01", Transactions!$D$2:$D$90, "&lt;&gt;Transfer")</f>
+        <f>SUMIFS(Transactions!$J$2:$J$104, Transactions!$C$2:$C$104, "2025-01", Transactions!$D$2:$D$104, "&lt;&gt;Transfer")</f>
         <v/>
       </c>
       <c r="C16" s="9">
-        <f>SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-01", Transactions!$D$2:$D$90, "&lt;&gt;Transfer")</f>
+        <f>SUMIFS(Transactions!$K$2:$K$104, Transactions!$C$2:$C$104, "2025-01", Transactions!$D$2:$D$104, "&lt;&gt;Transfer")</f>
         <v/>
       </c>
       <c r="D16" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-01", Transactions!$D$2:$D$90, "&lt;&gt;Transfer") - SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-01", Transactions!$D$2:$D$90, "&lt;&gt;Transfer")</f>
+        <f>SUMIFS(Transactions!$J$2:$J$104, Transactions!$C$2:$C$104, "2025-01", Transactions!$D$2:$D$104, "&lt;&gt;Transfer") - SUMIFS(Transactions!$K$2:$K$104, Transactions!$C$2:$C$104, "2025-01", Transactions!$D$2:$D$104, "&lt;&gt;Transfer")</f>
         <v/>
       </c>
     </row>
@@ -1736,176 +1746,176 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="C26" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>-3</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Mobilität</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B27" s="7" t="n">
-        <v>4200</v>
-      </c>
-      <c r="C27" s="7" t="n">
+      <c r="B28" s="7" t="n">
+        <v>4428.4</v>
+      </c>
+      <c r="C28" s="7" t="n">
         <v>2211.7</v>
       </c>
-      <c r="D27" s="7" t="n">
-        <v>1988.3</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>Check (Transactions)</t>
-        </is>
-      </c>
-      <c r="B28" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-02", Transactions!$D$2:$D$90, "&lt;&gt;Transfer")</f>
-        <v/>
-      </c>
-      <c r="C28" s="9">
-        <f>SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-02", Transactions!$D$2:$D$90, "&lt;&gt;Transfer")</f>
-        <v/>
-      </c>
-      <c r="D28" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-02", Transactions!$D$2:$D$90, "&lt;&gt;Transfer") - SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-02", Transactions!$D$2:$D$90, "&lt;&gt;Transfer")</f>
-        <v/>
+      <c r="D28" s="7" t="n">
+        <v>2216.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
+          <t>Check (Transactions)</t>
+        </is>
+      </c>
+      <c r="B29" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$104, Transactions!$C$2:$C$104, "2025-02", Transactions!$D$2:$D$104, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+      <c r="C29" s="9">
+        <f>SUMIFS(Transactions!$K$2:$K$104, Transactions!$C$2:$C$104, "2025-02", Transactions!$D$2:$D$104, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+      <c r="D29" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$104, Transactions!$C$2:$C$104, "2025-02", Transactions!$D$2:$D$104, "&lt;&gt;Transfer") - SUMIFS(Transactions!$K$2:$K$104, Transactions!$C$2:$C$104, "2025-02", Transactions!$D$2:$D$104, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
           <t>Difference</t>
         </is>
       </c>
-      <c r="B29" s="9">
-        <f>B28-B27</f>
+      <c r="B30" s="9">
+        <f>B29-B28</f>
         <v/>
       </c>
-      <c r="C29" s="9">
-        <f>C28-C27</f>
+      <c r="C30" s="9">
+        <f>C29-C28</f>
         <v/>
       </c>
-      <c r="D29" s="9">
-        <f>D28-D27</f>
+      <c r="D30" s="9">
+        <f>D29-D28</f>
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>March 2025</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Credit in CHF</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>Debit in CHF</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>Net in CHF</t>
         </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Einkommen</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>5700</v>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>5700</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1787.95</v>
+        <v>5700</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>418.55</v>
+        <v>0</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>1369.4</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>0</v>
+        <v>1787.95</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>1898.02</v>
+        <v>418.55</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>-1898.02</v>
+        <v>1369.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>352.79</v>
+        <v>1898.02</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>-352.79</v>
+        <v>-1898.02</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>165.5</v>
+        <v>352.79</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>-165.5</v>
+        <v>-352.79</v>
       </c>
     </row>
     <row r="40">
@@ -1915,293 +1925,325 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>0</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="C40" s="5" t="n">
         <v>96.90000000000001</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>-96.90000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>12.4</v>
+        <v>165.5</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>-12.4</v>
+        <v>-165.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>-12.4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>Finanzen</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" s="5" t="n">
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D42" s="5" t="n">
+      <c r="D43" s="5" t="n">
         <v>-5</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B43" s="7" t="n">
-        <v>7487.95</v>
-      </c>
-      <c r="C43" s="7" t="n">
+      <c r="B44" s="7" t="n">
+        <v>7584.85</v>
+      </c>
+      <c r="C44" s="7" t="n">
         <v>2949.16</v>
       </c>
-      <c r="D43" s="7" t="n">
-        <v>4538.79</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>Check (Transactions)</t>
-        </is>
-      </c>
-      <c r="B44" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-03", Transactions!$D$2:$D$90, "&lt;&gt;Transfer")</f>
-        <v/>
-      </c>
-      <c r="C44" s="9">
-        <f>SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-03", Transactions!$D$2:$D$90, "&lt;&gt;Transfer")</f>
-        <v/>
-      </c>
-      <c r="D44" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-03", Transactions!$D$2:$D$90, "&lt;&gt;Transfer") - SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-03", Transactions!$D$2:$D$90, "&lt;&gt;Transfer")</f>
-        <v/>
+      <c r="D44" s="7" t="n">
+        <v>4635.69</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
+          <t>Check (Transactions)</t>
+        </is>
+      </c>
+      <c r="B45" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$104, Transactions!$C$2:$C$104, "2025-03", Transactions!$D$2:$D$104, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+      <c r="C45" s="9">
+        <f>SUMIFS(Transactions!$K$2:$K$104, Transactions!$C$2:$C$104, "2025-03", Transactions!$D$2:$D$104, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+      <c r="D45" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$104, Transactions!$C$2:$C$104, "2025-03", Transactions!$D$2:$D$104, "&lt;&gt;Transfer") - SUMIFS(Transactions!$K$2:$K$104, Transactions!$C$2:$C$104, "2025-03", Transactions!$D$2:$D$104, "&lt;&gt;Transfer")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
           <t>Difference</t>
         </is>
       </c>
-      <c r="B45" s="9">
-        <f>B44-B43</f>
+      <c r="B46" s="9">
+        <f>B45-B44</f>
         <v/>
       </c>
-      <c r="C45" s="9">
-        <f>C44-C43</f>
+      <c r="C46" s="9">
+        <f>C45-C44</f>
         <v/>
       </c>
-      <c r="D45" s="9">
-        <f>D44-D43</f>
+      <c r="D46" s="9">
+        <f>D45-D44</f>
         <v/>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>April 2025</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Credit in CHF</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>Debit in CHF</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>Net in CHF</t>
         </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Einkommen</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="n">
-        <v>4200</v>
-      </c>
-      <c r="C51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>4200</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>0</v>
+        <v>9400</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>1774</v>
+        <v>0</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>-1774</v>
+        <v>9400</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="B53" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>361.65</v>
+        <v>1774</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>-361.65</v>
+        <v>-1774</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Finanzen</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>168.5</v>
+        <v>361.65</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>-168.5</v>
+        <v>-361.65</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Finanzen</t>
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>0</v>
+        <v>168.5</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>135</v>
+        <v>-168.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>69.05</v>
+        <v>135</v>
       </c>
       <c r="C56" s="5" t="n">
-        <v>46.2</v>
+        <v>0</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>22.85</v>
+        <v>135</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>22.85</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>Freizeit</t>
         </is>
       </c>
-      <c r="B57" s="5" t="n">
+      <c r="B58" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="C57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="5" t="n">
+      <c r="C58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="5" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Mobilität</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B58" s="7" t="n">
-        <v>4504.05</v>
-      </c>
-      <c r="C58" s="7" t="n">
+      <c r="B60" s="7" t="n">
+        <v>9749.549999999999</v>
+      </c>
+      <c r="C60" s="7" t="n">
         <v>2350.35</v>
       </c>
-      <c r="D58" s="7" t="n">
-        <v>2153.7</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+      <c r="D60" s="7" t="n">
+        <v>7399.2</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>Check (Transactions)</t>
         </is>
       </c>
-      <c r="B59" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-04", Transactions!$D$2:$D$90, "&lt;&gt;Transfer")</f>
+      <c r="B61" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$104, Transactions!$C$2:$C$104, "2025-04", Transactions!$D$2:$D$104, "&lt;&gt;Transfer")</f>
         <v/>
       </c>
-      <c r="C59" s="9">
-        <f>SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-04", Transactions!$D$2:$D$90, "&lt;&gt;Transfer")</f>
+      <c r="C61" s="9">
+        <f>SUMIFS(Transactions!$K$2:$K$104, Transactions!$C$2:$C$104, "2025-04", Transactions!$D$2:$D$104, "&lt;&gt;Transfer")</f>
         <v/>
       </c>
-      <c r="D59" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-04", Transactions!$D$2:$D$90, "&lt;&gt;Transfer") - SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-04", Transactions!$D$2:$D$90, "&lt;&gt;Transfer")</f>
+      <c r="D61" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$104, Transactions!$C$2:$C$104, "2025-04", Transactions!$D$2:$D$104, "&lt;&gt;Transfer") - SUMIFS(Transactions!$K$2:$K$104, Transactions!$C$2:$C$104, "2025-04", Transactions!$D$2:$D$104, "&lt;&gt;Transfer")</f>
         <v/>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="8" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>Difference</t>
         </is>
       </c>
-      <c r="B60" s="9">
-        <f>B59-B58</f>
+      <c r="B62" s="9">
+        <f>B61-B60</f>
         <v/>
       </c>
-      <c r="C60" s="9">
-        <f>C59-C58</f>
+      <c r="C62" s="9">
+        <f>C61-C60</f>
         <v/>
       </c>
-      <c r="D60" s="9">
-        <f>D59-D58</f>
+      <c r="D62" s="9">
+        <f>D61-D60</f>
         <v/>
       </c>
     </row>
@@ -2216,7 +2258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2307,97 +2349,97 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>4200</v>
+        <v>4000</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>4200</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Familienzulage</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>24.5</v>
+        <v>0</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-24.5</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Familie</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>19</v>
+        <v>24.5</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-19</v>
+        <v>-24.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mobilität</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Privater Verkehr</t>
+          <t>Familie</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>26.7</v>
+        <v>19</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-26.7</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Mobilität</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Miete und Hypothek</t>
+          <t>Privater Verkehr</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1774</v>
+        <v>26.7</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>-1774</v>
+        <v>-26.7</v>
       </c>
     </row>
     <row r="14">
@@ -2408,943 +2450,1153 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>Miete und Hypothek</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>1774</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1774</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>Haushalt</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="5" t="n">
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="n">
         <v>45.1</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E15" s="5" t="n">
         <v>-45.1</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C16" s="7" t="n">
         <v>4200</v>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D16" s="7" t="n">
         <v>2222.35</v>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="E16" s="7" t="n">
         <v>1977.65</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Check (Transactions)</t>
-        </is>
-      </c>
-      <c r="C16" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-01", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;")</f>
-        <v/>
-      </c>
-      <c r="D16" s="9">
-        <f>SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-01", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;")</f>
-        <v/>
-      </c>
-      <c r="E16" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-01", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;") - SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-01", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;")</f>
-        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
+          <t>Check (Transactions)</t>
+        </is>
+      </c>
+      <c r="C17" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$104, Transactions!$C$2:$C$104, "2025-01", Transactions!$D$2:$D$104, "&lt;&gt;Transfer", Transactions!$F$2:$F$104, "&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D17" s="9">
+        <f>SUMIFS(Transactions!$K$2:$K$104, Transactions!$C$2:$C$104, "2025-01", Transactions!$D$2:$D$104, "&lt;&gt;Transfer", Transactions!$F$2:$F$104, "&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="E17" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$104, Transactions!$C$2:$C$104, "2025-01", Transactions!$D$2:$D$104, "&lt;&gt;Transfer", Transactions!$F$2:$F$104, "&lt;&gt;") - SUMIFS(Transactions!$K$2:$K$104, Transactions!$C$2:$C$104, "2025-01", Transactions!$D$2:$D$104, "&lt;&gt;Transfer", Transactions!$F$2:$F$104, "&lt;&gt;")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
           <t>Difference</t>
         </is>
       </c>
-      <c r="C17" s="9">
-        <f>C16-C15</f>
+      <c r="C18" s="9">
+        <f>C17-C16</f>
         <v/>
       </c>
-      <c r="D17" s="9">
-        <f>D16-D15</f>
+      <c r="D18" s="9">
+        <f>D17-D16</f>
         <v/>
       </c>
-      <c r="E17" s="9">
-        <f>E16-E15</f>
+      <c r="E18" s="9">
+        <f>E17-E16</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>February 2025</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Subcategory</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Credit in CHF</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Debit in CHF</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Net in CHF</t>
         </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Einkaufen</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Supermärkte</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>434.7</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>-434.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Einkommen</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lohn</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>0</v>
+        <v>434.7</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>4200</v>
+        <v>-434.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Lohn</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>-3</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Einkommen</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Familienzulage</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Reisen und Erleben</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Gastronomie</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Mobilität</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Öffentlicher Verkehr</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Wohnen</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Miete und Hypothek</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="5" t="n">
+      <c r="C30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="5" t="n">
         <v>1774</v>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="E30" s="5" t="n">
         <v>-1774</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C27" s="7" t="n">
-        <v>4200</v>
-      </c>
-      <c r="D27" s="7" t="n">
+      <c r="C31" s="7" t="n">
+        <v>4428.4</v>
+      </c>
+      <c r="D31" s="7" t="n">
         <v>2211.7</v>
       </c>
-      <c r="E27" s="7" t="n">
-        <v>1988.3</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="E31" s="7" t="n">
+        <v>2216.7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>Check (Transactions)</t>
         </is>
       </c>
-      <c r="C28" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-02", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;")</f>
+      <c r="C32" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$104, Transactions!$C$2:$C$104, "2025-02", Transactions!$D$2:$D$104, "&lt;&gt;Transfer", Transactions!$F$2:$F$104, "&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D28" s="9">
-        <f>SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-02", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;")</f>
+      <c r="D32" s="9">
+        <f>SUMIFS(Transactions!$K$2:$K$104, Transactions!$C$2:$C$104, "2025-02", Transactions!$D$2:$D$104, "&lt;&gt;Transfer", Transactions!$F$2:$F$104, "&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="E28" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-02", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;") - SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-02", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;")</f>
+      <c r="E32" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$104, Transactions!$C$2:$C$104, "2025-02", Transactions!$D$2:$D$104, "&lt;&gt;Transfer", Transactions!$F$2:$F$104, "&lt;&gt;") - SUMIFS(Transactions!$K$2:$K$104, Transactions!$C$2:$C$104, "2025-02", Transactions!$D$2:$D$104, "&lt;&gt;Transfer", Transactions!$F$2:$F$104, "&lt;&gt;")</f>
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>Difference</t>
         </is>
       </c>
-      <c r="C29" s="9">
-        <f>C28-C27</f>
+      <c r="C33" s="9">
+        <f>C32-C31</f>
         <v/>
       </c>
-      <c r="D29" s="9">
-        <f>D28-D27</f>
+      <c r="D33" s="9">
+        <f>D32-D31</f>
         <v/>
       </c>
-      <c r="E29" s="9">
-        <f>E28-E27</f>
+      <c r="E33" s="9">
+        <f>E32-E31</f>
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>March 2025</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>Subcategory</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>Credit in CHF</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>Debit in CHF</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>Net in CHF</t>
         </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Einkaufen</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Supermärkte</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>170.85</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>-170.85</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Einkaufen</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Detail-Lebensmittel</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>167.29</v>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>-167.29</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Einkaufen</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Sonstiges Einkaufen</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>14.65</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>-14.65</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Einkommen</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Lohn</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="n">
-        <v>5700</v>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="5" t="n">
-        <v>5700</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Finanzen</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>5</v>
+        <v>170.85</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>-5</v>
+        <v>-170.85</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>150.5</v>
+        <v>167.29</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>-150.5</v>
+        <v>-167.29</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kultur</t>
+          <t>Sonstiges Einkaufen</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>15</v>
+        <v>14.65</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>-15</v>
+        <v>-14.65</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Krankenkasse</t>
+          <t>Lohn</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>1787.95</v>
+        <v>4000</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>77.45</v>
+        <v>0</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>1710.5</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Familie</t>
+          <t>Bonus</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>-200</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Styling und Wellness</t>
+          <t>Familienzulage</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>79.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>-79.90000000000001</v>
+        <v>200</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Finanzen</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sonstiges Leben</t>
+          <t>Fees</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>36.8</v>
+        <v>5</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>-36.8</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Gesundheit</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>24.4</v>
+        <v>150.5</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>-24.4</v>
+        <v>-150.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Mobilität</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Öffentlicher Verkehr</t>
+          <t>Kultur</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>96.90000000000001</v>
+        <v>15</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>-96.90000000000001</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Miete und Hypothek</t>
+          <t>Krankenkasse</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
-        <v>0</v>
+        <v>1787.95</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>1774</v>
+        <v>77.45</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>-1774</v>
+        <v>1710.5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kommunikation</t>
+          <t>Familie</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>70.27</v>
+        <v>200</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>-70.27</v>
+        <v>-200</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Haushalt</t>
+          <t>Styling und Wellness</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>42.85</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>-42.85</v>
+        <v>-79.90000000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Sonstiges Leben</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>-36.8</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Gesundheit</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>-24.4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Mobilität</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Öffentlicher Verkehr</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>Wohnen</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Miete und Hypothek</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>1774</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>-1774</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Kommunikation</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>70.27</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>-70.27</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Haushalt</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>42.85</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>-42.85</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
         <is>
           <t>Handwerk und Garten</t>
         </is>
       </c>
-      <c r="C51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="5" t="n">
+      <c r="C57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="5" t="n">
         <v>10.9</v>
       </c>
-      <c r="E51" s="5" t="n">
+      <c r="E57" s="5" t="n">
         <v>-10.9</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C52" s="7" t="n">
-        <v>7487.95</v>
-      </c>
-      <c r="D52" s="7" t="n">
+      <c r="C58" s="7" t="n">
+        <v>7584.85</v>
+      </c>
+      <c r="D58" s="7" t="n">
         <v>2936.76</v>
       </c>
-      <c r="E52" s="7" t="n">
-        <v>4551.19</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="E58" s="7" t="n">
+        <v>4648.09</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>Check (Transactions)</t>
         </is>
       </c>
-      <c r="C53" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-03", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;")</f>
+      <c r="C59" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$104, Transactions!$C$2:$C$104, "2025-03", Transactions!$D$2:$D$104, "&lt;&gt;Transfer", Transactions!$F$2:$F$104, "&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D53" s="9">
-        <f>SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-03", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;")</f>
+      <c r="D59" s="9">
+        <f>SUMIFS(Transactions!$K$2:$K$104, Transactions!$C$2:$C$104, "2025-03", Transactions!$D$2:$D$104, "&lt;&gt;Transfer", Transactions!$F$2:$F$104, "&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="E53" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-03", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;") - SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-03", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;")</f>
+      <c r="E59" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$104, Transactions!$C$2:$C$104, "2025-03", Transactions!$D$2:$D$104, "&lt;&gt;Transfer", Transactions!$F$2:$F$104, "&lt;&gt;") - SUMIFS(Transactions!$K$2:$K$104, Transactions!$C$2:$C$104, "2025-03", Transactions!$D$2:$D$104, "&lt;&gt;Transfer", Transactions!$F$2:$F$104, "&lt;&gt;")</f>
         <v/>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>Difference</t>
         </is>
       </c>
-      <c r="C54" s="9">
-        <f>C53-C52</f>
+      <c r="C60" s="9">
+        <f>C59-C58</f>
         <v/>
       </c>
-      <c r="D54" s="9">
-        <f>D53-D52</f>
+      <c r="D60" s="9">
+        <f>D59-D58</f>
         <v/>
       </c>
-      <c r="E54" s="9">
-        <f>E53-E52</f>
+      <c r="E60" s="9">
+        <f>E59-E58</f>
         <v/>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>April 2025</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>Subcategory</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>Credit in CHF</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>Debit in CHF</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E65" s="4" t="inlineStr">
         <is>
           <t>Net in CHF</t>
         </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Einkaufen</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Supermärkte</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" s="5" t="n">
-        <v>361.65</v>
-      </c>
-      <c r="E60" s="5" t="n">
-        <v>-361.65</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Einkommen</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Lohn</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="n">
-        <v>4200</v>
-      </c>
-      <c r="D61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="5" t="n">
-        <v>4200</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Finanzen</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Bargeldbezug</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="5" t="n">
-        <v>143.5</v>
-      </c>
-      <c r="E62" s="5" t="n">
-        <v>-143.5</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Finanzen</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Spenden</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="E63" s="5" t="n">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Freizeit</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Reisen und Erleben</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="D64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="5" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Leben</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Krankenkasse</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="D65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="5" t="n">
-        <v>120</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Familie</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="C66" s="5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>0</v>
+        <v>361.65</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>15</v>
+        <v>-361.65</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>Einkommen</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Nebenerwerb</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>4200</v>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Einkommen</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Lohn</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Einkommen</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Einkommen</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Familienzulage</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="D70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Finanzen</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Bargeldbezug</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>-143.5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Finanzen</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Spenden</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Reisen und Erleben</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Krankenkasse</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Familie</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Mobilität</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Öffentlicher Verkehr</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>Wohnen</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>Miete und Hypothek</t>
         </is>
       </c>
-      <c r="C67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" s="5" t="n">
+      <c r="C77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="5" t="n">
         <v>1774</v>
       </c>
-      <c r="E67" s="5" t="n">
+      <c r="E77" s="5" t="n">
         <v>-1774</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="6" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C68" s="7" t="n">
-        <v>4435</v>
-      </c>
-      <c r="D68" s="7" t="n">
+      <c r="C78" s="7" t="n">
+        <v>9680.5</v>
+      </c>
+      <c r="D78" s="7" t="n">
         <v>2304.15</v>
       </c>
-      <c r="E68" s="7" t="n">
-        <v>2130.85</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="8" t="inlineStr">
+      <c r="E78" s="7" t="n">
+        <v>7376.35</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
         <is>
           <t>Check (Transactions)</t>
         </is>
       </c>
-      <c r="C69" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-04", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;")</f>
+      <c r="C79" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$104, Transactions!$C$2:$C$104, "2025-04", Transactions!$D$2:$D$104, "&lt;&gt;Transfer", Transactions!$F$2:$F$104, "&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D69" s="9">
-        <f>SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-04", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;")</f>
+      <c r="D79" s="9">
+        <f>SUMIFS(Transactions!$K$2:$K$104, Transactions!$C$2:$C$104, "2025-04", Transactions!$D$2:$D$104, "&lt;&gt;Transfer", Transactions!$F$2:$F$104, "&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="E69" s="9">
-        <f>SUMIFS(Transactions!$J$2:$J$90, Transactions!$C$2:$C$90, "2025-04", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;") - SUMIFS(Transactions!$K$2:$K$90, Transactions!$C$2:$C$90, "2025-04", Transactions!$D$2:$D$90, "&lt;&gt;Transfer", Transactions!$F$2:$F$90, "&lt;&gt;")</f>
+      <c r="E79" s="9">
+        <f>SUMIFS(Transactions!$J$2:$J$104, Transactions!$C$2:$C$104, "2025-04", Transactions!$D$2:$D$104, "&lt;&gt;Transfer", Transactions!$F$2:$F$104, "&lt;&gt;") - SUMIFS(Transactions!$K$2:$K$104, Transactions!$C$2:$C$104, "2025-04", Transactions!$D$2:$D$104, "&lt;&gt;Transfer", Transactions!$F$2:$F$104, "&lt;&gt;")</f>
         <v/>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="8" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
         <is>
           <t>Difference</t>
         </is>
       </c>
-      <c r="C70" s="9">
-        <f>C69-C68</f>
+      <c r="C80" s="9">
+        <f>C79-C78</f>
         <v/>
       </c>
-      <c r="D70" s="9">
-        <f>D69-D68</f>
+      <c r="D80" s="9">
+        <f>D79-D78</f>
         <v/>
       </c>
-      <c r="E70" s="9">
-        <f>E69-E68</f>
+      <c r="E80" s="9">
+        <f>E79-E78</f>
         <v/>
       </c>
     </row>
@@ -3359,7 +3611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N90"/>
+  <dimension ref="A1:N104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3999,7 +4251,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TX-000070</t>
+          <t>TX-000070.1</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
@@ -4022,12 +4274,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lohn</t>
+          <t>Familienzulage</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Einkommen / Lohn</t>
+          <t>Einkommen / Familienzulage</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -4041,13 +4293,13 @@
         </is>
       </c>
       <c r="J11" s="5" t="n">
-        <v>4200</v>
+        <v>200</v>
       </c>
       <c r="K11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>-4200</v>
+        <v>-200</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -4063,11 +4315,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TX-000075</t>
+          <t>TX-000070.2</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>45685</v>
+        <v>45682</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -4076,41 +4328,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Supermärkte</t>
+          <t>Lohn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Einkaufen / Supermärkte</t>
+          <t>Einkommen / Lohn</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>MIGROS MARKTHALLE (8812)</t>
+          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SALAER JANUAR 2025 | SALA00000000000000000000000000000001 9988776655/1XXXX 250125CH0EXMPL01</t>
         </is>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>96.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>96.40000000000001</v>
+        <v>-4000</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>supermarket_1</t>
+          <t>income_1</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -4122,11 +4379,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TX-000074</t>
+          <t>TX-000091</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
-        <v>45688</v>
+        <v>45683</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -4135,46 +4392,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Transfer</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Vorsorge</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Miete und Hypothek</t>
+          <t>Säule 3a</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Wohnen / Miete und Hypothek</t>
+          <t>Vorsorge / Säule 3a</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>FINANZVERWALTUNG STADT SOLOTHURN</t>
+          <t>VORSORGESTIFTUNG MUSTERHAUSEN SENDER REFERENZ: SAEULE 3A</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2025/02/01 / 7045128</t>
+          <t>90-11223344</t>
         </is>
       </c>
       <c r="J13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>1774</v>
+        <v>200</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>1774</v>
+        <v>200</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>housing_1</t>
+          <t>savings_1</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -4186,15 +4443,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TX-000083</t>
+          <t>TX-000075</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
-        <v>45689</v>
+        <v>45685</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4219,17 +4476,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>MIGROS M RIVERSIDE (7741)</t>
+          <t>MIGROS MARKTHALLE (8812)</t>
         </is>
       </c>
       <c r="J14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>63.75</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>63.75</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4238,22 +4495,22 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>export.202502.categorized.csv</t>
+          <t>export.202501.categorized.csv</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TX-000082</t>
+          <t>TX-000074</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>45696</v>
+        <v>45688</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4263,52 +4520,57 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Supermärkte</t>
+          <t>Miete und Hypothek</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Einkaufen / Supermärkte</t>
+          <t>Wohnen / Miete und Hypothek</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>MIGROS MARKTHALLE (8812)</t>
+          <t>FINANZVERWALTUNG STADT SOLOTHURN</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2025/02/01 / 7045128</t>
         </is>
       </c>
       <c r="J15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>127.4</v>
+        <v>1774</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>127.4</v>
+        <v>1774</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>supermarket_1</t>
+          <t>housing_1</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>export.202502.categorized.csv</t>
+          <t>export.202501.categorized.csv</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TX-000081</t>
+          <t>TX-000083</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
-        <v>45702</v>
+        <v>45689</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -4337,17 +4599,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>COOP-5510 RIVERSIDE REST.</t>
+          <t>MIGROS M RIVERSIDE (7741)</t>
         </is>
       </c>
       <c r="J16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>88.95</v>
+        <v>63.75</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>88.95</v>
+        <v>63.75</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4363,11 +4625,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TX-000080</t>
+          <t>TX-000082</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
-        <v>45710</v>
+        <v>45696</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -4403,10 +4665,10 @@
         <v>0</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>154.6</v>
+        <v>127.4</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>154.6</v>
+        <v>127.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4422,11 +4684,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TX-000071</t>
+          <t>TX-000081</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
-        <v>45713</v>
+        <v>45702</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -4435,46 +4697,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Einkommen</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lohn</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Einkommen / Lohn</t>
+          <t>Einkaufen / Supermärkte</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>SALAER FEBRUAR 2025 | SALA00000000000000000000000000000002 9988776655/1XXXX 250225CH0EXMPL02</t>
+          <t>COOP-5510 RIVERSIDE REST.</t>
         </is>
       </c>
       <c r="J18" s="5" t="n">
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0</v>
+        <v>88.95</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>-4200</v>
+        <v>88.95</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>income_1</t>
+          <t>supermarket_1</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -4486,11 +4743,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TX-000060</t>
+          <t>TX-000080</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
-        <v>45715</v>
+        <v>45710</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -4504,36 +4761,36 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Freizeit / Gastronomie</t>
+          <t>Einkaufen / Supermärkte</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>MUSTER CAFE</t>
+          <t>MIGROS MARKTHALLE (8812)</t>
         </is>
       </c>
       <c r="J19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>3</v>
+        <v>154.6</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>3</v>
+        <v>154.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>gastronomy_6</t>
+          <t>supermarket_1</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -4545,11 +4802,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TX-000079</t>
+          <t>TX-000071.1</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
-        <v>45716</v>
+        <v>45713</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -4558,46 +4815,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Miete und Hypothek</t>
+          <t>Familienzulage</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Wohnen / Miete und Hypothek</t>
+          <t>Einkommen / Familienzulage</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>FINANZVERWALTUNG STADT SOLOTHURN</t>
+          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2025/03/01 / 7045128</t>
+          <t>SALAER FEBRUAR 2025 | SALA00000000000000000000000000000002 9988776655/1XXXX 250225CH0EXMPL02</t>
         </is>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>1774</v>
+        <v>0</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>1774</v>
+        <v>-200</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>housing_1</t>
+          <t>income_1</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -4609,246 +4866,271 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TX-000054</t>
+          <t>TX-000071.2</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
-        <v>45738</v>
+        <v>45713</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Lohn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Freizeit / Gastronomie</t>
+          <t>Einkommen / Lohn</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>+41790000000 MAX MUSTER</t>
+          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MITTEILUNGEN: ESSEN GESTERN ABEND</t>
+          <t>SALAER FEBRUAR 2025 | SALA00000000000000000000000000000002 9988776655/1XXXX 250225CH0EXMPL02</t>
         </is>
       </c>
       <c r="J21" s="5" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>20</v>
+        <v>-4000</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>gastronomy_5</t>
+          <t>income_1</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>export.202503.categorized.csv</t>
+          <t>export.202502.categorized.csv</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TX-000055</t>
+          <t>TX-000071.3</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
-        <v>45738</v>
+        <v>45713</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Refund</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Reisen und Erleben</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Freizeit / Reisen und Erleben</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>UNMATCHED TEST STORE</t>
+          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>SALAER FEBRUAR 2025 | SALA00000000000000000000000000000002 9988776655/1XXXX 250225CH0EXMPL02</t>
         </is>
       </c>
       <c r="J22" s="5" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>12.4</v>
+        <v>0</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>12.4</v>
+        <v>-180</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>income_1</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>export.202503.categorized.csv</t>
+          <t>export.202502.categorized.csv</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TX-000051</t>
+          <t>TX-000071.4</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
-        <v>45739</v>
+        <v>45713</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Refund</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Mobilität</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Detail-Lebensmittel</t>
+          <t>Öffentlicher Verkehr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Einkaufen / Detail-Lebensmittel</t>
+          <t>Mobilität / Öffentlicher Verkehr</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>BÄCKEREI HUG</t>
+          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>SALAER FEBRUAR 2025 | SALA00000000000000000000000000000002 9988776655/1XXXX 250225CH0EXMPL02</t>
         </is>
       </c>
       <c r="J23" s="5" t="n">
-        <v>0</v>
+        <v>48.4</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>17.3</v>
+        <v>0</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>17.3</v>
+        <v>-48.4</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>grocery_1</t>
+          <t>income_1</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>export.202503.categorized.csv</t>
+          <t>export.202502.categorized.csv</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TX-000052</t>
+          <t>TX-000092</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
-        <v>45739</v>
+        <v>45714</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Transfer</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Vorsorge</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Haushalt</t>
+          <t>Säule 3a</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Wohnen / Haushalt</t>
+          <t>Vorsorge / Säule 3a</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>MANOR AG - 771 (CENTRA)</t>
+          <t>VORSORGESTIFTUNG MUSTERHAUSEN SENDER REFERENZ: SAEULE 3A</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>90-11223344</t>
         </is>
       </c>
       <c r="J24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>23.95</v>
+        <v>200</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>23.95</v>
+        <v>200</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>home_2</t>
+          <t>savings_1</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>export.202503.categorized.csv</t>
+          <t>export.202502.categorized.csv</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TX-000053</t>
+          <t>TX-000060</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
-        <v>45739</v>
+        <v>45715</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4873,41 +5155,41 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>+41796666222 KEBAB, IMBISS</t>
+          <t>MUSTER CAFE</t>
         </is>
       </c>
       <c r="J25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>13.5</v>
+        <v>3</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>13.5</v>
+        <v>3</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>gastronomy_4</t>
+          <t>gastronomy_6</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>export.202503.categorized.csv</t>
+          <t>export.202502.categorized.csv</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TX-000045</t>
+          <t>TX-000079</t>
         </is>
       </c>
       <c r="B26" s="11" t="n">
-        <v>45740</v>
+        <v>45716</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4917,52 +5199,57 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Detail-Lebensmittel</t>
+          <t>Miete und Hypothek</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Einkaufen / Detail-Lebensmittel</t>
+          <t>Wohnen / Miete und Hypothek</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>WAKARA GMBH</t>
+          <t>FINANZVERWALTUNG STADT SOLOTHURN</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2025/03/01 / 7045128</t>
         </is>
       </c>
       <c r="J26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>27.6</v>
+        <v>1774</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>27.6</v>
+        <v>1774</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>grocery_2</t>
+          <t>housing_1</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>export.202503.categorized.csv</t>
+          <t>export.202502.categorized.csv</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TX-000046</t>
+          <t>TX-000054</t>
         </is>
       </c>
       <c r="B27" s="11" t="n">
-        <v>45740</v>
+        <v>45738</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4976,36 +5263,41 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Styling und Wellness</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leben / Styling und Wellness</t>
+          <t>Freizeit / Gastronomie</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>THE BODY SHOP</t>
+          <t>+41790000000 MAX MUSTER</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>MITTEILUNGEN: ESSEN GESTERN ABEND</t>
         </is>
       </c>
       <c r="J27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>4.95</v>
+        <v>20</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>4.95</v>
+        <v>20</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>wellness_1</t>
+          <t>gastronomy_5</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -5017,54 +5309,44 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TX-000047</t>
+          <t>TX-000055</t>
         </is>
       </c>
       <c r="B28" s="11" t="n">
-        <v>45740</v>
+        <v>45738</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Supermärkte</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Einkaufen / Supermärkte</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>COOP-5510 RIVERSIDE REST.</t>
+          <t>UNMATCHED TEST STORE</t>
         </is>
       </c>
       <c r="J28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>44</v>
+        <v>12.4</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>44</v>
+        <v>12.4</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>supermarket_1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -5076,11 +5358,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TX-000048.1</t>
+          <t>TX-000051</t>
         </is>
       </c>
       <c r="B29" s="11" t="n">
-        <v>45740</v>
+        <v>45739</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -5094,36 +5376,36 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Haushalt</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Wohnen / Haushalt</t>
+          <t>Einkaufen / Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>MIGROS MARKTHALLE (8812)</t>
+          <t>BÄCKEREI HUG</t>
         </is>
       </c>
       <c r="J29" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>18.9</v>
+        <v>17.3</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>18.9</v>
+        <v>17.3</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>supermarket_1</t>
+          <t>grocery_1</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -5135,11 +5417,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TX-000048.2</t>
+          <t>TX-000052</t>
         </is>
       </c>
       <c r="B30" s="11" t="n">
-        <v>45740</v>
+        <v>45739</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -5153,36 +5435,36 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Supermärkte</t>
+          <t>Haushalt</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Einkaufen / Supermärkte</t>
+          <t>Wohnen / Haushalt</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>MIGROS MARKTHALLE (8812)</t>
+          <t>MANOR AG - 771 (CENTRA)</t>
         </is>
       </c>
       <c r="J30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>34.6</v>
+        <v>23.95</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>34.6</v>
+        <v>23.95</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>supermarket_1</t>
+          <t>home_2</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -5194,11 +5476,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TX-000049</t>
+          <t>TX-000053</t>
         </is>
       </c>
       <c r="B31" s="11" t="n">
-        <v>45740</v>
+        <v>45739</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -5227,21 +5509,21 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>MIGROS CITY TAKE AWAY (6624)</t>
+          <t>+41796666222 KEBAB, IMBISS</t>
         </is>
       </c>
       <c r="J31" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>gastronomy_1</t>
+          <t>gastronomy_4</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -5253,7 +5535,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TX-000050</t>
+          <t>TX-000045</t>
         </is>
       </c>
       <c r="B32" s="11" t="n">
@@ -5271,36 +5553,36 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Krankenkasse</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leben / Krankenkasse</t>
+          <t>Einkaufen / Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>MEDICURA PLUS AG GESUNDHEITSWEG 8 4052 BASEL</t>
+          <t>WAKARA GMBH</t>
         </is>
       </c>
       <c r="J32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>77.45</v>
+        <v>27.6</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>77.45</v>
+        <v>27.6</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>health_2</t>
+          <t>grocery_2</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -5312,11 +5594,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TX-000039</t>
+          <t>TX-000046</t>
         </is>
       </c>
       <c r="B33" s="11" t="n">
-        <v>45741</v>
+        <v>45740</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5330,36 +5612,36 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Detail-Lebensmittel</t>
+          <t>Styling und Wellness</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Einkaufen / Detail-Lebensmittel</t>
+          <t>Leben / Styling und Wellness</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>BÄCKEREI HUG</t>
+          <t>THE BODY SHOP</t>
         </is>
       </c>
       <c r="J33" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>6.1</v>
+        <v>4.95</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>6.1</v>
+        <v>4.95</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>grocery_1</t>
+          <t>wellness_1</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5371,11 +5653,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TX-000040</t>
+          <t>TX-000047</t>
         </is>
       </c>
       <c r="B34" s="11" t="n">
-        <v>45741</v>
+        <v>45740</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5394,31 +5676,31 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Detail-Lebensmittel</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Einkaufen / Detail-Lebensmittel</t>
+          <t>Einkaufen / Supermärkte</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>BRANKOVIC BREZELSTUBE</t>
+          <t>COOP-5510 RIVERSIDE REST.</t>
         </is>
       </c>
       <c r="J34" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>4.3</v>
+        <v>44</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>4.3</v>
+        <v>44</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>grocery_1</t>
+          <t>supermarket_1</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5430,11 +5712,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TX-000041</t>
+          <t>TX-000048.1</t>
         </is>
       </c>
       <c r="B35" s="11" t="n">
-        <v>45741</v>
+        <v>45740</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5448,32 +5730,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Supermärkte</t>
+          <t>Haushalt</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Einkaufen / Supermärkte</t>
+          <t>Wohnen / Haushalt</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>MIGROS M RIVERSIDE (7741)</t>
+          <t>MIGROS MARKTHALLE (8812)</t>
         </is>
       </c>
       <c r="J35" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>10.35</v>
+        <v>18.9</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>10.35</v>
+        <v>18.9</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -5489,11 +5771,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TX-000043</t>
+          <t>TX-000048.2</t>
         </is>
       </c>
       <c r="B36" s="11" t="n">
-        <v>45741</v>
+        <v>45740</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5502,46 +5784,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Refund</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Krankenkasse</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leben / Krankenkasse</t>
+          <t>Einkaufen / Supermärkte</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>MEDICURA PLUS AG GESUNDHEITSWEG 8 4052 BASEL</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>LEISTUNGSABRECHNUNG NR.: 700112233445566 VERSICHERTE PERSON 445566 BETRIFFT LEISTUNGEN | MED95CB11F8253446278F81749F26F10588</t>
+          <t>MIGROS MARKTHALLE (8812)</t>
         </is>
       </c>
       <c r="J36" s="5" t="n">
-        <v>1787.95</v>
+        <v>0</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>0</v>
+        <v>34.6</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>-1787.95</v>
+        <v>34.6</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>refund_2</t>
+          <t>supermarket_1</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5553,11 +5830,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TX-000044</t>
+          <t>TX-000049</t>
         </is>
       </c>
       <c r="B37" s="11" t="n">
-        <v>45741</v>
+        <v>45740</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5571,36 +5848,36 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kommunikation</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Wohnen / Kommunikation</t>
+          <t>Freizeit / Gastronomie</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>CLOUDSERVICE INC SAN</t>
+          <t>MIGROS CITY TAKE AWAY (6624)</t>
         </is>
       </c>
       <c r="J37" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>18.67</v>
+        <v>6.8</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>18.67</v>
+        <v>6.8</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>communication_3</t>
+          <t>gastronomy_1</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5612,11 +5889,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TX-000058</t>
+          <t>TX-000050</t>
         </is>
       </c>
       <c r="B38" s="11" t="n">
-        <v>45741</v>
+        <v>45740</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5625,46 +5902,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Transfer</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Überträge</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Account Transfer</t>
+          <t>Krankenkasse</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Überträge / Account Transfer</t>
+          <t>Leben / Krankenkasse</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>EIGENES SPARKONTO KONTOUEBERTRAG TRANSFER-20250325</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>EIGENES SPARKONTO KONTOUEBERTRAG TRANSFER-20250325</t>
+          <t>MEDICURA PLUS AG GESUNDHEITSWEG 8 4052 BASEL</t>
         </is>
       </c>
       <c r="J38" s="5" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>0</v>
+        <v>77.45</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>-450</v>
+        <v>77.45</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>transfer_1</t>
+          <t>health_2</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5676,7 +5948,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TX-000072</t>
+          <t>TX-000039</t>
         </is>
       </c>
       <c r="B39" s="11" t="n">
@@ -5689,46 +5961,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Einkommen</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lohn</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Einkommen / Lohn</t>
+          <t>Einkaufen / Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>SALAER BONUS 2024 | SALA00000000000000000000000000000003 9988776655/1XXXX 250325CH0EXMPL03</t>
+          <t>BÄCKEREI HUG</t>
         </is>
       </c>
       <c r="J39" s="5" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>-1500</v>
+        <v>6.1</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>income_1</t>
+          <t>grocery_1</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5740,7 +6007,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TX-000073</t>
+          <t>TX-000040</t>
         </is>
       </c>
       <c r="B40" s="11" t="n">
@@ -5753,46 +6020,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Einkommen</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lohn</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Einkommen / Lohn</t>
+          <t>Einkaufen / Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>SALAER MAERZ 2025 | SALA80E5ED528784F48B451A4175649C112 9988776655/1XXXX 250325CH7LMNQRTS</t>
+          <t>BRANKOVIC BREZELSTUBE</t>
         </is>
       </c>
       <c r="J40" s="5" t="n">
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>-4200</v>
+        <v>4.3</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>income_1</t>
+          <t>grocery_1</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5804,11 +6066,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TX-000035</t>
+          <t>TX-000041</t>
         </is>
       </c>
       <c r="B41" s="11" t="n">
-        <v>45742</v>
+        <v>45741</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5822,36 +6084,36 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mobilität</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Öffentlicher Verkehr</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Mobilität / Öffentlicher Verkehr</t>
+          <t>Einkaufen / Supermärkte</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>TRANSPORTS PUBLICS FRIBOURGEOIS (FAIRTIQ) N/A PAYMENT ID 250326064915818975ZX BESTELLNUMMER</t>
+          <t>MIGROS M RIVERSIDE (7741)</t>
         </is>
       </c>
       <c r="J41" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>62.6</v>
+        <v>10.35</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>62.6</v>
+        <v>10.35</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>transport_1</t>
+          <t>supermarket_1</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -5863,11 +6125,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TX-000036</t>
+          <t>TX-000043</t>
         </is>
       </c>
       <c r="B42" s="11" t="n">
-        <v>45742</v>
+        <v>45741</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5876,41 +6138,46 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Refund</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Handwerk und Garten</t>
+          <t>Krankenkasse</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Wohnen / Handwerk und Garten</t>
+          <t>Leben / Krankenkasse</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>JUMBO-7782 INDUSTRIEPARK</t>
+          <t>MEDICURA PLUS AG GESUNDHEITSWEG 8 4052 BASEL</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>LEISTUNGSABRECHNUNG NR.: 700112233445566 VERSICHERTE PERSON 445566 BETRIFFT LEISTUNGEN | MED95CB11F8253446278F81749F26F10588</t>
         </is>
       </c>
       <c r="J42" s="5" t="n">
-        <v>0</v>
+        <v>1787.95</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>10.9</v>
+        <v>0</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>10.9</v>
+        <v>-1787.95</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>home_1</t>
+          <t>refund_2</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -5922,11 +6189,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TX-000037</t>
+          <t>TX-000044</t>
         </is>
       </c>
       <c r="B43" s="11" t="n">
-        <v>45742</v>
+        <v>45741</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5940,41 +6207,36 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Kommunikation</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Freizeit / Gastronomie</t>
+          <t>Wohnen / Kommunikation</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>+41796666222 KEBAB, IMBISS</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>MITTEILUNGEN: KEBAB</t>
+          <t>CLOUDSERVICE INC SAN</t>
         </is>
       </c>
       <c r="J43" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>14</v>
+        <v>18.67</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>14</v>
+        <v>18.67</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>gastronomy_4</t>
+          <t>communication_3</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5986,11 +6248,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TX-000038</t>
+          <t>TX-000058</t>
         </is>
       </c>
       <c r="B44" s="11" t="n">
-        <v>45742</v>
+        <v>45741</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5999,46 +6261,46 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Transfer</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Überträge</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Familie</t>
+          <t>Account Transfer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leben / Familie</t>
+          <t>Überträge / Account Transfer</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>FAMILIENKASSE MUSTERHAUSEN SENDER REFERENZ: FAMILIENZULAGE</t>
+          <t>EIGENES SPARKONTO KONTOUEBERTRAG TRANSFER-20250325</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>90-33445566</t>
+          <t>EIGENES SPARKONTO KONTOUEBERTRAG TRANSFER-20250325</t>
         </is>
       </c>
       <c r="J44" s="5" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>200</v>
+        <v>-450</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>family_1</t>
+          <t>transfer_1</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6050,11 +6312,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TX-000024</t>
+          <t>TX-000072</t>
         </is>
       </c>
       <c r="B45" s="11" t="n">
-        <v>45743</v>
+        <v>45741</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6063,41 +6325,46 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kommunikation</t>
+          <t>Bonus</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Wohnen / Kommunikation</t>
+          <t>Einkommen / Bonus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>APPLE.COM/BILL</t>
+          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>SALAER BONUS 2024 | SALA00000000000000000000000000000003 9988776655/1XXXX 250325CH0EXMPL03</t>
         </is>
       </c>
       <c r="J45" s="5" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>2</v>
+        <v>-1500</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>communication_2</t>
+          <t>income_2</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6109,11 +6376,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TX-000025</t>
+          <t>TX-000073.1</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
-        <v>45743</v>
+        <v>45741</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6122,41 +6389,46 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Familienzulage</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Freizeit / Gastronomie</t>
+          <t>Einkommen / Familienzulage</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>YOOJI'S ROSENGARTEN</t>
+          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>SALAER MAERZ 2025 | SALA80E5ED528784F48B451A4175649C112 9988776655/1XXXX 250325CH7LMNQRTS</t>
         </is>
       </c>
       <c r="J46" s="5" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>6.9</v>
+        <v>-200</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>gastronomy_2</t>
+          <t>income_1</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6168,11 +6440,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TX-000026</t>
+          <t>TX-000073.2</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
-        <v>45743</v>
+        <v>45741</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6181,41 +6453,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Einkommen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Detail-Lebensmittel</t>
+          <t>Lohn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Einkaufen / Detail-Lebensmittel</t>
+          <t>Einkommen / Lohn</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>CONFISERIE SPRÜNGLI AG</t>
+          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>SALAER MAERZ 2025 | SALA80E5ED528784F48B451A4175649C112 9988776655/1XXXX 250325CH7LMNQRTS</t>
         </is>
       </c>
       <c r="J47" s="5" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>22.05</v>
+        <v>0</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>22.05</v>
+        <v>-4000</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>grocery_1</t>
+          <t>income_1</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6227,11 +6504,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TX-000027</t>
+          <t>TX-000073.3</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
-        <v>45743</v>
+        <v>45741</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6240,41 +6517,46 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Refund</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Mobilität</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Styling und Wellness</t>
+          <t>Öffentlicher Verkehr</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leben / Styling und Wellness</t>
+          <t>Mobilität / Öffentlicher Verkehr</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>THE BODY SHOP</t>
+          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>SALAER MAERZ 2025 | SALA80E5ED528784F48B451A4175649C112 9988776655/1XXXX 250325CH7LMNQRTS</t>
         </is>
       </c>
       <c r="J48" s="5" t="n">
-        <v>0</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>24.95</v>
+        <v>0</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>24.95</v>
+        <v>-96.90000000000001</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>wellness_1</t>
+          <t>income_1</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -6286,11 +6568,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TX-000028</t>
+          <t>TX-000035</t>
         </is>
       </c>
       <c r="B49" s="11" t="n">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6304,36 +6586,36 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Mobilität</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Öffentlicher Verkehr</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Freizeit / Gastronomie</t>
+          <t>Mobilität / Öffentlicher Verkehr</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>YOOJI'S ROSENGARTEN</t>
+          <t>TRANSPORTS PUBLICS FRIBOURGEOIS (FAIRTIQ) N/A PAYMENT ID 250326064915818975ZX BESTELLNUMMER</t>
         </is>
       </c>
       <c r="J49" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>11.9</v>
+        <v>62.6</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>11.9</v>
+        <v>62.6</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>gastronomy_2</t>
+          <t>transport_1</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -6345,11 +6627,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TX-000029</t>
+          <t>TX-000036</t>
         </is>
       </c>
       <c r="B50" s="11" t="n">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6363,36 +6645,36 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Handwerk und Garten</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Freizeit / Gastronomie</t>
+          <t>Wohnen / Handwerk und Garten</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>YOOJI'S ROSENGARTEN</t>
+          <t>JUMBO-7782 INDUSTRIEPARK</t>
         </is>
       </c>
       <c r="J50" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>43.5</v>
+        <v>10.9</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>43.5</v>
+        <v>10.9</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>gastronomy_2</t>
+          <t>home_1</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -6404,11 +6686,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TX-000030</t>
+          <t>TX-000037</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6437,21 +6719,26 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>COFFEE AND PLANTS</t>
+          <t>+41796666222 KEBAB, IMBISS</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>MITTEILUNGEN: KEBAB</t>
         </is>
       </c>
       <c r="J51" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>gastronomy_3</t>
+          <t>gastronomy_4</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -6463,11 +6750,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TX-000032</t>
+          <t>TX-000038</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6481,36 +6768,41 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Detail-Lebensmittel</t>
+          <t>Familie</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Einkaufen / Detail-Lebensmittel</t>
+          <t>Leben / Familie</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>YUMIHANA</t>
+          <t>FAMILIENKASSE MUSTERHAUSEN SENDER REFERENZ: FAMILIENZULAGE</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>90-33445566</t>
         </is>
       </c>
       <c r="J52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>18.55</v>
+        <v>200</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>18.55</v>
+        <v>200</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>grocery_2</t>
+          <t>family_1</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6522,11 +6814,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TX-000033</t>
+          <t>TX-000093</t>
         </is>
       </c>
       <c r="B53" s="11" t="n">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6535,41 +6827,46 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Transfer</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Vorsorge</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Detail-Lebensmittel</t>
+          <t>Säule 3a</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Einkaufen / Detail-Lebensmittel</t>
+          <t>Vorsorge / Säule 3a</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>YUMI HANA</t>
+          <t>VORSORGESTIFTUNG MUSTERHAUSEN SENDER REFERENZ: SAEULE 3A</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>90-11223344</t>
         </is>
       </c>
       <c r="J53" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>26.8</v>
+        <v>200</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>26.8</v>
+        <v>200</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>grocery_2</t>
+          <t>savings_1</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6581,7 +6878,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TX-000034</t>
+          <t>TX-000024</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
@@ -6599,36 +6896,36 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Supermärkte</t>
+          <t>Kommunikation</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Einkaufen / Supermärkte</t>
+          <t>Wohnen / Kommunikation</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>COOP - 7811 QUAI WEST</t>
+          <t>APPLE.COM/BILL</t>
         </is>
       </c>
       <c r="J54" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>7.75</v>
+        <v>2</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>7.75</v>
+        <v>2</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>supermarket_1</t>
+          <t>communication_2</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6640,11 +6937,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TX-000018</t>
+          <t>TX-000025</t>
         </is>
       </c>
       <c r="B55" s="11" t="n">
-        <v>45744</v>
+        <v>45743</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6658,36 +6955,36 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mobilität</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Öffentlicher Verkehr</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Mobilität / Öffentlicher Verkehr</t>
+          <t>Freizeit / Gastronomie</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>TRANSPORTS PUBLICS FRIBOURGEOIS (FAIRTIQ) N/A PAYMENT ID 250328064754083058ZX BESTELLNUMMER</t>
+          <t>YOOJI'S ROSENGARTEN</t>
         </is>
       </c>
       <c r="J55" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>34.3</v>
+        <v>6.9</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>34.3</v>
+        <v>6.9</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>transport_1</t>
+          <t>gastronomy_2</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6699,11 +6996,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TX-000019</t>
+          <t>TX-000026</t>
         </is>
       </c>
       <c r="B56" s="11" t="n">
-        <v>45744</v>
+        <v>45743</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6732,17 +7029,17 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>SUMUP *BACKEREI ZUR K</t>
+          <t>CONFISERIE SPRÜNGLI AG</t>
         </is>
       </c>
       <c r="J56" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>11.1</v>
+        <v>22.05</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>11.1</v>
+        <v>22.05</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -6758,11 +7055,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TX-000020</t>
+          <t>TX-000027</t>
         </is>
       </c>
       <c r="B57" s="11" t="n">
-        <v>45744</v>
+        <v>45743</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6776,36 +7073,36 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sonstiges Einkaufen</t>
+          <t>Styling und Wellness</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Einkaufen / Sonstiges Einkaufen</t>
+          <t>Leben / Styling und Wellness</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>KKIOSK 45810</t>
+          <t>THE BODY SHOP</t>
         </is>
       </c>
       <c r="J57" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>7.1</v>
+        <v>24.95</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>7.1</v>
+        <v>24.95</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>shopping_1</t>
+          <t>wellness_1</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6817,11 +7114,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TX-000021</t>
+          <t>TX-000028</t>
         </is>
       </c>
       <c r="B58" s="11" t="n">
-        <v>45744</v>
+        <v>45743</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6835,36 +7132,36 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gesundheit</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Leben / Gesundheit</t>
+          <t>Freizeit / Gastronomie</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>BAHNHOF APOTHEKE AG</t>
+          <t>YOOJI'S ROSENGARTEN</t>
         </is>
       </c>
       <c r="J58" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>24.4</v>
+        <v>11.9</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>24.4</v>
+        <v>11.9</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>health_1</t>
+          <t>gastronomy_2</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6876,11 +7173,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TX-000022</t>
+          <t>TX-000029</t>
         </is>
       </c>
       <c r="B59" s="11" t="n">
-        <v>45744</v>
+        <v>45743</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6894,36 +7191,36 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Detail-Lebensmittel</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Einkaufen / Detail-Lebensmittel</t>
+          <t>Freizeit / Gastronomie</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>BÄCKEREI HUG</t>
+          <t>YOOJI'S ROSENGARTEN</t>
         </is>
       </c>
       <c r="J59" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>8.1</v>
+        <v>43.5</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>8.1</v>
+        <v>43.5</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>grocery_1</t>
+          <t>gastronomy_2</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6935,11 +7232,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TX-000023</t>
+          <t>TX-000030</t>
         </is>
       </c>
       <c r="B60" s="11" t="n">
-        <v>45744</v>
+        <v>45743</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6953,36 +7250,36 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Supermärkte</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Einkaufen / Supermärkte</t>
+          <t>Freizeit / Gastronomie</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>MIGROS M RIVERSIDE (7741)</t>
+          <t>COFFEE AND PLANTS</t>
         </is>
       </c>
       <c r="J60" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>28.35</v>
+        <v>10</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>28.35</v>
+        <v>10</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>supermarket_1</t>
+          <t>gastronomy_3</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6994,11 +7291,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TX-000015</t>
+          <t>TX-000032</t>
         </is>
       </c>
       <c r="B61" s="11" t="n">
-        <v>45745</v>
+        <v>45743</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7027,21 +7324,21 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>BÄCKEREI HUG</t>
+          <t>YUMIHANA</t>
         </is>
       </c>
       <c r="J61" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>8.5</v>
+        <v>18.55</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>8.5</v>
+        <v>18.55</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>grocery_1</t>
+          <t>grocery_2</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -7053,11 +7350,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TX-000016</t>
+          <t>TX-000033</t>
         </is>
       </c>
       <c r="B62" s="11" t="n">
-        <v>45745</v>
+        <v>45743</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7076,31 +7373,31 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Supermärkte</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Einkaufen / Supermärkte</t>
+          <t>Einkaufen / Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>MIGROS M RIVERSIDE (7741)</t>
+          <t>YUMI HANA</t>
         </is>
       </c>
       <c r="J62" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>2.9</v>
+        <v>26.8</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>2.9</v>
+        <v>26.8</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>supermarket_1</t>
+          <t>grocery_2</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -7112,11 +7409,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TX-000017</t>
+          <t>TX-000034</t>
         </is>
       </c>
       <c r="B63" s="11" t="n">
-        <v>45745</v>
+        <v>45743</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7130,36 +7427,36 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kommunikation</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Wohnen / Kommunikation</t>
+          <t>Einkaufen / Supermärkte</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>SUNRISE GMBH POSTFACH 8050 ZURICH</t>
+          <t>COOP - 7811 QUAI WEST</t>
         </is>
       </c>
       <c r="J63" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>49.6</v>
+        <v>7.75</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>49.6</v>
+        <v>7.75</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>communication_1</t>
+          <t>supermarket_1</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7171,11 +7468,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TX-000010</t>
+          <t>TX-000018</t>
         </is>
       </c>
       <c r="B64" s="11" t="n">
-        <v>45746</v>
+        <v>45744</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7189,36 +7486,36 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Mobilität</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Öffentlicher Verkehr</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Freizeit / Gastronomie</t>
+          <t>Mobilität / Öffentlicher Verkehr</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>SIGNOR ROSSI</t>
+          <t>TRANSPORTS PUBLICS FRIBOURGEOIS (FAIRTIQ) N/A PAYMENT ID 250328064754083058ZX BESTELLNUMMER</t>
         </is>
       </c>
       <c r="J64" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>20</v>
+        <v>34.3</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>20</v>
+        <v>34.3</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>gastronomy_2</t>
+          <t>transport_1</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7230,11 +7527,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TX-000011</t>
+          <t>TX-000019</t>
         </is>
       </c>
       <c r="B65" s="11" t="n">
-        <v>45746</v>
+        <v>45744</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7253,31 +7550,31 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Supermärkte</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Einkaufen / Supermärkte</t>
+          <t>Einkaufen / Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>MIGROS MARKTHALLE (8812)</t>
+          <t>SUMUP *BACKEREI ZUR K</t>
         </is>
       </c>
       <c r="J65" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>20.7</v>
+        <v>11.1</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>20.7</v>
+        <v>11.1</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>supermarket_1</t>
+          <t>grocery_1</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7289,11 +7586,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TX-000012</t>
+          <t>TX-000020</t>
         </is>
       </c>
       <c r="B66" s="11" t="n">
-        <v>45746</v>
+        <v>45744</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7307,36 +7604,36 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Sonstiges Einkaufen</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Freizeit / Gastronomie</t>
+          <t>Einkaufen / Sonstiges Einkaufen</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>MIGROS CITY TAKE AWAY (6624)</t>
+          <t>KKIOSK 45810</t>
         </is>
       </c>
       <c r="J66" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>3.9</v>
+        <v>7.1</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>3.9</v>
+        <v>7.1</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>gastronomy_1</t>
+          <t>shopping_1</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7348,11 +7645,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TX-000013</t>
+          <t>TX-000021</t>
         </is>
       </c>
       <c r="B67" s="11" t="n">
-        <v>45746</v>
+        <v>45744</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7366,36 +7663,36 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kultur</t>
+          <t>Gesundheit</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Freizeit / Kultur</t>
+          <t>Leben / Gesundheit</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>BYRO</t>
+          <t>BAHNHOF APOTHEKE AG</t>
         </is>
       </c>
       <c r="J67" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>15</v>
+        <v>24.4</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>15</v>
+        <v>24.4</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>life_1</t>
+          <t>health_1</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7407,11 +7704,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TX-000014</t>
+          <t>TX-000022</t>
         </is>
       </c>
       <c r="B68" s="11" t="n">
-        <v>45746</v>
+        <v>45744</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7425,36 +7722,36 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sonstiges Leben</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Leben / Sonstiges Leben</t>
+          <t>Einkaufen / Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>BYRO</t>
+          <t>BÄCKEREI HUG</t>
         </is>
       </c>
       <c r="J68" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>36.8</v>
+        <v>8.1</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>36.8</v>
+        <v>8.1</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>life_1</t>
+          <t>grocery_1</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7466,11 +7763,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TX-000003</t>
+          <t>TX-000023</t>
         </is>
       </c>
       <c r="B69" s="11" t="n">
-        <v>45747</v>
+        <v>45744</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7489,31 +7786,31 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Detail-Lebensmittel</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Einkaufen / Detail-Lebensmittel</t>
+          <t>Einkaufen / Supermärkte</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>CITY TANKSTELLE</t>
+          <t>MIGROS M RIVERSIDE (7741)</t>
         </is>
       </c>
       <c r="J69" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>10.34</v>
+        <v>28.35</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>10.34</v>
+        <v>28.35</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>grocery_3</t>
+          <t>supermarket_1</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -7525,11 +7822,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TX-000004</t>
+          <t>TX-000015</t>
         </is>
       </c>
       <c r="B70" s="11" t="n">
-        <v>45747</v>
+        <v>45745</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7558,21 +7855,21 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>CITY TANKSTELLE</t>
+          <t>BÄCKEREI HUG</t>
         </is>
       </c>
       <c r="J70" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>6.55</v>
+        <v>8.5</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>6.55</v>
+        <v>8.5</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>grocery_3</t>
+          <t>grocery_1</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -7584,11 +7881,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TX-000006</t>
+          <t>TX-000016</t>
         </is>
       </c>
       <c r="B71" s="11" t="n">
-        <v>45747</v>
+        <v>45745</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7607,31 +7904,31 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sonstiges Einkaufen</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Einkaufen / Sonstiges Einkaufen</t>
+          <t>Einkaufen / Supermärkte</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>KKIOSK 45810</t>
+          <t>MIGROS M RIVERSIDE (7741)</t>
         </is>
       </c>
       <c r="J71" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>7.55</v>
+        <v>2.9</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>7.55</v>
+        <v>2.9</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>shopping_1</t>
+          <t>supermarket_1</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -7643,11 +7940,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TX-000007</t>
+          <t>TX-000017</t>
         </is>
       </c>
       <c r="B72" s="11" t="n">
-        <v>45747</v>
+        <v>45745</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7661,36 +7958,36 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Supermärkte</t>
+          <t>Kommunikation</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Einkaufen / Supermärkte</t>
+          <t>Wohnen / Kommunikation</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>MIGROS MARKTHALLE (8812)</t>
+          <t>SUNRISE GMBH POSTFACH 8050 ZURICH</t>
         </is>
       </c>
       <c r="J72" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>22.2</v>
+        <v>49.6</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>22.2</v>
+        <v>49.6</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>supermarket_1</t>
+          <t>communication_1</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -7702,11 +7999,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TX-000008</t>
+          <t>TX-000010</t>
         </is>
       </c>
       <c r="B73" s="11" t="n">
-        <v>45747</v>
+        <v>45746</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7720,41 +8017,36 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Finanzen</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Finanzen / Fees</t>
+          <t>Freizeit / Gastronomie</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>PREIS FÜR BANKPAKET SMART 02.2025</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>PREIS FÜR BANKPAKET SMART 02.2025</t>
+          <t>SIGNOR ROSSI</t>
         </is>
       </c>
       <c r="J73" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>finance_2</t>
+          <t>gastronomy_2</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -7766,11 +8058,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TX-000009</t>
+          <t>TX-000011</t>
         </is>
       </c>
       <c r="B74" s="11" t="n">
-        <v>45747</v>
+        <v>45746</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -7784,41 +8076,36 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Miete und Hypothek</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Wohnen / Miete und Hypothek</t>
+          <t>Einkaufen / Supermärkte</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>FINANZVERWALTUNG STADT SOLOTHURN</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2025/04/01 / 7045128</t>
+          <t>MIGROS MARKTHALLE (8812)</t>
         </is>
       </c>
       <c r="J74" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>1774</v>
+        <v>20.7</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>1774</v>
+        <v>20.7</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>housing_1</t>
+          <t>supermarket_1</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -7830,11 +8117,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TX-000064</t>
+          <t>TX-000012</t>
         </is>
       </c>
       <c r="B75" s="11" t="n">
-        <v>45747</v>
+        <v>45746</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -7848,36 +8135,36 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Styling und Wellness</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Leben / Styling und Wellness</t>
+          <t>Freizeit / Gastronomie</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>SUMUP *COIFFEUR HAIRCUT</t>
+          <t>MIGROS CITY TAKE AWAY (6624)</t>
         </is>
       </c>
       <c r="J75" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>50</v>
+        <v>3.9</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>50</v>
+        <v>3.9</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>wellness_2</t>
+          <t>gastronomy_1</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -7889,79 +8176,79 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TX-000089</t>
+          <t>TX-000013</t>
         </is>
       </c>
       <c r="B76" s="11" t="n">
-        <v>45748</v>
+        <v>45746</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Refund</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Krankenkasse</t>
+          <t>Kultur</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Leben / Krankenkasse</t>
+          <t>Freizeit / Kultur</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>MUSTER UND BEISPIEL GEMEINSCHAFTSKONTO MUSTERWEG 1 4600 OLTEN</t>
+          <t>BYRO</t>
         </is>
       </c>
       <c r="J76" s="5" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>-120</v>
+        <v>15</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>refund_example_amount_1</t>
+          <t>life_1</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>export.202504.categorized.csv</t>
+          <t>export.202503.categorized.csv</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TX-000090</t>
+          <t>TX-000014</t>
         </is>
       </c>
       <c r="B77" s="11" t="n">
-        <v>45748</v>
+        <v>45746</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Refund</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7971,110 +8258,110 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Familie</t>
+          <t>Sonstiges Leben</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Leben / Familie</t>
+          <t>Leben / Sonstiges Leben</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>MUSTER UND BEISPIEL GEMEINSCHAFTSKONTO MUSTERWEG 1 4600 OLTEN</t>
+          <t>BYRO</t>
         </is>
       </c>
       <c r="J77" s="5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>0</v>
+        <v>36.8</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>-15</v>
+        <v>36.8</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>refund_example_counterparty_1</t>
+          <t>life_1</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>export.202504.categorized.csv</t>
+          <t>export.202503.categorized.csv</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TX-000061</t>
+          <t>TX-000003</t>
         </is>
       </c>
       <c r="B78" s="11" t="n">
-        <v>45751</v>
+        <v>45747</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Refund</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Reisen und Erleben</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Freizeit / Reisen und Erleben</t>
+          <t>Einkaufen / Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>UEFA WOMEN'S EURO 2025 NYON</t>
+          <t>CITY TANKSTELLE</t>
         </is>
       </c>
       <c r="J78" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>0</v>
+        <v>10.34</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>-100</v>
+        <v>10.34</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>refund_3</t>
+          <t>grocery_3</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>export.202504.categorized.csv</t>
+          <t>export.202503.categorized.csv</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TX-000084</t>
+          <t>TX-000004</t>
         </is>
       </c>
       <c r="B79" s="11" t="n">
-        <v>45752</v>
+        <v>45747</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -8089,51 +8376,51 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Supermärkte</t>
+          <t>Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Einkaufen / Supermärkte</t>
+          <t>Einkaufen / Detail-Lebensmittel</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>MIGROS MARKTHALLE (8812)</t>
+          <t>CITY TANKSTELLE</t>
         </is>
       </c>
       <c r="J79" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>108.9</v>
+        <v>6.55</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>108.9</v>
+        <v>6.55</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>supermarket_1</t>
+          <t>grocery_3</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>export.202504.categorized.csv</t>
+          <t>export.202503.categorized.csv</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TX-000085</t>
+          <t>TX-000006</t>
         </is>
       </c>
       <c r="B80" s="11" t="n">
-        <v>45759</v>
+        <v>45747</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -8148,115 +8435,110 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Supermärkte</t>
+          <t>Sonstiges Einkaufen</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Einkaufen / Supermärkte</t>
+          <t>Einkaufen / Sonstiges Einkaufen</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>COOP-5510 RIVERSIDE REST.</t>
+          <t>KKIOSK 45810</t>
         </is>
       </c>
       <c r="J80" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>76.3</v>
+        <v>7.55</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>76.3</v>
+        <v>7.55</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>supermarket_1</t>
+          <t>shopping_1</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>export.202504.categorized.csv</t>
+          <t>export.202503.categorized.csv</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TX-000062</t>
+          <t>TX-000007</t>
         </is>
       </c>
       <c r="B81" s="11" t="n">
-        <v>45763</v>
+        <v>45747</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Einkommen</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lohn</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Einkommen / Lohn</t>
+          <t>Einkaufen / Supermärkte</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>FIKTIVE LOHN AG PERSONALABTEILUNG</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>LOHNBEISPIEL APRIL 2025 | DEMO REF 001</t>
+          <t>MIGROS MARKTHALLE (8812)</t>
         </is>
       </c>
       <c r="J81" s="5" t="n">
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>-4200</v>
+        <v>22.2</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>income_example_counterparty_1</t>
+          <t>supermarket_1</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>export.202504.categorized.csv</t>
+          <t>export.202503.categorized.csv</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TX-000063</t>
+          <t>TX-000008</t>
         </is>
       </c>
       <c r="B82" s="11" t="n">
-        <v>45764</v>
+        <v>45747</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -8271,155 +8553,175 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spenden</t>
+          <t>Fees</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Finanzen / Spenden</t>
+          <t>Finanzen / Fees</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>ANONYMISIERTER VEREIN MITTEILUNGEN: DEMO-ZWECK JAHRESBEITRAG</t>
+          <t>PREIS FÜR BANKPAKET SMART 02.2025</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>PREIS FÜR BANKPAKET SMART 02.2025</t>
         </is>
       </c>
       <c r="J82" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>expense_example_counterparty_iban_1</t>
+          <t>finance_2</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>export.202504.categorized.csv</t>
+          <t>export.202503.categorized.csv</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TX-000065</t>
+          <t>TX-000009</t>
         </is>
       </c>
       <c r="B83" s="11" t="n">
-        <v>45765</v>
+        <v>45747</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Wohnen</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Miete und Hypothek</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Wohnen / Miete und Hypothek</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>FIKTIVE DIGITAL GMBH</t>
+          <t>FINANZVERWALTUNG STADT SOLOTHURN</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>PAYMENT ID 000A00D0 BESTELLNUMMER AB00CD00</t>
+          <t>2025/04/01 / 7045128</t>
         </is>
       </c>
       <c r="J83" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>33.7</v>
+        <v>1774</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>33.7</v>
+        <v>1774</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>housing_1</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>export.202504.categorized.csv</t>
+          <t>export.202503.categorized.csv</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TX-000066</t>
+          <t>TX-000064</t>
         </is>
       </c>
       <c r="B84" s="11" t="n">
-        <v>45766</v>
+        <v>45747</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Styling und Wellness</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Leben / Styling und Wellness</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>FIKTIVE POST AG</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>PAYMENT ID AB0CD0EF00GH0IJ0 BESTELLNUMMER MYS_AB0CD0EF00GH0I</t>
+          <t>SUMUP *COIFFEUR HAIRCUT</t>
         </is>
       </c>
       <c r="J84" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>wellness_2</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>export.202504.categorized.csv</t>
+          <t>export.202503.categorized.csv</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TX-000086</t>
+          <t>TX-000089</t>
         </is>
       </c>
       <c r="B85" s="11" t="n">
-        <v>45766</v>
+        <v>45748</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -8428,41 +8730,41 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Refund</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Supermärkte</t>
+          <t>Krankenkasse</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Einkaufen / Supermärkte</t>
+          <t>Leben / Krankenkasse</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>MIGROS M RIVERSIDE (7741)</t>
+          <t>MUSTER UND BEISPIEL GEMEINSCHAFTSKONTO MUSTERWEG 1 4600 OLTEN</t>
         </is>
       </c>
       <c r="J85" s="5" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>54.85</v>
+        <v>0</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>54.85</v>
+        <v>-120</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>supermarket_1</t>
+          <t>refund_example_amount_1</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -8474,44 +8776,54 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TX-000067</t>
+          <t>TX-000090</t>
         </is>
       </c>
       <c r="B86" s="11" t="n">
-        <v>45767</v>
+        <v>45748</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
           <t>2025-04</t>
         </is>
       </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Refund</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Familie</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Leben / Familie</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>FIKTIVER SCHUHLADEN BIEL</t>
+          <t>MUSTER UND BEISPIEL GEMEINSCHAFTSKONTO MUSTERWEG 1 4600 OLTEN</t>
         </is>
       </c>
       <c r="J86" s="5" t="n">
-        <v>49.9</v>
+        <v>15</v>
       </c>
       <c r="K86" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>-49.9</v>
+        <v>-15</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>refund_example_counterparty_1</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -8523,44 +8835,54 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TX-000068</t>
+          <t>TX-000061</t>
         </is>
       </c>
       <c r="B87" s="11" t="n">
-        <v>45768</v>
+        <v>45751</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
           <t>2025-04</t>
         </is>
       </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Refund</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Freizeit</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Reisen und Erleben</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Freizeit / Reisen und Erleben</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>FIKTIVER FAHRSCHEIN BERLIN DEUTSCHLAND</t>
+          <t>UEFA WOMEN'S EURO 2025 NYON</t>
         </is>
       </c>
       <c r="J87" s="5" t="n">
-        <v>19.15</v>
+        <v>100</v>
       </c>
       <c r="K87" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>-19.15</v>
+        <v>-100</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>refund_3</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -8572,11 +8894,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>TX-000069</t>
+          <t>TX-000084</t>
         </is>
       </c>
       <c r="B88" s="11" t="n">
-        <v>45769</v>
+        <v>45752</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -8590,36 +8912,36 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Finanzen</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bargeldbezug</t>
+          <t>Supermärkte</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Finanzen / Bargeldbezug</t>
+          <t>Einkaufen / Supermärkte</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>BAHNHOF</t>
+          <t>MIGROS MARKTHALLE (8812)</t>
         </is>
       </c>
       <c r="J88" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K88" s="5" t="n">
-        <v>143.5</v>
+        <v>108.9</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>143.5</v>
+        <v>108.9</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>finance_1</t>
+          <t>supermarket_1</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -8631,11 +8953,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TX-000087</t>
+          <t>TX-000085</t>
         </is>
       </c>
       <c r="B89" s="11" t="n">
-        <v>45773</v>
+        <v>45759</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -8664,17 +8986,17 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>MIGROS MARKTHALLE (8812)</t>
+          <t>COOP-5510 RIVERSIDE REST.</t>
         </is>
       </c>
       <c r="J89" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>121.6</v>
+        <v>76.3</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>121.6</v>
+        <v>76.3</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
@@ -8690,69 +9012,895 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>TX-000062</t>
+        </is>
+      </c>
+      <c r="B90" s="11" t="n">
+        <v>45763</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Einkommen</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Nebenerwerb</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Einkommen / Nebenerwerb</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>FIKTIVE LOHN AG PERSONALABTEILUNG</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>LOHNBEISPIEL APRIL 2025 | DEMO REF 001</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>4200</v>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>-4200</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>income_example_counterparty_1</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>TX-000063</t>
+        </is>
+      </c>
+      <c r="B91" s="11" t="n">
+        <v>45764</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Finanzen</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Spenden</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Finanzen / Spenden</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>ANONYMISIERTER VEREIN MITTEILUNGEN: DEMO-ZWECK JAHRESBEITRAG</t>
+        </is>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>expense_example_counterparty_iban_1</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>TX-000065</t>
+        </is>
+      </c>
+      <c r="B92" s="11" t="n">
+        <v>45765</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>FIKTIVE DIGITAL GMBH</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>PAYMENT ID 000A00D0 BESTELLNUMMER AB00CD00</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>TX-000066</t>
+        </is>
+      </c>
+      <c r="B93" s="11" t="n">
+        <v>45766</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>FIKTIVE POST AG</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>PAYMENT ID AB0CD0EF00GH0IJ0 BESTELLNUMMER MYS_AB0CD0EF00GH0I</t>
+        </is>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>TX-000086</t>
+        </is>
+      </c>
+      <c r="B94" s="11" t="n">
+        <v>45766</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Einkaufen / Supermärkte</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>MIGROS M RIVERSIDE (7741)</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>54.85</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>54.85</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>supermarket_1</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>TX-000067</t>
+        </is>
+      </c>
+      <c r="B95" s="11" t="n">
+        <v>45767</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>FIKTIVER SCHUHLADEN BIEL</t>
+        </is>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>-49.9</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>TX-000068</t>
+        </is>
+      </c>
+      <c r="B96" s="11" t="n">
+        <v>45768</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>FIKTIVER FAHRSCHEIN BERLIN DEUTSCHLAND</t>
+        </is>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>-19.15</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>TX-000069</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="n">
+        <v>45769</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Finanzen</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Bargeldbezug</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Finanzen / Bargeldbezug</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>BAHNHOF</t>
+        </is>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>finance_1</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>TX-000095.1</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="n">
+        <v>45772</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Einkommen</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Familienzulage</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Einkommen / Familienzulage</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>SALAER APRIL 2025 | SALA00000000000000000000000000000004 9988776655/1XXXX 250425CH0EXMPL04</t>
+        </is>
+      </c>
+      <c r="J98" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>-200</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>income_1</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>TX-000095.2</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="n">
+        <v>45772</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Einkommen</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Lohn</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Einkommen / Lohn</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>SALAER APRIL 2025 | SALA00000000000000000000000000000004 9988776655/1XXXX 250425CH0EXMPL04</t>
+        </is>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>4000</v>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>-4000</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>income_1</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>TX-000095.3</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="n">
+        <v>45772</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Einkommen</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Einkommen / Bonus</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>SALAER APRIL 2025 | SALA00000000000000000000000000000004 9988776655/1XXXX 250425CH0EXMPL04</t>
+        </is>
+      </c>
+      <c r="J100" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>income_1</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>TX-000095.4</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="n">
+        <v>45772</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Refund</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Mobilität</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Öffentlicher Verkehr</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Mobilität / Öffentlicher Verkehr</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>SALAER APRIL 2025 | SALA00000000000000000000000000000004 9988776655/1XXXX 250425CH0EXMPL04</t>
+        </is>
+      </c>
+      <c r="J101" s="5" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>-45.5</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>income_1</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>TX-000087</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="n">
+        <v>45773</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Einkaufen</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Supermärkte</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Einkaufen / Supermärkte</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>MIGROS MARKTHALLE (8812)</t>
+        </is>
+      </c>
+      <c r="J102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>supermarket_1</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>TX-000094</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="n">
+        <v>45773</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Vorsorge</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Säule 3a</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Vorsorge / Säule 3a</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>VORSORGESTIFTUNG MUSTERHAUSEN SENDER REFERENZ: SAEULE 3A</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>90-11223344</t>
+        </is>
+      </c>
+      <c r="J103" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>savings_1</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>export.202504.categorized.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
           <t>TX-000088</t>
         </is>
       </c>
-      <c r="B90" s="11" t="n">
+      <c r="B104" s="11" t="n">
         <v>45777</v>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>Wohnen</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>Miete und Hypothek</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>Wohnen / Miete und Hypothek</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="H104" t="inlineStr">
         <is>
           <t>FINANZVERWALTUNG STADT SOLOTHURN</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t>2025/05/01 / 7045128</t>
         </is>
       </c>
-      <c r="J90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" s="5" t="n">
+      <c r="J104" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" s="5" t="n">
         <v>1774</v>
       </c>
-      <c r="L90" s="5" t="n">
+      <c r="L104" s="5" t="n">
         <v>1774</v>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t>housing_1</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr">
+      <c r="N104" t="inlineStr">
         <is>
           <t>export.202504.categorized.csv</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N90"/>
+  <autoFilter ref="A1:N104"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8763,7 +9911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9621,21 +10769,21 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mobilität</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Öffentlicher Verkehr</t>
+          <t>Haushalt</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TRANSPORTS PUBLICS FRIBOURGEOIS (FAIRTIQ) N/A PAYMENT ID 250326064915818975ZX BESTELLNUMMER</t>
+          <t>COOP-5510 RIVERSIDE REST.</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>62.6</v>
+        <v>31.2</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -9644,7 +10792,7 @@
         <v>1</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.646</v>
+        <v>0.3547</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
@@ -9653,21 +10801,21 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mobilität</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Öffentlicher Verkehr</t>
+          <t>Haushalt</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TRANSPORTS PUBLICS FRIBOURGEOIS (FAIRTIQ) N/A PAYMENT ID 250328064754083058ZX BESTELLNUMMER</t>
+          <t>MANOR AG - 771 (CENTRA)</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>34.3</v>
+        <v>23.95</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -9676,7 +10824,7 @@
         <v>1</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.354</v>
+        <v>0.2723</v>
       </c>
       <c r="H28" t="n">
         <v>2</v>
@@ -9695,11 +10843,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>COOP-5510 RIVERSIDE REST.</t>
+          <t>MIGROS MARKTHALLE</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>31.2</v>
+        <v>18.9</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -9708,10 +10856,10 @@
         <v>1</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.3547</v>
+        <v>0.2149</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -9727,11 +10875,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MANOR AG - 771 (CENTRA)</t>
+          <t>ONLINE HAUSHALT AG</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>23.95</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -9740,30 +10888,30 @@
         <v>1</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.2723</v>
+        <v>0.158</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Haushalt</t>
+          <t>Styling und Wellness</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MIGROS MARKTHALLE</t>
+          <t>SUMUP *COIFFEUR HAIRCUT</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>18.9</v>
+        <v>50</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -9772,62 +10920,62 @@
         <v>1</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.2149</v>
+        <v>0.6258</v>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Haushalt</t>
+          <t>Styling und Wellness</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ONLINE HAUSHALT AG</t>
+          <t>THE BODY SHOP</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>13.9</v>
+        <v>29.9</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.158</v>
+        <v>0.3742</v>
       </c>
       <c r="H32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Styling und Wellness</t>
+          <t>Kommunikation</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SUMUP *COIFFEUR HAIRCUT</t>
+          <t>SUNRISE GMBH POSTFACH 8050 ZURICH</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>50</v>
+        <v>49.6</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -9836,7 +10984,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.6258</v>
+        <v>0.7058</v>
       </c>
       <c r="H33" t="n">
         <v>1</v>
@@ -9845,30 +10993,30 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Styling und Wellness</t>
+          <t>Kommunikation</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>THE BODY SHOP</t>
+          <t>CLOUDSERVICE INC SAN</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>29.9</v>
+        <v>18.67</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.3742</v>
+        <v>0.2657</v>
       </c>
       <c r="H34" t="n">
         <v>2</v>
@@ -9887,11 +11035,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SUNRISE GMBH POSTFACH 8050 ZURICH</t>
+          <t>APPLE.COM/BILL</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>49.6</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -9900,30 +11048,30 @@
         <v>1</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.7058</v>
+        <v>0.0285</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kommunikation</t>
+          <t>Sonstiges Leben</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLOUDSERVICE INC SAN</t>
+          <t>BYRO</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>18.67</v>
+        <v>36.8</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
@@ -9932,30 +11080,30 @@
         <v>1</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.2657</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Wohnen</t>
+          <t>Mobilität</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kommunikation</t>
+          <t>Privater Verkehr</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>APPLE.COM/BILL</t>
+          <t>MOBILITY MUSTER GENOSSENSCHAFT 6343 ROTKREUZ</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>2</v>
+        <v>26.7</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -9964,30 +11112,30 @@
         <v>1</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.0285</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Finanzen</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sonstiges Leben</t>
+          <t>Spenden</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BYRO</t>
+          <t>ANONYMISIERTER VEREIN MITTEILUNGEN: DEMO-ZWECK JAHRESBEITRAG</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>36.8</v>
+        <v>25</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
@@ -10005,21 +11153,21 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mobilität</t>
+          <t>Leben</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Privater Verkehr</t>
+          <t>Gesundheit</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MOBILITY MUSTER GENOSSENSCHAFT 6343 ROTKREUZ</t>
+          <t>BAHNHOF APOTHEKE AG</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>26.7</v>
+        <v>24.4</v>
       </c>
       <c r="E39" t="n">
         <v>1</v>
@@ -10037,21 +11185,21 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Finanzen</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Spenden</t>
+          <t>Kultur</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ANONYMISIERTER VEREIN MITTEILUNGEN: DEMO-ZWECK JAHRESBEITRAG</t>
+          <t>BYRO</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E40" t="n">
         <v>1</v>
@@ -10069,24 +11217,24 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Gesundheit</t>
+          <t>Sonstiges Einkaufen</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BAHNHOF APOTHEKE AG</t>
+          <t>KKIOSK 45810</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>24.4</v>
+        <v>14.65</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
         <v>1</v>
@@ -10101,21 +11249,21 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Wohnen</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kultur</t>
+          <t>Handwerk und Garten</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BYRO</t>
+          <t>JUMBO-7782 INDUSTRIEPARK</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>15</v>
+        <v>10.9</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>
@@ -10133,24 +11281,24 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Einkaufen</t>
+          <t>Finanzen</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sonstiges Einkaufen</t>
+          <t>Fees</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>KKIOSK 45810</t>
+          <t>PREIS FÜR BANKPAKET SMART 02.2025</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>14.65</v>
+        <v>5</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
         <v>1</v>
@@ -10165,21 +11313,16 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Wohnen</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Handwerk und Garten</t>
+          <t>Rückerstattungen</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>JUMBO-7782 INDUSTRIEPARK</t>
+          <t>+41790000000 MAX MUSTER</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>10.9</v>
+        <v>-1</v>
       </c>
       <c r="E44" t="n">
         <v>1</v>
@@ -10197,21 +11340,16 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Finanzen</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Fees</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PREIS FÜR BANKPAKET SMART 02.2025</t>
+          <t>FIKTIVE DIGITAL GMBH</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>5</v>
+        <v>33.7</v>
       </c>
       <c r="E45" t="n">
         <v>1</v>
@@ -10220,7 +11358,7 @@
         <v>1</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>1</v>
+        <v>-3.2249</v>
       </c>
       <c r="H45" t="n">
         <v>1</v>
@@ -10229,16 +11367,16 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Rückerstattungen</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>+41790000000 MAX MUSTER</t>
+          <t>FIKTIVE POST AG</t>
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>-1</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="n">
         <v>1</v>
@@ -10247,10 +11385,10 @@
         <v>1</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>1</v>
+        <v>-1.1962</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -10261,11 +11399,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FIKTIVE DIGITAL GMBH</t>
+          <t>UNMATCHED TEST STORE</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>33.7</v>
+        <v>12.4</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
@@ -10274,10 +11412,10 @@
         <v>1</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>-3.2249</v>
+        <v>-1.1866</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -10288,11 +11426,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FIKTIVE POST AG</t>
+          <t>FIKTIVER FAHRSCHEIN BERLIN DEUTSCHLAND</t>
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>12.5</v>
+        <v>-19.15</v>
       </c>
       <c r="E48" t="n">
         <v>1</v>
@@ -10301,10 +11439,10 @@
         <v>1</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>-1.1962</v>
+        <v>1.8325</v>
       </c>
       <c r="H48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -10315,11 +11453,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>UNMATCHED TEST STORE</t>
+          <t>FIKTIVER SCHUHLADEN BIEL</t>
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>12.4</v>
+        <v>-49.9</v>
       </c>
       <c r="E49" t="n">
         <v>1</v>
@@ -10328,25 +11466,30 @@
         <v>1</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>-1.1866</v>
+        <v>4.7751</v>
       </c>
       <c r="H49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Mobilität</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Öffentlicher Verkehr</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FIKTIVER FAHRSCHEIN BERLIN DEUTSCHLAND</t>
+          <t>TRANSPORTS PUBLICS FRIBOURGEOIS (FAIRTIQ) N/A PAYMENT ID 250326064915818975ZX BESTELLNUMMER</t>
         </is>
       </c>
       <c r="D50" s="5" t="n">
-        <v>-19.15</v>
+        <v>62.6</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
@@ -10355,25 +11498,30 @@
         <v>1</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1.8325</v>
+        <v>-0.6667</v>
       </c>
       <c r="H50" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Mobilität</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Öffentlicher Verkehr</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FIKTIVER SCHUHLADEN BIEL</t>
+          <t>TRANSPORTS PUBLICS FRIBOURGEOIS (FAIRTIQ) N/A PAYMENT ID 250328064754083058ZX BESTELLNUMMER</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>-49.9</v>
+        <v>34.3</v>
       </c>
       <c r="E51" t="n">
         <v>1</v>
@@ -10382,62 +11530,62 @@
         <v>1</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>4.7751</v>
+        <v>-0.3653</v>
       </c>
       <c r="H51" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Freizeit</t>
+          <t>Mobilität</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Reisen und Erleben</t>
+          <t>Öffentlicher Verkehr</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>UEFA WOMEN'S EURO 2025 NYON</t>
+          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
         </is>
       </c>
       <c r="D52" s="5" t="n">
-        <v>-100</v>
+        <v>-190.8</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>1</v>
+        <v>2.0319</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Krankenkasse</t>
+          <t>Reisen und Erleben</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MUSTER UND BEISPIEL GEMEINSCHAFTSKONTO MUSTERWEG 1 4600 OLTEN</t>
+          <t>UEFA WOMEN'S EURO 2025 NYON</t>
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>-120</v>
+        <v>-100</v>
       </c>
       <c r="E53" t="n">
         <v>1</v>
@@ -10446,7 +11594,7 @@
         <v>1</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.3571</v>
       </c>
       <c r="H53" t="n">
         <v>1</v>
@@ -10455,37 +11603,101 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Leben</t>
+          <t>Freizeit</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Krankenkasse</t>
+          <t>Reisen und Erleben</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MEDICURA PLUS AG GESUNDHEITSWEG 8 4052 BASEL</t>
+          <t>ALPENWERK AG INDUSTRIESTRASSE 12 CH-5430 WETTINGEN AG</t>
         </is>
       </c>
       <c r="D54" s="5" t="n">
-        <v>-1710.5</v>
+        <v>-180</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
         <v>1</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.9344</v>
+        <v>0.6429</v>
       </c>
       <c r="H54" t="n">
         <v>2</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Krankenkasse</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>MUSTER UND BEISPIEL GEMEINSCHAFTSKONTO MUSTERWEG 1 4600 OLTEN</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>-120</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="12" t="n">
+        <v>0.06560000000000001</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Leben</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Krankenkasse</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>MEDICURA PLUS AG GESUNDHEITSWEG 8 4052 BASEL</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>-1710.5</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="12" t="n">
+        <v>0.9344</v>
+      </c>
+      <c r="H56" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H54"/>
+  <autoFilter ref="A1:H56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>